--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D186"/>
+  <dimension ref="A1:D248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ABVC</t>
+          <t>CBAT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ACFN</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -456,2217 +456,2573 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ALAR</t>
+          <t>AUR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADAMO</t>
+          <t>GEGGL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADAMG</t>
+          <t>ABCL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLSK</t>
+          <t>AVX</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ASPS</t>
+          <t>BAND</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADPT</t>
+          <t>GTEC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AIXC</t>
+          <t>ABTC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>CUE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AVX</t>
+          <t>BGL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AGIG</t>
+          <t>HSDT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>ACGCW</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ENVB</t>
+          <t>PRTH</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GGR</t>
+          <t>CLFD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALVO</t>
+          <t>HVIIU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ALP</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>FUNC</t>
-        </is>
-      </c>
+          <t>ADAMI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MWC</t>
+          <t>EOSE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALZN</t>
+          <t>HWH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ANL</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+          <t>ADAMO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
         <is>
           <t>HUT</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SEDG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMBR</t>
+          <t>KBSX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ANNA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+          <t>AFRI</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t>ICMB</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>NUAI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AOUT</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>MARA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>AGIG</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>KE</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>PRHIZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ATER</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>NATH</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>AGPU</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMTX</t>
+          <t>SVRN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ATLCL</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ONT</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>AIXC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ORKT</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>APPF</t>
+          <t>TAOX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ATLCP</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>REF</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>OWLS</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ARW</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BMNP</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>SECZ</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>ALLT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SATL</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ASST</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BNC</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>SYM</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>ALP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SEGG</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ATLCZ</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BNR</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>TMS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>ALT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SINT</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AUBN</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BRTX</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>VISN</t>
-        </is>
-      </c>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>AVBC</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BUUU</t>
+          <t>AMPH</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>AVT</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>ANGH</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>AVTR</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BWIV</t>
+          <t>ANL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>BAFN</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CENN</t>
+          <t>AOUT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>BANR</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CHSCL</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>BCHT</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CRDF</t>
+          <t>ASBH</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>BDSX</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DFDVW</t>
+          <t>ATLCZ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>BGC</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DLTH</t>
+          <t>ATRA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>BLSH</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>ATRC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>BMRA</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EEIQ</t>
+          <t>AUDC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>BPRN</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ELLA</t>
+          <t>AUGO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>BRR</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ELMT</t>
+          <t>AVTR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>BRRWW</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>BAFN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>BSEM</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ENSC</t>
+          <t>BANX</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>CAC</t>
-        </is>
-      </c>
+      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EPRX</t>
+          <t>BBCP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>CAPN</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EUDA</t>
+          <t>BGC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>CBAT</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FTEK</t>
+          <t>BLSH</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>CFFI</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GAING</t>
+          <t>BLSM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>CFFN</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GAME</t>
+          <t>BMNP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>CHCI</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>BNC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>CHOW</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GECCH</t>
+          <t>BNGO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>CHSCO</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>BNKK</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>CLGN</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GITS</t>
+          <t>BNR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>CLST</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GREEL</t>
+          <t>BRR</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>CMPS</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HMR</t>
+          <t>BRRWW</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>CMTV</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ITHA</t>
+          <t>BUSEP</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>CODA</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JF</t>
+          <t>CDIO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>COSM</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JMSB</t>
+          <t>CDLR</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>CPOP</t>
-        </is>
-      </c>
+      <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>KRSA</t>
+          <t>CHSCL</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>CRSR</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MBINN</t>
+          <t>CHSCM</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>CTKB</t>
-        </is>
-      </c>
+      <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MLAA</t>
+          <t>CLMB</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>CTOR</t>
-        </is>
-      </c>
+      <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MSBIP</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>CVLT</t>
-        </is>
-      </c>
+      <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>CLSK</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>CYPH</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NEWTG</t>
+          <t>CLW</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>CYRX</t>
-        </is>
-      </c>
+      <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OIM</t>
+          <t>CODA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>CZNC</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ORKT</t>
+          <t>COHU</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>DBX</t>
-        </is>
-      </c>
+      <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OXBR</t>
+          <t>COSM</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>DCOM</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OXLCG</t>
+          <t>CPOP</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>DJCO</t>
-        </is>
-      </c>
+      <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OXLCL</t>
+          <t>CRAC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>DMLP</t>
-        </is>
-      </c>
+      <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>OXLCM</t>
+          <t>CRDF</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>DOYU</t>
-        </is>
-      </c>
+      <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>OXLCZ</t>
+          <t>CRSR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>DSGR</t>
-        </is>
-      </c>
+      <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>OXSQG</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>ECOR</t>
-        </is>
-      </c>
+      <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>EFSI</t>
-        </is>
-      </c>
+      <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>CURI</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>EGBN</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PHVS</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>ELOX</t>
-        </is>
-      </c>
+      <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PMEC</t>
+          <t>CYRX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>EOSEW</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>QLEP</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>ETS</t>
-        </is>
-      </c>
+      <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>QNRX</t>
+          <t>DCOM</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>FDBC</t>
-        </is>
-      </c>
+      <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RECT</t>
+          <t>DFDVW</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>FEIM</t>
-        </is>
-      </c>
+      <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RWAYI</t>
+          <t>DRK</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>FIRY</t>
-        </is>
-      </c>
+      <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RWAYL</t>
+          <t>DSGR</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>FNLC</t>
-        </is>
-      </c>
+      <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SAV</t>
+          <t>ECHO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>FRAF</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SFBC</t>
+          <t>ECOR</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>FROG</t>
-        </is>
-      </c>
+      <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SLMBP</t>
+          <t>ECPG</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>FSBW</t>
-        </is>
-      </c>
+      <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>STRC</t>
+          <t>EDHL</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>GCBC</t>
-        </is>
-      </c>
+      <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SUNC</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>GMAB</t>
-        </is>
-      </c>
+      <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>ELOX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>HAFC</t>
-        </is>
-      </c>
+      <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>HALO</t>
-        </is>
-      </c>
+      <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>UCAR</t>
+          <t>ENVB</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>HELP</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>EPRX</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>HNNA</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ESQ</t>
+        </is>
+      </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>HOPE</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>HOWL</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>EUDA</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>HQI</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>FBLA</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>HSCS</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>FDUS</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>HSDT</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>FEIM</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>HTFL</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>FFIV</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>HVIIU</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>FIVN</t>
+        </is>
+      </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>HWH</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>FLGT</t>
+        </is>
+      </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>IBRX</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>FMAO</t>
+        </is>
+      </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>INKT</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>FOSL</t>
+        </is>
+      </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>IOVA</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>FRNM</t>
+        </is>
+      </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>IREN</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>FROG</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>KPLT</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>FTAIM</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>KPRX</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>FTEK</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>LEDS</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>LSBK</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>FTRE</t>
+        </is>
+      </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>LTGO</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>GAME</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>MDXG</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>GASS</t>
+        </is>
+      </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>MEDP</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>GCL</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr"/>
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>GCT</t>
+        </is>
+      </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>MGRT</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>GECCI</t>
+        </is>
+      </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>MKTX</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>GENB</t>
+        </is>
+      </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>MRVL</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>GILD</t>
+        </is>
+      </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>MTC</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>GITS</t>
+        </is>
+      </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>MTCH</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>GLBS</t>
+        </is>
+      </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>NAKA</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>GLE</t>
+        </is>
+      </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>NBBK</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr"/>
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>GLOO</t>
+        </is>
+      </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>NBN</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr"/>
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>GMAB</t>
+        </is>
+      </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>NCI</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>GOLD</t>
+        </is>
+      </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>NEO</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>GPRO</t>
+        </is>
+      </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>NEOG</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr"/>
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>GSAT</t>
+        </is>
+      </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>NKSH</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr"/>
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>GTBP</t>
+        </is>
+      </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>NTAP</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>HBANP</t>
+        </is>
+      </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>NTRA</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr"/>
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>HCM</t>
+        </is>
+      </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>NTRB</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>HIVE</t>
+        </is>
+      </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>NTRP</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>HNNA</t>
+        </is>
+      </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>NTSK</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr"/>
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>HOWL</t>
+        </is>
+      </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>NUAI</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>HYPD</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>OABI</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>IEP</t>
+        </is>
+      </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>OBIO</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr"/>
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>OBT</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>IMPPP</t>
+        </is>
+      </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>OCCIN</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>IMTE</t>
+        </is>
+      </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>OFS</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr"/>
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>INFQ</t>
+        </is>
+      </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>OPK</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr"/>
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>INKT</t>
+        </is>
+      </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>OPRT</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>OPTU</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>INTG</t>
+        </is>
+      </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>OVLY</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>IOND</t>
+        </is>
+      </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>PANW</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr"/>
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>IRD</t>
+        </is>
+      </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>PBFS</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr"/>
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>IREN</t>
+        </is>
+      </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>PBHC</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ISRG</t>
+        </is>
+      </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>PBM</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>JRSH</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>PBYI</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>KMDA</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>PFBC</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr"/>
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>LEDS</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>PFG</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>LIEN</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr"/>
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>LQDT</t>
+        </is>
+      </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>PLBC</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>MARA</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>PLMR</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>MBINM</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>PMVP</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>MDXG</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>PPHC</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>MEDP</t>
+        </is>
+      </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>PPIH</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>PPSI</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr"/>
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>MFI</t>
+        </is>
+      </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>PRAA</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>MKTX</t>
+        </is>
+      </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>MLAB</t>
+        </is>
+      </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>PSIX</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>MNOV</t>
+        </is>
+      </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>PUBM</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>MNTK</t>
+        </is>
+      </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>PXS</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>MRNA</t>
+        </is>
+      </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>QCOM</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>QLYS</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>MSBI</t>
+        </is>
+      </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>QMCO</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>QNBC</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>MTLS</t>
+        </is>
+      </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>QSEA</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>MXL</t>
+        </is>
+      </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>RBB</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>NAKA</t>
+        </is>
+      </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>RBKB</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>NEO</t>
+        </is>
+      </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>RILYN</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr"/>
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>NEOG</t>
+        </is>
+      </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>RLYB</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr"/>
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>NEWTP</t>
+        </is>
+      </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>RVSB</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr"/>
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>NFEGP</t>
+        </is>
+      </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>SAFX</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr"/>
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>NICE</t>
+        </is>
+      </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>SAIL</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr"/>
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>NKTX</t>
+        </is>
+      </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>SATA</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr"/>
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>NSLRL</t>
+        </is>
+      </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>SBC</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr"/>
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>NTAP</t>
+        </is>
+      </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>SBFG</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr"/>
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>NTNX</t>
+        </is>
+      </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>SBLK</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr"/>
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>NTRP</t>
+        </is>
+      </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>SCSC</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr"/>
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>NTSK</t>
+        </is>
+      </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>SCTX</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr"/>
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>NTWK</t>
+        </is>
+      </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>SFNC</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr"/>
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>NVAX</t>
+        </is>
+      </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>SHC</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr"/>
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>OABI</t>
+        </is>
+      </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>SHIP</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr"/>
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>OCCIN</t>
+        </is>
+      </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>SKHY</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr"/>
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>OESX</t>
+        </is>
+      </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>SLAB</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr"/>
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>OKTA</t>
+        </is>
+      </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>SLDE</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr"/>
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>OLLI</t>
+        </is>
+      </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>SLE</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr"/>
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>OPRT</t>
+        </is>
+      </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>SMMT</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr"/>
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>OPTU</t>
+        </is>
+      </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>SMTC</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr"/>
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>OXLCG</t>
+        </is>
+      </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>SND</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr"/>
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>OXLCM</t>
+        </is>
+      </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>STLN</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr"/>
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>STRF</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr"/>
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>PANL</t>
+        </is>
+      </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>SVAQ</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr"/>
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>PDSB</t>
+        </is>
+      </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>SVRN</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr"/>
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>PEBK</t>
+        </is>
+      </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>TASK</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr"/>
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>PFBC</t>
+        </is>
+      </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>TH</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr"/>
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>PGEN</t>
+        </is>
+      </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>TJGC</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr"/>
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>TNMG</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr"/>
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>PLMR</t>
+        </is>
+      </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>TOP</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr"/>
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>TRMK</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr"/>
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>PMEC</t>
+        </is>
+      </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>TTRX</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr"/>
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>PPIH</t>
+        </is>
+      </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>USDEW</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr"/>
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>PPSI</t>
+        </is>
+      </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>VALU</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr"/>
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>PRTS</t>
+        </is>
+      </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>VOGX</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr"/>
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>PUBM</t>
+        </is>
+      </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>XIIIU</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr"/>
+      <c r="A186" t="inlineStr"/>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>PURR</t>
+        </is>
+      </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>PXS</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>QLYS</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>QMCO</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>QXL</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr"/>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>RBKB</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>RCEL</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>RDIB</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>RECT</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>REFI</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>RFAI</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>RGEN</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>RILYN</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>RIOT</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr"/>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>RUM</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>RUSHB</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr"/>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>RWAYI</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr"/>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>RXRX</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr"/>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>SABR</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr"/>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>SAFT</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr"/>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>SAFX</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr"/>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>SAIH</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr"/>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr"/>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr"/>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr"/>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>SECZ</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr"/>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>SILC</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr"/>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>SKYA</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr"/>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>SLDE</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr"/>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr"/>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>SMCIP</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr"/>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>SMMT</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr"/>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>SMTC</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr"/>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>SMTI</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr"/>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>SONO</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr"/>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>SOPH</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr"/>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>SORA</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr"/>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr"/>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>STRC</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr"/>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>STRF</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr"/>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>SY</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr"/>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>TASK</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr"/>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>TAYD</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr"/>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>TCGX</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr"/>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>TDWD</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr"/>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>TEAM</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr"/>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr"/>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr"/>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>TENB</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr"/>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>TGTX</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr"/>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr"/>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>TITN</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr"/>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>TKNO</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr"/>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>TMS</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr"/>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>TNMG</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr"/>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>TOP</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr"/>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>TRMK</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr"/>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>UCAR</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr"/>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>USDEW</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr"/>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>WCCB</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr"/>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>XMTR</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr"/>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>XZO</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D170"/>
+  <dimension ref="A1:D162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AERT</t>
+          <t>CHAD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,19 +451,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ONCO</t>
+          <t>NEON</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ACGLO</t>
+          <t>AEHL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>COSM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -471,346 +471,334 @@
           <t>ABLV</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>RDNW</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>AER</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>FJDIU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACU</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>RFAMU</t>
-        </is>
-      </c>
+          <t>ACRV</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BLNK</t>
+          <t>AMKR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNKK</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADAMG</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BPRE</t>
+          <t>AUUD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRKRP</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>AERT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>COLA</t>
+          <t>CAMT</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHSCO</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>AGEN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CRUS</t>
+          <t>CBRS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GGR</t>
+          <t>QSI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AEMD</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DOMH</t>
+          <t>COLA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>SDEV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ALVO</t>
+          <t>AIIA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FAC</t>
+          <t>CRUS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LAFA</t>
+          <t>SXTP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ALZN</t>
+          <t>ALP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IQST</t>
+          <t>GCDT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MEDS</t>
+          <t>TACH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMBR</t>
+          <t>ARW</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MWC</t>
+          <t>GNLN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>XRPN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>ASBH</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OCC</t>
+          <t>GRDX</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NRSN</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>QMLS</t>
+          <t>KLAC</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NTWK</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>ASST</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SSYS</t>
+          <t>MSS</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PACB</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>ASYS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SWRD</t>
+          <t>MWC</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PCAP</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
+          <t>ATEC</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>OCC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>ATKR</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>SBMT</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ATRC</t>
-        </is>
-      </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PDC</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SDEV</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>ATLCL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PLAB</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>SINT</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>ATLCZ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>POM</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SONM</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BATRA</t>
+          <t>AUC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>RDNW</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>WSHP</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BCSS</t>
+          <t>AVAT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RXT</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BDSX</t>
+          <t>AVX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SHLS</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BFRG</t>
+          <t>AXTI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SPHL</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BHFAL</t>
+          <t>BCHT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -820,7 +808,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>BCSS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -830,7 +818,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BLFS</t>
+          <t>BMNP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -840,7 +828,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BMNP</t>
+          <t>BNR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -850,7 +838,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BNGO</t>
+          <t>BPRE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -860,7 +848,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>BTCS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -870,7 +858,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>BURU</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -880,7 +868,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -890,7 +878,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CBAT</t>
+          <t>BWMN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -900,7 +888,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CCNEP</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -910,7 +898,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -920,7 +908,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>CDRO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -930,7 +918,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CEVA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -940,7 +928,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CHEC</t>
+          <t>CHOW</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -950,7 +938,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CHOW</t>
+          <t>CHSCL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -960,7 +948,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CLMB</t>
+          <t>CHSCO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -970,7 +958,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CNET</t>
+          <t>CLGN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -980,7 +968,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CNTN</t>
+          <t>CNET</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1000,7 +988,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CODA</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1010,7 +998,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CPOP</t>
+          <t>CPIX</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1020,7 +1008,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CRCT</t>
+          <t>CPOP</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1030,7 +1018,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>CURX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1040,7 +1028,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>DGII</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1050,7 +1038,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CSTL</t>
+          <t>DIOD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1060,7 +1048,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>DJCO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1070,7 +1058,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CURI</t>
+          <t>DJT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1080,7 +1068,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>DXPE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1090,7 +1078,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CWD</t>
+          <t>EDHL</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1100,7 +1088,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>EEIQ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1110,7 +1098,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DJCO</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1120,7 +1108,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DMAA</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1130,7 +1118,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DMAC</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1140,7 +1128,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>ENTG</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1150,7 +1138,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DXPE</t>
+          <t>EPRX</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1160,7 +1148,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>FBLA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1170,7 +1158,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ECX</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1180,7 +1168,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EDTK</t>
+          <t>FLXS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1190,7 +1178,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1200,7 +1188,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>FSBW</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1210,7 +1198,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1220,7 +1208,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>GLND</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1230,7 +1218,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FRNM</t>
+          <t>GRI</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1240,7 +1228,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FSBW</t>
+          <t>GTBP</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1250,7 +1238,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>GYRE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1260,7 +1248,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>HBIO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1270,7 +1258,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GEGGL</t>
+          <t>HITI</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1280,7 +1268,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>HQI</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1290,7 +1278,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>HSDT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1300,7 +1288,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GIW</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1310,7 +1298,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GLSI</t>
+          <t>IBRX</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1320,7 +1308,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>IFBD</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1330,7 +1318,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>III</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1340,7 +1328,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GTBP</t>
+          <t>INAB</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1350,7 +1338,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GYRE</t>
+          <t>IOND</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1360,7 +1348,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>IOSP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1370,7 +1358,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>KAZR</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1380,7 +1368,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>KLIC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1390,7 +1378,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>KMDA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1400,7 +1388,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IMPPP</t>
+          <t>KMTS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1410,7 +1398,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>INAB</t>
+          <t>LAUR</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1420,7 +1408,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>INOD</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1430,7 +1418,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IOND</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1440,7 +1428,7 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>LTRX</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1450,7 +1438,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>MATH</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1460,7 +1448,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1470,7 +1458,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IVVD</t>
+          <t>MCHPP</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1480,7 +1468,7 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>MQ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1490,7 +1478,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>MRAM</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1500,7 +1488,7 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JTAI</t>
+          <t>MTC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1510,7 +1498,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>KAZR</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1520,7 +1508,7 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>MYGN</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -1530,7 +1518,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -1540,7 +1528,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>NNBR</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1550,7 +1538,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LTRX</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -1560,7 +1548,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -1570,7 +1558,7 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MBINM</t>
+          <t>NTRBW</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1580,7 +1568,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MDWD</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1590,7 +1578,7 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MIRA</t>
+          <t>NVEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1600,7 +1588,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MKTW</t>
+          <t>NWGL</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1610,7 +1598,7 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MLCI</t>
+          <t>NXXT</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -1620,7 +1608,7 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>OLLI</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -1630,7 +1618,7 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -1640,7 +1628,7 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NSTS</t>
+          <t>ORBS</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -1650,7 +1638,7 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>OXBR</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -1660,7 +1648,7 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>OXLCZ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -1670,7 +1658,7 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>PAAI</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -1680,7 +1668,7 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NVEC</t>
+          <t>PCAP</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -1690,7 +1678,7 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NXXT</t>
+          <t>PGEN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -1700,7 +1688,7 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>OCCIN</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -1710,7 +1698,7 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>PLXS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -1720,7 +1708,7 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ONC</t>
+          <t>POWW</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -1730,7 +1718,7 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ORIC</t>
+          <t>PSHG</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -1740,7 +1728,7 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>OXLCI</t>
+          <t>PSIG</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -1750,7 +1738,7 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>OXLCM</t>
+          <t>PXLW</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -1760,7 +1748,7 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>QMCO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -1770,7 +1758,7 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PAAI</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -1780,7 +1768,7 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PACH</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -1790,7 +1778,7 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>QTRX</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -1800,7 +1788,7 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PDFS</t>
+          <t>RCMT</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -1810,7 +1798,7 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PFLA</t>
+          <t>RGS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -1820,7 +1808,7 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PGEN</t>
+          <t>RMTI</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -1830,7 +1818,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PHOS</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -1840,7 +1828,7 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>RVSB</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -1850,7 +1838,7 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PLPC</t>
+          <t>RWAYL</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -1860,7 +1848,7 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -1870,7 +1858,7 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -1880,7 +1868,7 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -1890,7 +1878,7 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPSI</t>
+          <t>SBMT</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -1900,7 +1888,7 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>SGHT</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -1910,7 +1898,7 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PSIG</t>
+          <t>SHMD</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -1920,7 +1908,7 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>QNTM</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -1930,7 +1918,7 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>QTRX</t>
+          <t>SIMO</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -1940,7 +1928,7 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>QUBT</t>
+          <t>SKYA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -1950,7 +1938,7 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>RCMT</t>
+          <t>SLAB</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -1960,7 +1948,7 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>RDIB</t>
+          <t>SLMT</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -1970,7 +1958,7 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -1980,7 +1968,7 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>RGEN</t>
+          <t>SONO</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -1990,7 +1978,7 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>RGS</t>
+          <t>SRZN</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -2000,7 +1988,7 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>RIGL</t>
+          <t>SSYS</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -2010,7 +1998,7 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>RILYN</t>
+          <t>STRC</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -2020,7 +2008,7 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>RNW</t>
+          <t>STRF</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -2030,7 +2018,7 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SAIH</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2040,7 +2028,7 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>SUIG</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2050,7 +2038,7 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SDGR</t>
+          <t>SVCO</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2060,7 +2048,7 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SGHT</t>
+          <t>SVIA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2070,7 +2058,7 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SIMO</t>
+          <t>SVIAW</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2080,7 +2068,7 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SLAB</t>
+          <t>SVRN</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2090,7 +2078,7 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SMTI</t>
+          <t>SWRD</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2100,7 +2088,7 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SOPH</t>
+          <t>TAOX</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2110,7 +2098,7 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SQFTP</t>
+          <t>TCPC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2120,7 +2108,7 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>STLN</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2130,7 +2118,7 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>STRC</t>
+          <t>TITN</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2140,7 +2128,7 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>STRF</t>
+          <t>TKNO</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2150,7 +2138,7 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>TONX</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -2160,7 +2148,7 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SVRN</t>
+          <t>TWAV</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -2170,7 +2158,7 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>VICR</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -2180,7 +2168,7 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>TAYD</t>
+          <t>WLTH</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2190,91 +2178,11 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TELO</t>
+          <t>XCBE</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr"/>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>TEM</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr"/>
-      <c r="D163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr"/>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>TLACU</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr"/>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>TMS</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr"/>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>TONT</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr"/>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>TONX</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr"/>
-      <c r="D167" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr"/>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>TRLV</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr"/>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>VAI</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr"/>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>XXI</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr"/>
-      <c r="D170" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D238"/>
+  <dimension ref="A1:D231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,11 +449,7 @@
           <t>ABLV</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>BZFD</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>AAON</t>
@@ -463,7 +459,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AIIA</t>
+          <t>BOT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -471,456 +467,404 @@
           <t>ABSI</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>FUFU</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AMBA</t>
+          <t>ATOM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHSCO</t>
+          <t>CURX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACU</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>GNLN</t>
-        </is>
-      </c>
+          <t>ABXL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ATII</t>
+          <t>AZUL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CRVO</t>
+          <t>DLXY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADMA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>HTLM</t>
-        </is>
-      </c>
+          <t>ACLS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AVO</t>
+          <t>BTTC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ELLA</t>
+          <t>DUKRW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADPT</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>RGC</t>
-        </is>
-      </c>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CRUS</t>
+          <t>CRD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>FRSH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AEHL</t>
+          <t>ADMA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>CRNT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AEIS</t>
+          <t>ADPT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HWKN</t>
+          <t>CRWV</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GSRF</t>
+          <t>KBSX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>AEHL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ICHR</t>
+          <t>DMRC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INAB</t>
+          <t>MACI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AIIR</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>INDV</t>
+          <t>DUOT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KFII</t>
+          <t>MDAI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>AEIS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IQMX</t>
+          <t>EMPD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ALMR</t>
+          <t>AFRI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IRMD</t>
+          <t>EVCM</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NSLRL</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ALNT</t>
+          <t>AHG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>HBANL</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NTWK</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>AIB</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>HYPR</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>OPTX</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>AIIR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MDLN</t>
+          <t>INEO</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>OXLCM</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MKSI</t>
+          <t>IQMX</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>PDSB</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>ALLT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NEON</t>
+          <t>ITRN</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>PMTR</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AOUT</t>
+          <t>ALNT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PWRL</t>
+          <t>MAZE</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PTC</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ARAY</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SLMT</t>
+          <t>MIND</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>PXS</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ARW</t>
+          <t>AMBR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>NMAD</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>RELL</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ASPS</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VERU</t>
+          <t>NTRSO</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>RXRX</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ASST</t>
+          <t>AMPH</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ZSQR</t>
+          <t>POWL</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>SDEV</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
+          <t>AMPL</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>QUIK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AMRX</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RYAAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ANDG</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SNWV</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ASST</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>STRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>ATKR</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>SOTK</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ATLCL</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>SXTP</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>AUUD</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>THEO</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>AVPT</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>WCCB</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>AZTA</t>
-        </is>
-      </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TLN</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BCML</t>
+          <t>AVAT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ZSQR</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BCTX</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -930,7 +874,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BKHA</t>
+          <t>AVX</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -940,7 +884,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BLRK</t>
+          <t>AXTI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -950,7 +894,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BNC</t>
+          <t>BATRA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -960,7 +904,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BPRE</t>
+          <t>BBCP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -970,7 +914,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>BCAL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -980,7 +924,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BTBD</t>
+          <t>BELFB</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -990,7 +934,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BTTC</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1000,7 +944,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>BNR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1010,7 +954,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -1020,7 +964,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CAMT</t>
+          <t>BPRE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -1030,7 +974,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>BSVN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -1040,7 +984,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>BTBD</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1050,7 +994,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CELU</t>
+          <t>BZUN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -1060,7 +1004,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CBAT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1070,7 +1014,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1080,7 +1024,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1090,7 +1034,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>CELU</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1100,7 +1044,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CHSCL</t>
+          <t>CEVA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1110,7 +1054,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CLMB</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1120,7 +1064,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>COHU</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1130,7 +1074,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CORT</t>
+          <t>CGNX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1140,7 +1084,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>COSM</t>
+          <t>CHAD</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1150,7 +1094,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>CHSCL</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1160,7 +1104,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>CLMB</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1170,7 +1114,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CRSR</t>
+          <t>CNXN</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1180,7 +1124,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1190,7 +1134,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1200,7 +1144,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CSTL</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1210,7 +1154,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CTKB</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1220,7 +1164,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1230,7 +1174,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CWBC</t>
+          <t>CTKB</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1240,7 +1184,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CYRX</t>
+          <t>CVCO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1250,7 +1194,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1260,7 +1204,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DMAC</t>
+          <t>CWBC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1270,7 +1214,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1280,7 +1224,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1290,7 +1234,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>DIOD</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1300,7 +1244,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>DSGR</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1310,7 +1254,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DTST</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1320,7 +1264,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EEIQ</t>
+          <t>DXPE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1330,7 +1274,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1340,7 +1284,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FBLA</t>
+          <t>EGHT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1350,7 +1294,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>ELMT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1360,7 +1304,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1370,7 +1314,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1380,7 +1324,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FLGT</t>
+          <t>ENTG</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1390,7 +1334,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FNRN</t>
+          <t>EUDA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1400,7 +1344,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FORM</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1410,7 +1354,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FRHC</t>
+          <t>FBLA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1420,7 +1364,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>FEIM</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1430,7 +1374,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1440,7 +1384,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>FIRY</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1450,7 +1394,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1460,7 +1404,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1470,7 +1414,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GSAT</t>
+          <t>FOSL</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1480,7 +1424,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>FPS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1490,7 +1434,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1500,7 +1444,7 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HIMX</t>
+          <t>FROG</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1510,7 +1454,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>FSBW</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1520,7 +1464,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1530,7 +1474,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1540,7 +1484,7 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>FWDI</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1550,7 +1494,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IDAI</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1560,7 +1504,7 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1570,7 +1514,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1580,7 +1524,7 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IMPPP</t>
+          <t>HBIO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -1590,7 +1534,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>INCR</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -1600,7 +1544,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>INKT</t>
+          <t>HQI</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1610,7 +1554,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>HQWWW</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -1620,7 +1564,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>HWKN</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -1630,7 +1574,7 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IPGP</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1640,7 +1584,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>INKT</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1650,7 +1594,7 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>IOSP</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1660,7 +1604,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>IRDM</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1690,7 +1634,7 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>KAZR</t>
+          <t>KFII</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -1700,7 +1644,7 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>KCHV</t>
+          <t>KMRK</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -1710,7 +1654,7 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>KFFB</t>
+          <t>KMTS</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -1720,7 +1664,7 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>KMTS</t>
+          <t>KOD</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -1730,7 +1674,7 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>KOPN</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -1740,7 +1684,7 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>KOSS</t>
+          <t>LCUT</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -1750,7 +1694,7 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -1760,7 +1704,7 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>LEDS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -1770,7 +1714,7 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LAFA</t>
+          <t>LGND</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -1780,7 +1724,7 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -1790,7 +1734,7 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -1800,7 +1744,7 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -1810,7 +1754,7 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>LITS</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -1820,7 +1764,7 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -1830,7 +1774,7 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -1840,7 +1784,7 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -1870,7 +1814,7 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>LTRX</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -1880,7 +1824,7 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MATH</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -1890,7 +1834,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MBINM</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -1900,7 +1844,7 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>MCHPP</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -1910,7 +1854,7 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -1920,7 +1864,7 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MKTW</t>
+          <t>MGRC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -1930,7 +1874,7 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MLAB</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -1940,7 +1884,7 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MNTK</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -1950,7 +1894,7 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>MSGY</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -1960,7 +1904,7 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -1970,7 +1914,7 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MRVI</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -1980,7 +1924,7 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MTSI</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -1990,7 +1934,7 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MSGM</t>
+          <t>MXL</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -2000,7 +1944,7 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>NATH</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -2010,7 +1954,7 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MTSI</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -2020,7 +1964,7 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -2030,7 +1974,7 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MXL</t>
+          <t>NDSN</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -2040,7 +1984,7 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>NAKA</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -2050,7 +1994,7 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>NKSH</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -2060,7 +2004,7 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>NOVT</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -2070,7 +2014,7 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -2080,7 +2024,7 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>NDRA</t>
+          <t>NTCT</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -2090,7 +2034,7 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2100,7 +2044,7 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>NHPBP</t>
+          <t>NTRP</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2110,7 +2054,7 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NTCT</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2120,7 +2064,7 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2130,7 +2074,7 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2140,7 +2084,7 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NTRP</t>
+          <t>NVEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2150,7 +2094,7 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2160,7 +2104,7 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>OCC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2170,7 +2114,7 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NVAX</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2180,7 +2124,7 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2190,7 +2134,7 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>NVEC</t>
+          <t>ONC</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2200,7 +2144,7 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>OPRT</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2210,7 +2154,7 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -2220,7 +2164,7 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>OPTX</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -2230,7 +2174,7 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>OSPN</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -2240,7 +2184,7 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>OTAI</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2250,7 +2194,7 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>OUST</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -2260,7 +2204,7 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -2270,7 +2214,7 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -2280,7 +2224,7 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>OSUR</t>
+          <t>PDFS</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -2290,7 +2234,7 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>OTAI</t>
+          <t>PKOH</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -2300,7 +2244,7 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>OXLCZ</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -2310,7 +2254,7 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>PLXS</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -2320,7 +2264,7 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PACB</t>
+          <t>PMVP</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -2330,7 +2274,7 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -2340,7 +2284,7 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PAYO</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -2350,7 +2294,7 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -2360,7 +2304,7 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PDFS</t>
+          <t>PSIG</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -2370,7 +2314,7 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PENG</t>
+          <t>PSIX</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -2380,7 +2324,7 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PKOH</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -2390,7 +2334,7 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PLUN</t>
+          <t>PUBM</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -2400,7 +2344,7 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PLXS</t>
+          <t>PWP</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -2410,7 +2354,7 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>PXS</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -2420,7 +2364,7 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PPLI</t>
+          <t>QMCO</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -2430,7 +2374,7 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>QSI</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -2440,7 +2384,7 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>RBKB</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -2450,7 +2394,7 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>RCBC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -2460,7 +2404,7 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -2470,7 +2414,7 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>QSEA</t>
+          <t>RDWR</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -2480,7 +2424,7 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>QTRX</t>
+          <t>RFAI</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -2490,7 +2434,7 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -2500,7 +2444,7 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>RCMT</t>
+          <t>RMBS</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -2510,7 +2454,7 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>RVMD</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -2520,7 +2464,7 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>REFR</t>
+          <t>RWAYL</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -2530,7 +2474,7 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>RFAI</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -2540,7 +2484,7 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>RILYG</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -2550,7 +2494,7 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>SCSC</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -2560,7 +2504,7 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>SDGR</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -2570,7 +2514,7 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SAMG</t>
+          <t>SGC</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -2580,7 +2524,7 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SANM</t>
+          <t>SHLS</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -2590,7 +2534,7 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SAX</t>
+          <t>SHMD</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -2600,7 +2544,7 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -2610,7 +2554,7 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SCSC</t>
+          <t>SILC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -2620,7 +2564,7 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SCYX</t>
+          <t>SIMO</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -2630,7 +2574,7 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SDGR</t>
+          <t>SITM</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -2640,7 +2584,7 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SEER</t>
+          <t>SKYA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -2650,7 +2594,7 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>SGC</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -2660,7 +2604,7 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -2670,7 +2614,7 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SIGA</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -2680,7 +2624,7 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SILC</t>
+          <t>SOTK</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -2690,7 +2634,7 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SIMO</t>
+          <t>SPCX</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -2700,7 +2644,7 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SINT</t>
+          <t>SPOK</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -2710,7 +2654,7 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SITM</t>
+          <t>SSTI</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -2720,7 +2664,7 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SKHY</t>
+          <t>STRC</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -2730,7 +2674,7 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>SLAB</t>
+          <t>STRD</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -2740,7 +2684,7 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SLGL</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -2750,7 +2694,7 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>SUIG</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -2760,7 +2704,7 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>SUJA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -2770,7 +2714,7 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>SRZN</t>
+          <t>SUNB</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -2780,7 +2724,7 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>SSYS</t>
+          <t>SVCO</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -2790,7 +2734,7 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>STRC</t>
+          <t>TAOX</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -2800,7 +2744,7 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>STRD</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -2810,7 +2754,7 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>STRF</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -2820,7 +2764,7 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>TITN</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -2830,7 +2774,7 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>SUIG</t>
+          <t>TLSA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -2840,7 +2784,7 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>SUNB</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -2850,7 +2794,7 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>SVIA</t>
+          <t>TRNI</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -2860,7 +2804,7 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>SVRN</t>
+          <t>TRNS</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -2870,7 +2814,7 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>SWBI</t>
+          <t>USDEW</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -2880,7 +2824,7 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>VAI</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -2890,7 +2834,7 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>TAOX</t>
+          <t>WCCB</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -2900,7 +2844,7 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>WLTH</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -2910,7 +2854,7 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>XFLH</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -2920,7 +2864,7 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>TONT</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -2930,7 +2874,7 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>XRPN</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -2940,81 +2884,11 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>TRNS</t>
+          <t>XXI</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr"/>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr"/>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>TWAV</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr"/>
-      <c r="D232" t="inlineStr"/>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr"/>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>VALU</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr"/>
-      <c r="D233" t="inlineStr"/>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr"/>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>VIR</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr"/>
-      <c r="D234" t="inlineStr"/>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr"/>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>WLTH</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr"/>
-      <c r="D235" t="inlineStr"/>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr"/>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>XFLH</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr"/>
-      <c r="D236" t="inlineStr"/>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr"/>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>XMTR</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr"/>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr"/>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>XRPNU</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D174"/>
+  <dimension ref="A1:D209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,17 +441,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AFRI</t>
+          <t>ALISU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ACB</t>
+          <t>AACI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AERO</t>
+          <t>LVLU</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -463,29 +463,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>AMBR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>ACIC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CGNX</t>
+          <t>TBCH</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AZUL</t>
+          <t>AERO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>AUC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -493,109 +493,89 @@
           <t>AEHL</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CRNT</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DUO</t>
+          <t>BVFL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AUC</t>
+          <t>BKHAU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AHG</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>GFS</t>
-        </is>
-      </c>
+          <t>AFRI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FBYD</t>
+          <t>ECHO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BKHAU</t>
+          <t>BMR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AIFA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>HCAT</t>
-        </is>
-      </c>
+          <t>AGBK</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>EMPD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BMR</t>
+          <t>CHNR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AISP</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>HRTX</t>
-        </is>
-      </c>
+          <t>AIRT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>INSG</t>
+          <t>HWKN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BPRE</t>
+          <t>DLXY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ALAB</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LVLU</t>
-        </is>
-      </c>
+          <t>AISP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IRMD</t>
+          <t>INSG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRBI</t>
+          <t>ELOG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -603,55 +583,43 @@
           <t>ALRM</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>NTES</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ITRN</t>
+          <t>IRMD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRLT</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMBR</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Q</t>
-        </is>
-      </c>
+          <t>AMGN</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KMRK</t>
+          <t>ITRN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>FVNNU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMGN</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>QETA</t>
-        </is>
-      </c>
+          <t>AMPH</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>LFS</t>
@@ -661,19 +629,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMPH</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>SJ</t>
-        </is>
-      </c>
+          <t>AMRX</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>LMB</t>
@@ -683,70 +647,66 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CAPNU</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>SYPR</t>
-        </is>
-      </c>
+          <t>ANDG</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NTCT</t>
+          <t>MYRG</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>ICG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NXT</t>
+          <t>NTES</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CCCT</t>
+          <t>IDAI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>APEI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OCG</t>
+          <t>OFLX</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>LSAK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>APOG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -759,876 +719,640 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>ASO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>OSW</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CLFD</t>
+          <t>OTAI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>ATEC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OPTX</t>
+          <t>PWP</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CLOV</t>
+          <t>PEBK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>AVBC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PWP</t>
+          <t>PWRL</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CMRC</t>
+          <t>QQQX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>PWRL</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>RFAI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ATEC</t>
+          <t>BIRD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>RDGT</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>DDOG</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ATLCZ</t>
+          <t>BMNP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>TBCH</t>
-        </is>
-      </c>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>EXEL</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ATRA</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>FEAM</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>BPRE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>FLD</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>GCT</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>BSET</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>GECCI</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AXIN</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>GIBO</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>BWMN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>GOOGM</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BGM</t>
+          <t>BYRN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>GSAT</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BLZR</t>
+          <t>CAKE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>HLP</t>
-        </is>
-      </c>
+      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BVFL</t>
+          <t>CAPNU</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>HPK</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>HSTM</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CAMT</t>
+          <t>CBRL</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>IBRX</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>IMKTA</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CELU</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>INTR</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>IPXG</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CLMB</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>JAKK</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CNXN</t>
+          <t>CHAD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>KRT</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CORT</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>MEOH</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>CNXN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>MRNA</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>COPR</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>MTLS</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>NAUT</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CURX</t>
+          <t>CPHC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>NDSN</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>NMAD</t>
-        </is>
-      </c>
+      <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CWCO</t>
+          <t>CRCT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>NTRP</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>NTSK</t>
-        </is>
-      </c>
+      <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DGII</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>NVAX</t>
-        </is>
-      </c>
+      <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>NVEC</t>
-        </is>
-      </c>
+      <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DMAC</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>NXPL</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DNMX</t>
+          <t>CWCO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>ODD</t>
-        </is>
-      </c>
+      <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>ONBPP</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DTST</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>OPRT</t>
-        </is>
-      </c>
+      <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DUOL</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>OSPN</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EFOI</t>
+          <t>DLO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>OTAI</t>
-        </is>
-      </c>
+      <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>DMLP</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
+      <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>PDSB</t>
-        </is>
-      </c>
+      <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>DTST</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>PENG</t>
-        </is>
-      </c>
+      <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>DUOL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>PHUN</t>
-        </is>
-      </c>
+      <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EUDA</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>PICS</t>
-        </is>
-      </c>
+      <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>ECPG</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>PRME</t>
-        </is>
-      </c>
+      <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FCAP</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>PSIG</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>QQQX</t>
-        </is>
-      </c>
+      <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FFR</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>QSI</t>
-        </is>
-      </c>
+      <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>ENSC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>RDWR</t>
-        </is>
-      </c>
+      <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>EVCM</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>RELL</t>
-        </is>
-      </c>
+      <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FOSL</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>RUSHB</t>
-        </is>
-      </c>
+      <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FROG</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>RXRX</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>SRZN</t>
-        </is>
-      </c>
+      <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>STNE</t>
-        </is>
-      </c>
+      <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>FIRY</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>SYNA</t>
-        </is>
-      </c>
+      <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>FLXS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>TENB</t>
-        </is>
-      </c>
+      <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>FNKO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>TLSA</t>
-        </is>
-      </c>
+      <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>FOSL</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>VAI</t>
-        </is>
-      </c>
+      <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>FRAF</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>VCTR</t>
-        </is>
-      </c>
+      <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>ZSQR</t>
-        </is>
-      </c>
+      <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GOOGN</t>
+          <t>FROG</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1638,7 +1362,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>FSBW</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1648,7 +1372,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1658,7 +1382,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1668,7 +1392,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>GECCH</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1678,7 +1402,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HQWWW</t>
+          <t>GLBE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1688,7 +1412,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1698,7 +1422,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1708,7 +1432,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1718,7 +1442,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>GOOGM</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1728,7 +1452,7 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>GOOGN</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1738,7 +1462,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1748,7 +1472,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1758,7 +1482,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1768,7 +1492,7 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>HBIO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1778,7 +1502,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LCUT</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1788,7 +1512,7 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LFCR</t>
+          <t>HPK</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1798,7 +1522,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1808,7 +1532,7 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MACI</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -1818,7 +1542,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>HYFT</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -1828,7 +1552,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MASS</t>
+          <t>HYNE</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1838,7 +1562,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -1848,7 +1572,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MBVI</t>
+          <t>III</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -1858,7 +1582,7 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MDLN</t>
+          <t>INAC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1868,7 +1592,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>INGN</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1878,7 +1602,7 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>INTR</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1888,7 +1612,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>IRIX</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1898,7 +1622,7 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MSGY</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -1908,7 +1632,7 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>JANX</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -1918,7 +1642,7 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>JFU</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -1928,7 +1652,7 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NICE</t>
+          <t>JOYY</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -1938,7 +1662,7 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>KE</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -1948,7 +1672,7 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -1958,7 +1682,7 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NTGR</t>
+          <t>KMRK</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -1968,7 +1692,7 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>KRAQ</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -1978,7 +1702,7 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>KRNT</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -1988,7 +1712,7 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>KRSA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -1998,7 +1722,7 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2008,7 +1732,7 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>LAUR</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2018,7 +1742,7 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>OLB</t>
+          <t>LCUT</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2028,7 +1752,7 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2038,7 +1762,7 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2048,7 +1772,7 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2058,7 +1782,7 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2068,7 +1792,7 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PAHC</t>
+          <t>MAT</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2078,7 +1802,7 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2088,7 +1812,7 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>MQ</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2098,7 +1822,7 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PBYI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -2108,7 +1832,7 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PCVX</t>
+          <t>MSGM</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -2118,7 +1842,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PDFS</t>
+          <t>MWYN</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -2128,7 +1852,7 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PKOH</t>
+          <t>NATH</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -2138,7 +1862,7 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>NDSN</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -2148,7 +1872,7 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>NECB</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -2158,7 +1882,7 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PRHI</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -2168,7 +1892,7 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PRTH</t>
+          <t>NKSH</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -2178,7 +1902,7 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>NMAD</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -2188,7 +1912,7 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PXS</t>
+          <t>NNBR</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -2198,7 +1922,7 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>NSIT</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -2208,7 +1932,7 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>QTEX</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -2218,7 +1942,7 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>RCBC</t>
+          <t>NTGR</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -2228,7 +1952,7 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>RFAI</t>
+          <t>NTRP</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -2238,7 +1962,7 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>RIBBU</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -2248,7 +1972,7 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>RLYB</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -2258,7 +1982,7 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>NXPL</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -2268,7 +1992,7 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>RRGB</t>
+          <t>OCTV</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -2278,7 +2002,7 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>ODD</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -2288,7 +2012,7 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>RWAYL</t>
+          <t>OLLI</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -2298,7 +2022,7 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>RYZ</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -2308,7 +2032,7 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SAV</t>
+          <t>ONBPP</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -2318,7 +2042,7 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2328,7 +2052,7 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SCSC</t>
+          <t>OPRT</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2338,7 +2062,7 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SGC</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2348,7 +2072,7 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SHLS</t>
+          <t>PAX</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2358,7 +2082,7 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>PBYI</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2368,7 +2092,7 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2378,7 +2102,7 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SLAB</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2388,7 +2112,7 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>PDSB</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2398,7 +2122,7 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SOTK</t>
+          <t>PENG</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2408,7 +2132,7 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SSTI</t>
+          <t>PICS</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2418,7 +2142,7 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>STRC</t>
+          <t>PLUS</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2428,7 +2152,7 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>PNRG</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2438,7 +2162,7 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SUJA</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -2448,7 +2172,7 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SUNB</t>
+          <t>POCI</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -2458,7 +2182,7 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -2468,7 +2192,7 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SWRD</t>
+          <t>PRDO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2478,7 +2202,7 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>PRHI</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -2488,7 +2212,7 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>TJGC</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -2498,7 +2222,7 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>PSIX</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -2508,7 +2232,7 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>TPCS</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -2518,7 +2242,7 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>PUBM</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -2528,7 +2252,7 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>TRNI</t>
+          <t>QLYS</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -2538,7 +2262,7 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>RCBC</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -2548,7 +2272,7 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>UTHR</t>
+          <t>RCKY</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -2558,7 +2282,7 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>VIR</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -2568,7 +2292,7 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>VYLR</t>
+          <t>RDWR</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -2578,7 +2302,7 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>WCCB</t>
+          <t>RGS</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -2588,7 +2312,7 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>RMCF</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -2598,11 +2322,361 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>YDES</t>
+          <t>RPD</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>RVSB</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>RWAYM</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>RYZ</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SAFT</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SAMG</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SCHL</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SGC</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SIBN</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>SKK</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>SKWD</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>SLDE</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SMXT</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>SNPS</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>SOTK</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>SPSC</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr"/>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>STDN</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>STRA</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>STRC</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>SUNB</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>SVRN</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>SWKHL</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>TACH</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>TLN</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr"/>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>TLSA</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>TPCS</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr"/>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr"/>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr"/>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>UTHR</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr"/>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>VAI</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr"/>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>VCTR</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr"/>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>VYLR</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr"/>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>WCCB</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D209"/>
+  <dimension ref="A1:D182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,29 +441,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ALISU</t>
+          <t>AGBK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AACI</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LVLU</t>
+          <t>GFUZ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ACHC</t>
+          <t>AEP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMBR</t>
+          <t>ALISU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -473,326 +473,274 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>JYD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AERO</t>
+          <t>BCML</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AUC</t>
+          <t>CHNR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AEHL</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PFAI</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BVFL</t>
+          <t>DLHC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BKHAU</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AFRI</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SIMA</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ECHO</t>
+          <t>EMPD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BMR</t>
+          <t>ELOG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AGBK</t>
+          <t>AIRT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EMPD</t>
+          <t>LVLU</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHNR</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AIRT</t>
+          <t>AISP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HWKN</t>
+          <t>NTRSO</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DLXY</t>
+          <t>ENSC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AISP</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>INSG</t>
+          <t>NXT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ELOG</t>
+          <t>FLYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>IRMD</t>
+          <t>OSG</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>PEBK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>AMRX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ITRN</t>
+          <t>RMCF</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FVNNU</t>
+          <t>SJ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LFS</t>
+          <t>RPGL</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>GCL</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>AOUT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LMB</t>
+          <t>RSVR</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>HLP</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MYRG</t>
+          <t>SCHL</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ICG</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>APEI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NTES</t>
+          <t>SNWV</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>IDAI</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>ARTW</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>OFLX</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>LSAK</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>ASO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>OMCL</t>
-        </is>
-      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>NCPL</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>ATKR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>OSW</t>
-        </is>
-      </c>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>OTAI</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ATEC</t>
+          <t>AUDC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>PWP</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PEBK</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AVBC</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>PWRL</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>QQQX</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>BKHAU</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>RFAI</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BIRD</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -812,7 +760,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BOW</t>
+          <t>BOLT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -822,7 +770,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BPRE</t>
+          <t>BORR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -832,7 +780,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -852,7 +800,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>BSVN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -862,7 +810,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -872,7 +820,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>BVFL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -882,7 +830,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -892,7 +840,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CAPNU</t>
+          <t>BZUN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -902,7 +850,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>CAKE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -912,7 +860,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -922,7 +870,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>CBRL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -932,7 +880,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -942,7 +890,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -952,7 +900,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -962,7 +910,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -972,7 +920,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -982,7 +930,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CNXN</t>
+          <t>CLMB</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -992,7 +940,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>COPR</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1002,7 +950,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>CLOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -1012,7 +960,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CPHC</t>
+          <t>CMRC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1022,7 +970,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>CNXN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1032,7 +980,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CRCT</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1042,7 +990,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1052,7 +1000,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>CORT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1062,7 +1010,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1072,7 +1020,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>CRCT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1082,7 +1030,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CWCO</t>
+          <t>CRNC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1092,7 +1040,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1102,7 +1050,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1112,7 +1060,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CVSA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1122,7 +1070,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DLO</t>
+          <t>DAVE</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1132,7 +1080,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DMLP</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1142,7 +1090,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1152,7 +1100,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DTST</t>
+          <t>DLO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1162,7 +1110,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DUOL</t>
+          <t>DMLP</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1172,7 +1120,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1182,7 +1130,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ECPG</t>
+          <t>DSGR</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1192,7 +1140,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1202,7 +1150,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1212,7 +1160,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>ECPG</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1222,7 +1170,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>EEIQ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1232,7 +1180,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ENSC</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1242,7 +1190,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EVCM</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1252,7 +1200,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1262,7 +1210,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1272,7 +1220,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1282,7 +1230,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1292,7 +1240,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>FIVN</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1302,7 +1250,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FLXS</t>
+          <t>FSBW</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1312,7 +1260,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1322,7 +1270,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FOSL</t>
+          <t>GIBO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1332,7 +1280,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FRAF</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1342,7 +1290,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1352,7 +1300,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FROG</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1362,7 +1310,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FSBW</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1372,7 +1320,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>GOOGM</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1382,7 +1330,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>GOOGN</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1392,7 +1340,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GECCH</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1402,7 +1350,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GLBE</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1412,7 +1360,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1422,7 +1370,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1432,7 +1380,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>HMR</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1442,7 +1390,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GOOGM</t>
+          <t>HOWL</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1452,7 +1400,7 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GOOGN</t>
+          <t>HPK</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1462,7 +1410,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1472,7 +1420,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1482,7 +1430,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1492,7 +1440,7 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>IBRX</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1502,7 +1450,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>ICG</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1512,7 +1460,7 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>III</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1522,7 +1470,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>IMPP</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1532,7 +1480,7 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>INGN</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -1542,7 +1490,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>HYFT</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -1552,7 +1500,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>HYNE</t>
+          <t>IRMD</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1562,7 +1510,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>JANX</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -1572,7 +1520,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>JOYY</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -1582,7 +1530,7 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>INAC</t>
+          <t>KBON</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1592,7 +1540,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>KFFB</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1602,7 +1550,7 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1612,7 +1560,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>IRIX</t>
+          <t>KNSA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1622,7 +1570,7 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>KROS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -1632,7 +1580,7 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JANX</t>
+          <t>KRSA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -1642,7 +1590,7 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JFU</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -1652,7 +1600,7 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>LAUR</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -1662,7 +1610,7 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -1672,7 +1620,7 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>LOCO</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -1682,7 +1630,7 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>KMRK</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -1692,7 +1640,7 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>KRAQ</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -1702,7 +1650,7 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>MANE</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -1712,7 +1660,7 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>KRSA</t>
+          <t>MCGA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -1722,7 +1670,7 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -1732,7 +1680,7 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>MESH</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -1742,7 +1690,7 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LCUT</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -1752,7 +1700,7 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -1762,7 +1710,7 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>MQ</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -1772,7 +1720,7 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>LOPE</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -1782,7 +1730,7 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>MWYN</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -1792,7 +1740,7 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>NATH</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -1802,7 +1750,7 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -1812,7 +1760,7 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>NECB</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -1822,7 +1770,7 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>NKSH</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -1832,7 +1780,7 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MSGM</t>
+          <t>NRDS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -1842,7 +1790,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>NSIT</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -1852,7 +1800,7 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -1862,7 +1810,7 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>NXTC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -1872,7 +1820,7 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>NECB</t>
+          <t>ODD</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -1882,7 +1830,7 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NICE</t>
+          <t>OLLI</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -1892,7 +1840,7 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>NKSH</t>
+          <t>OPLN</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -1902,7 +1850,7 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>NMAD</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -1912,7 +1860,7 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>NNBR</t>
+          <t>PANL</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -1922,7 +1870,7 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -1932,7 +1880,7 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -1942,7 +1890,7 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>NTGR</t>
+          <t>PDSB</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -1952,7 +1900,7 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>NTRP</t>
+          <t>PGNY</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -1962,7 +1910,7 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -1972,7 +1920,7 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>PLUS</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -1982,7 +1930,7 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>NXPL</t>
+          <t>PNRG</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -1992,7 +1940,7 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>PRAA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -2002,7 +1950,7 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>PRDO</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -2012,7 +1960,7 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>PSIX</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -2022,7 +1970,7 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -2032,7 +1980,7 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ONBPP</t>
+          <t>PUBM</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -2042,7 +1990,7 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>PXS</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2052,7 +2000,7 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2062,7 +2010,7 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>QDEL</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2072,7 +2020,7 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PAX</t>
+          <t>QLEP</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2082,7 +2030,7 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PBYI</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2092,7 +2040,7 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>QTEX</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2102,7 +2050,7 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>RFAI</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2112,7 +2060,7 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>RGC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2122,7 +2070,7 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PENG</t>
+          <t>RIGL</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2132,7 +2080,7 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PICS</t>
+          <t>RVSB</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2142,7 +2090,7 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2152,7 +2100,7 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PNRG</t>
+          <t>SAMG</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2162,7 +2110,7 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>SCSC</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -2172,7 +2120,7 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>POCI</t>
+          <t>SLDE</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -2182,7 +2130,7 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>SLSN</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -2192,7 +2140,7 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PRDO</t>
+          <t>SMTI</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2202,7 +2150,7 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PRHI</t>
+          <t>SMXT</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -2212,7 +2160,7 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -2222,7 +2170,7 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PSIX</t>
+          <t>SNFCA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -2232,7 +2180,7 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -2242,7 +2190,7 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PUBM</t>
+          <t>SPT</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -2252,7 +2200,7 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>SSTI</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -2262,7 +2210,7 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>RCBC</t>
+          <t>STGW</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -2272,7 +2220,7 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>RCKY</t>
+          <t>SUJA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -2282,7 +2230,7 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>SUNB</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -2292,7 +2240,7 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>SWKHL</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -2302,7 +2250,7 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>RGS</t>
+          <t>SWRD</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -2312,7 +2260,7 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>RMCF</t>
+          <t>TBCH</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -2322,7 +2270,7 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -2332,7 +2280,7 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -2342,7 +2290,7 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>RWAYM</t>
+          <t>TJGC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -2352,7 +2300,7 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>RYZ</t>
+          <t>TLN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -2362,7 +2310,7 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -2372,7 +2320,7 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SAMG</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -2382,7 +2330,7 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>WCCB</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -2392,7 +2340,7 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SGC</t>
+          <t>XFLH</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -2402,281 +2350,11 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>ZSQR</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr"/>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>SIBN</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr"/>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>SKK</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr"/>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>SKWD</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr"/>
-      <c r="D185" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr"/>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>SLDE</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr"/>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>SMXT</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr"/>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>SNPS</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr"/>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>SOTK</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr"/>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>SPCX</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr"/>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>SPSC</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr"/>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>STDN</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr"/>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>STRA</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr"/>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>STRC</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr"/>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>SUNB</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr"/>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>SVRN</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr"/>
-      <c r="D196" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr"/>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>SWKHL</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr"/>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>TACH</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr"/>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>TECH</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr"/>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>TLN</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr"/>
-      <c r="D200" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr"/>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>TLSA</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr"/>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>TPCS</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr"/>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>TRMB</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr"/>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>TRMD</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr"/>
-      <c r="D204" t="inlineStr"/>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr"/>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>UTHR</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr"/>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>VAI</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr"/>
-      <c r="D206" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr"/>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>VCTR</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr"/>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>VYLR</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr"/>
-      <c r="D208" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr"/>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>WCCB</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr"/>
-      <c r="D209" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D182"/>
+  <dimension ref="A1:D158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AGBK</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -449,238 +449,162 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>GFUZ</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
+          <t>AHCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ACHC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FNGR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ADMA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IIIV</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>AEP</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ALISU</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ACIC</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>JYD</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>BCML</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CHNR</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ADI</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>PFAI</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>DLHC</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DCBO</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>AFRM</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SIMA</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EMPD</t>
+          <t>IMKTA</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ELOG</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AIRT</t>
+          <t>AFRI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LVLU</t>
+          <t>ISPR</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ENGS</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AISP</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NTRSO</t>
+          <t>LIF</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ENSC</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>AFYA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NXT</t>
+          <t>TLS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>FLYE</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>AGBK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>OSG</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>PEBK</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>AGCC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>RMCF</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SJ</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>AISP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>RPGL</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AOUT</t>
+          <t>ALLT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>RSVR</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>SCHL</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>SNWV</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ARTW</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -690,7 +614,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>AOUT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -700,7 +624,7 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ATKR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -710,7 +634,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -720,7 +644,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>ARQT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -730,7 +654,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BKHAU</t>
+          <t>ASTH</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -740,7 +664,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>ATEC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -750,7 +674,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BMNP</t>
+          <t>AUGO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -760,7 +684,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BOLT</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -770,7 +694,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BORR</t>
+          <t>AVTR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -780,7 +704,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BOW</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -790,7 +714,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -800,7 +724,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>BMBL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -810,7 +734,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -820,7 +744,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BVFL</t>
+          <t>BPRE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -830,7 +754,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -840,7 +764,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -850,7 +774,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -860,7 +784,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>BZUN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -870,7 +794,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -880,7 +804,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -890,7 +814,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -910,7 +834,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -920,7 +844,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -930,7 +854,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CLMB</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -940,7 +864,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>CLOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -950,7 +874,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CLOV</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -960,7 +884,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CMRC</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -970,7 +894,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CNXN</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -980,7 +904,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -990,7 +914,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>CRNC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1000,7 +924,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CORT</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1010,7 +934,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1020,7 +944,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CRCT</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1030,7 +954,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CRNC</t>
+          <t>CVSA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1040,7 +964,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1050,7 +974,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1060,7 +984,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1070,7 +994,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DAVE</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1080,7 +1004,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>DLO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1090,7 +1014,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1100,7 +1024,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DLO</t>
+          <t>DSGR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1110,7 +1034,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DMLP</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1120,7 +1044,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1130,7 +1054,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>EDHL</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1140,7 +1064,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1150,7 +1074,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1160,7 +1084,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ECPG</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1170,7 +1094,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EEIQ</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1180,7 +1104,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1190,7 +1114,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1200,7 +1124,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1210,7 +1134,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>FIVN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1220,7 +1144,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>FLYW</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1230,7 +1154,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>FRPT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1240,7 +1164,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>FRSH</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1250,7 +1174,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FSBW</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1260,7 +1184,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1270,7 +1194,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1280,7 +1204,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>GIW</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1340,7 +1264,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>GRAL</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1350,7 +1274,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1360,7 +1284,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1370,7 +1294,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>HPK</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1380,7 +1304,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HMR</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1390,7 +1314,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HOWL</t>
+          <t>IBRX</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1400,7 +1324,7 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1410,7 +1334,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>INGN</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1420,7 +1344,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>INTR</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1430,7 +1354,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1440,7 +1364,7 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>IRMD</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1450,7 +1374,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>JFU</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1460,7 +1384,7 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>JOYY</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1470,7 +1394,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IMPP</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1480,7 +1404,7 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -1490,7 +1414,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>KNSA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -1500,7 +1424,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IRMD</t>
+          <t>KOD</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1510,7 +1434,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JANX</t>
+          <t>KRNT</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -1520,7 +1444,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -1530,7 +1454,7 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>KBON</t>
+          <t>LAUR</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1540,7 +1464,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>KFFB</t>
+          <t>LCUT</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1550,7 +1474,7 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>LGND</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1560,7 +1484,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>KNSA</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1570,7 +1494,7 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>KROS</t>
+          <t>LVLU</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -1580,7 +1504,7 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>KRSA</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -1590,7 +1514,7 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>MANE</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -1600,7 +1524,7 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -1610,7 +1534,7 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>MATH</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -1620,7 +1544,7 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LOCO</t>
+          <t>MDLN</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -1630,7 +1554,7 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LOPE</t>
+          <t>MDXG</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -1640,7 +1564,7 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -1650,7 +1574,7 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -1660,7 +1584,7 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MCGA</t>
+          <t>MORN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -1670,7 +1594,7 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -1680,7 +1604,7 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MESH</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -1690,7 +1614,7 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>MWYN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -1700,7 +1624,7 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -1710,7 +1634,7 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -1720,7 +1644,7 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>NMAD</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -1730,7 +1654,7 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>NVAX</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -1740,7 +1664,7 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>OCTV</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -1750,7 +1674,7 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -1760,7 +1684,7 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>NECB</t>
+          <t>OLLI</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -1770,7 +1694,7 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>NKSH</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -1780,7 +1704,7 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>NRDS</t>
+          <t>PAX</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -1790,7 +1714,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -1800,7 +1724,7 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -1810,7 +1734,7 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>NXTC</t>
+          <t>PRHI</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -1820,7 +1744,7 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>PRTH</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -1830,7 +1754,7 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>PRVA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -1840,7 +1764,7 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>OPLN</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -1850,7 +1774,7 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>QDEL</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -1860,7 +1784,7 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PANL</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -1870,7 +1794,7 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>RCBC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -1880,7 +1804,7 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>RGC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -1890,7 +1814,7 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>RPD</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -1900,7 +1824,7 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PGNY</t>
+          <t>RTSN</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -1910,7 +1834,7 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>RZLT</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -1920,7 +1844,7 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -1930,7 +1854,7 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PNRG</t>
+          <t>SANG</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -1940,7 +1864,7 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PRAA</t>
+          <t>SCHL</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -1950,7 +1874,7 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PRDO</t>
+          <t>SEZL</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -1960,7 +1884,7 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PSIX</t>
+          <t>SJ</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -1970,7 +1894,7 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>SMXT</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -1980,7 +1904,7 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PUBM</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -1990,7 +1914,7 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PXS</t>
+          <t>SOTK</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2000,7 +1924,7 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>SPT</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2010,7 +1934,7 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>QDEL</t>
+          <t>SSNC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2020,7 +1944,7 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>QLEP</t>
+          <t>STNE</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2030,7 +1954,7 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>SWKHL</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2040,7 +1964,7 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>QTEX</t>
+          <t>SWRD</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2050,7 +1974,7 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>RFAI</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2060,7 +1984,7 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>RGC</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2070,7 +1994,7 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>RIGL</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2080,7 +2004,7 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2090,7 +2014,7 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>VAI</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2100,7 +2024,7 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SAMG</t>
+          <t>VALU</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2110,251 +2034,11 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SCSC</t>
+          <t>WCCB</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr"/>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>SLDE</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr"/>
-      <c r="D159" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr"/>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>SLSN</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr"/>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>SMTI</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr"/>
-      <c r="D161" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr"/>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>SMXT</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr"/>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>SND</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr"/>
-      <c r="D163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr"/>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>SNFCA</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr"/>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>SPSC</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr"/>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>SPT</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr"/>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>SSTI</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr"/>
-      <c r="D167" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr"/>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>STGW</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr"/>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>SUJA</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr"/>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>SUNB</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr"/>
-      <c r="D170" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr"/>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>SWKHL</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr"/>
-      <c r="D171" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr"/>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>SWRD</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr"/>
-      <c r="D172" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr"/>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>TBCH</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr"/>
-      <c r="D173" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr"/>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>TEAM</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr"/>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>TENB</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr"/>
-      <c r="D175" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr"/>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>TJGC</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr"/>
-      <c r="D176" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr"/>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>TLN</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr"/>
-      <c r="D177" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr"/>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>TRI</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr"/>
-      <c r="D178" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr"/>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr"/>
-      <c r="D179" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr"/>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>WCCB</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr"/>
-      <c r="D180" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr"/>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>XFLH</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr"/>
-      <c r="D181" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr"/>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>ZSQR</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr"/>
-      <c r="D182" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D158"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,1604 +441,1244 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>ADMA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AHCO</t>
+          <t>AER</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACHC</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ACHC</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>AFYA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ATOS</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FNGR</t>
+          <t>CLWT</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AEP</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADMA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>AHG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GOOGM</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>CWCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AFRI</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AISP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>JDZG</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FBYD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ALRM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ANGH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>RPGL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>IIIV</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>AEP</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>IMKTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>AFRI</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AMGN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>APPN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RSVR</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>ISPR</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>AFRM</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LIF</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AOUT</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AFYA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>ARQT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TLS</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>RZLT</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ATLCL</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AGBK</t>
+          <t>ARX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AUGO</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AGCC</t>
+          <t>ASO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AVTR</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AISP</t>
+          <t>ATEC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BIIB</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ALLT</t>
+          <t>ATRA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BLKB</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>AUC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BMBL</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BMNP</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>BLIV</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BORR</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AOUT</t>
+          <t>BPRE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BREZ</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BRLT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BYRN</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>BSET</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BZ</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>BTSG</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CAKE</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ASTH</t>
+          <t>BTSGU</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CBC</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ATEC</t>
+          <t>BUUU</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CBFV</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AUGO</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CBLL</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>CBRL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CME</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>CLGN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CRAC</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BMBL</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CTAS</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BOW</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CVSA</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BPRE</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DDOG</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DLO</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DOCU</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DSGR</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DSGX</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>FERA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ECPG</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>FLYE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>EDHL</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>FRPT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>FRSH</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>EVRG</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>GIW</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>EXEL</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>FAST</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>FDBC</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CLOV</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>FLYW</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>FTRE</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>IMKTA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>GAINZ</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>INGN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>GCT</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>INTR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>GECCI</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CRNC</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>GILD</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>IRMD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>HLP</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ICG</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>KRNT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>IPXG</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ISRG</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>LAUR</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>MANE</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>JRSH</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>MATH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>KOD</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>MDLN</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>KRSA</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DLO</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>LIN</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>MMSI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>LVLU</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>OCTV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>PAX</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MCGA</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>PCRX</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>PLGO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MWYN</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>NCPL</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>PPLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>NMFCZ</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>PRTH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>NTWK</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>PRVA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>OKTA</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>OLLI</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>OTEX</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>RGCO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PACH</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>RPD</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PAHC</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FRPT</t>
+          <t>RTSN</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>SCHL</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SEZL</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PRHI</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>SJ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>RCBC</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GIW</t>
+          <t>SLDE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>RILYG</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SLSN</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>RPAY</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>SMXT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>RWAYL</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SND</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GOOGM</t>
+          <t>SPT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SOTK</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GOOGN</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SSNC</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>STNE</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>STGW</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>SWKHL</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SUJA</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TJGC</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>YDES</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TRI</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>ZSQR</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>IBRX</t>
-        </is>
-      </c>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>VALU</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>ICFI</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>INGN</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>INTR</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>IOVA</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr"/>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>IRMD</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr"/>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>JFU</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>JOYY</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr"/>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>JRSH</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr"/>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>KDP</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr"/>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>KNSA</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr"/>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>KOD</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr"/>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>KRNT</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr"/>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>KRT</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr"/>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>LAUR</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr"/>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>LCUT</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr"/>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>LGND</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr"/>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>LIN</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr"/>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>LVLU</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr"/>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>LYFT</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr"/>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>MANE</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr"/>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr"/>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>MATH</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr"/>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>MDLN</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr"/>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>MDXG</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr"/>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>MEDP</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr"/>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>MKTX</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr"/>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>MORN</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr"/>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>MRNA</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr"/>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr"/>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>MWYN</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr"/>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>NICE</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr"/>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>NIQ</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr"/>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>NMAD</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr"/>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>NVAX</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr"/>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>OCTV</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr"/>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>OKTA</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr"/>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>OLLI</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr"/>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>OTEX</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr"/>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr"/>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>PCTY</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr"/>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr"/>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>PRHI</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr"/>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>PRTH</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr"/>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>PRVA</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr"/>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>PTC</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr"/>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>QDEL</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr"/>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>QNBC</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr"/>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>RCBC</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr"/>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>RGC</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr"/>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>RPD</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr"/>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>RTSN</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr"/>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>RZLT</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr"/>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>SAFT</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr"/>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>SANG</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr"/>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>SCHL</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr"/>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>SEZL</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr"/>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>SJ</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr"/>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>SMXT</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr"/>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>SND</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr"/>
-      <c r="D145" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr"/>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>SOTK</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr"/>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>SPT</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr"/>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>SSNC</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr"/>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>STNE</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr"/>
-      <c r="D149" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr"/>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>SWKHL</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr"/>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>SWRD</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr"/>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>TEAM</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr"/>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>TRI</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr"/>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>TRMB</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr"/>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr"/>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>VAI</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr"/>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>VALU</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr"/>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>WCCB</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>FELE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -463,83 +463,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACHC</t>
+          <t>ACIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AFYA</t>
+          <t>AFRI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ATOS</t>
+          <t>FLX</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CLWT</t>
+          <t>AHCO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AHG</t>
+          <t>AIXI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GOOGM</t>
+          <t>LMAT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CWCO</t>
+          <t>FBYD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AFRI</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AISP</t>
+          <t>AMPH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FBYD</t>
+          <t>FOIL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ANGH</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RPGL</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -551,70 +551,78 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>AERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RSVR</t>
+          <t>PHUN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ISPR</t>
+          <t>MAZE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AOUT</t>
+          <t>AGYS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>PTON</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RZLT</t>
+          <t>PNRG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ATLCL</t>
+          <t>AIRT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ARX</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>APEI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SOMN</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RPC</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AUGO</t>
+          <t>ALLT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>ASTH</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -623,12 +631,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ATEC</t>
+          <t>ATLCL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -637,7 +645,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -651,12 +659,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>ANGI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AUC</t>
+          <t>ATRC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -665,7 +673,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BMBL</t>
+          <t>AOUT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -679,12 +687,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BMNP</t>
+          <t>API</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BLIV</t>
+          <t>AVTR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -693,12 +701,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BORR</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BPRE</t>
+          <t>AXIN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -707,12 +715,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BREZ</t>
+          <t>ARQT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BRLT</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -721,12 +729,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>ASBH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>BEBE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -735,12 +743,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>ASO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BTSG</t>
+          <t>BMR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -749,12 +757,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>ATEC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BTSGU</t>
+          <t>BORR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -763,12 +771,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>AUPH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BUUU</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -777,12 +785,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CBFV</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>BUUU</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -791,12 +799,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CBLL</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -805,12 +813,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>BYRN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -819,12 +827,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CLGN</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -833,12 +841,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>CBNK</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -847,12 +855,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CRAC</t>
+          <t>BVFL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -861,12 +869,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>BZUN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -875,12 +883,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>CAKE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>CHPG</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -889,12 +897,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>CMRC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -903,12 +911,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DLO</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>CRAC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -917,12 +925,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>CBFV</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -931,12 +939,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>CBLL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -945,12 +953,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>CBRL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FERA</t>
+          <t>DLO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -959,12 +967,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ECPG</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FLYE</t>
+          <t>DLXY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -973,12 +981,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FRPT</t>
+          <t>DMRC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -987,12 +995,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>EDHL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1001,12 +1009,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>CENT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GIW</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -1015,12 +1023,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>ELOG</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -1029,12 +1037,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>CHRD</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -1043,12 +1051,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FDBC</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>ENSC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1057,12 +1065,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>CNXN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ICFI</t>
+          <t>EVCM</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -1071,12 +1079,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IMKTA</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1085,12 +1093,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GAINZ</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>FCBC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1099,12 +1107,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>CRCT</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>FIZZ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1113,12 +1121,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GECCI</t>
+          <t>CRNC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>FRSH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1127,12 +1135,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IRMD</t>
+          <t>FVNNU</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1141,12 +1149,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>FXAC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1155,12 +1163,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1169,12 +1177,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IPXG</t>
+          <t>DAVE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1183,12 +1191,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1197,12 +1205,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>DHCNL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1211,12 +1219,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MATH</t>
+          <t>GRAN</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1225,12 +1233,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>DSGR</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MDLN</t>
+          <t>HOWL</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1239,12 +1247,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>KRSA</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>HTFL</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1253,12 +1261,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MMSI</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1267,12 +1275,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LVLU</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1281,12 +1289,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1295,12 +1303,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PAX</t>
+          <t>III</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1309,12 +1317,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MCGA</t>
+          <t>EXFY</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PCRX</t>
+          <t>IMKTA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1323,12 +1331,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PLGO</t>
+          <t>INTR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1337,12 +1345,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>EZPW</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1351,12 +1359,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>FDBC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PPLC</t>
+          <t>JANX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1365,12 +1373,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NMFCZ</t>
+          <t>FLYW</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PRTH</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1379,12 +1387,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>FNKO</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PRVA</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1393,12 +1401,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1407,12 +1415,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>LVLU</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1421,12 +1429,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>FWRG</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RGCO</t>
+          <t>MACI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1435,12 +1443,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PACH</t>
+          <t>GAING</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>MAT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1449,12 +1457,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PAHC</t>
+          <t>GAINZ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RTSN</t>
+          <t>MDLN</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1463,12 +1471,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1477,12 +1485,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>GDRX</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>MORN</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1491,12 +1499,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>GIBO</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SEZL</t>
+          <t>MQ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1505,12 +1513,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PRHI</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SJ</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1519,12 +1527,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RCBC</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>MSGM</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1533,12 +1541,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>RILYG</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SLSN</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1547,12 +1555,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RPAY</t>
+          <t>HBIO</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SMXT</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1561,12 +1569,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>RWAYL</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>NKSH</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1575,12 +1583,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>NTES</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1589,12 +1597,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SOTK</t>
+          <t>HNNA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>NXTC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1603,12 +1611,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>STNE</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1617,12 +1625,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STGW</t>
+          <t>IBRX</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1631,12 +1639,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SUJA</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>OPRT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1645,12 +1653,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TJGC</t>
+          <t>IPXG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>YDES</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1659,12 +1667,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ZSQR</t>
+          <t>OVBC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1673,12 +1681,730 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>VALU</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+          <t>JAKK</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PAHC</t>
+        </is>
+      </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>JOYY</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>KDP</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PAYS</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>KGEI</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PCVX</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>KNSA</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>PDSB</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>LAUR</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>PENG</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>LIN</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>PFXNZ</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>LOCO</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>PLGO</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>LOPE</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PLMR</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PRDO</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>MANH</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>QQQX</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>MDLZ</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>RILYG</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>MEDP</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>RTSN</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>MKTX</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>RUSHB</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MMSI</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>RVSB</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>MWYN</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SAFT</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>NAVN</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SAMG</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>NCPL</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SBAC</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>NRDS</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SCHL</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>NSIT</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>NTAP</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SGC</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>NTWK</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SHPH</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>OCTV</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SIBN</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SJ</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>OLLI</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SKWD</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>OSW</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SKYA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>OTEX</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SMPL</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SMTI</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>PBYI</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>SNFCA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>SOTK</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>PCYO</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>PNTG</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SSTI</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>PPLC</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>STRA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>PRHI</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SWKHL</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>PRVA</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SWRD</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>PTLO</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>RCEL</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>TLN</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>RELY</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>RGC</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>RPAY</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>VYLR</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>RPD</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>YDES</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>RRGB</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>SLDE</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>SPSC</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>SSNC</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>STLN</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>STRC</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>STRF</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>TASK</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>TBCH</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>TEAM</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>TRI</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>VSXY</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>WLTH</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D141"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,46 +446,46 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>ACHC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FELE</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>BHST</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>ACGL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AFRI</t>
+          <t>AFYA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FLX</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AHCO</t>
+          <t>CABR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>ACIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,29 +495,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LMAT</t>
+          <t>MAZE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FBYD</t>
+          <t>EXC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>NDLS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -534,109 +534,97 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMPL</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>PDD</t>
-        </is>
-      </c>
+          <t>AMPH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IIIV</t>
+          <t>GTM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AERO</t>
+          <t>AGBK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ANDG</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>PHUN</t>
-        </is>
-      </c>
+          <t>APOG</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>IIIV</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AGYS</t>
+          <t>AGCC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>APA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>PTON</t>
-        </is>
-      </c>
+          <t>ASO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PNRG</t>
+          <t>LNT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AIRT</t>
+          <t>AOUT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>APEI</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>SOMN</t>
-        </is>
-      </c>
+          <t>ATLCZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>OMCL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALLT</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ASTH</t>
+          <t>ATOS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RPC</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>APEI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ATLCL</t>
+          <t>ATRC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -645,12 +633,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ATRA</t>
+          <t>AUGO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -659,12 +647,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>ARX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>BCPC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -673,12 +661,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AOUT</t>
+          <t>ASBH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>BOLT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -687,12 +675,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>ATKR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>BORR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -701,12 +689,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>AVTR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AXIN</t>
+          <t>BRLT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -715,12 +703,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -729,12 +717,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ASBH</t>
+          <t>BLMN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BEBE</t>
+          <t>CBNK</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -743,12 +731,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BMR</t>
+          <t>CDRO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -757,12 +745,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ATEC</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BORR</t>
+          <t>CENTA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -771,12 +759,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>BYRN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BOW</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -785,12 +773,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BUUU</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -799,12 +787,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>BZUN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -813,12 +801,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -827,12 +815,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>CBRL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -841,12 +829,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CBNK</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -855,12 +843,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BVFL</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>EDHL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -869,12 +857,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>ELOG</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -883,12 +871,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>CENT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CHPG</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -897,12 +885,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>CHRD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CMRC</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -911,12 +899,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CRAC</t>
+          <t>FELE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -925,12 +913,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CBFV</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>FRPT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -939,12 +927,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CBLL</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>FSBW</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -953,12 +941,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DLO</t>
+          <t>GAING</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -967,12 +955,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DLXY</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -981,12 +969,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>GGR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -995,12 +983,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>DAAQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1009,12 +997,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CENT</t>
+          <t>DBCA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>GRAN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -1023,12 +1011,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ELOG</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -1037,12 +1025,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CHRD</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -1051,12 +1039,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>DMLP</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ENSC</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1065,12 +1053,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CNXN</t>
+          <t>DUKU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EVCM</t>
+          <t>III</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -1079,12 +1067,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>INBKZ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1093,12 +1081,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FCBC</t>
+          <t>INGN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1107,12 +1095,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CRCT</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FIZZ</t>
+          <t>IRMD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1121,12 +1109,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CRNC</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>JBDI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1135,12 +1123,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>FCBC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FVNNU</t>
+          <t>JCSE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1149,12 +1137,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>FDBC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FXAC</t>
+          <t>JYD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1163,12 +1151,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>FIZZ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1177,12 +1165,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DAVE</t>
+          <t>FOSL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1191,12 +1179,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1205,12 +1193,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DHCNL</t>
+          <t>FVNNU</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1219,12 +1207,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GRAN</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1233,12 +1221,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HOWL</t>
+          <t>LVLU</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1247,12 +1235,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>HPK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>MATH</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1261,12 +1249,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1275,12 +1263,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>MSGM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1289,12 +1277,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ICFI</t>
+          <t>NKSH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1303,12 +1291,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1317,12 +1305,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EXFY</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IMKTA</t>
+          <t>OLB</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1331,12 +1319,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>OLLI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1345,12 +1333,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EZPW</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>OPLN</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1359,12 +1347,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FDBC</t>
+          <t>LOCO</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JANX</t>
+          <t>OSW</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1373,12 +1361,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>PAHC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1387,12 +1375,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1401,12 +1389,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>PDSB</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1415,12 +1403,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LVLU</t>
+          <t>PEBK</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1429,12 +1417,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FWRG</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MACI</t>
+          <t>PLGO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1443,12 +1431,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GAING</t>
+          <t>MWYN</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>RGCO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1457,12 +1445,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GAINZ</t>
+          <t>NATH</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MDLN</t>
+          <t>RILYG</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1471,12 +1459,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>NAVN</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>RTSN</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1485,12 +1473,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GDRX</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>RWAYM</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1499,12 +1487,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>PLMR</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1513,12 +1501,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>PPLC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>SBAC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1527,12 +1515,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>PTLO</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MSGM</t>
+          <t>SGRY</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1541,12 +1529,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>RGC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>SJ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1555,12 +1543,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>RYZ</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>SKWD</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1569,12 +1557,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>SGC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NKSH</t>
+          <t>SMPL</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1583,12 +1571,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>SLDE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NTES</t>
+          <t>SMXT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1597,12 +1585,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HNNA</t>
+          <t>SOMN</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NXTC</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1611,12 +1599,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>STRA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1625,12 +1613,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>SWKHL</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1639,12 +1627,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>SWRD</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1653,758 +1641,76 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>IPXG</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>TCRT</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>ISRG</t>
-        </is>
-      </c>
+      <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>OVBC</t>
+          <t>TDAY</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>JAKK</t>
-        </is>
-      </c>
+      <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PAHC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>JOYY</t>
-        </is>
-      </c>
+      <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PAX</t>
+          <t>UTHR</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>KDP</t>
-        </is>
-      </c>
+      <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>VSXY</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>KGEI</t>
-        </is>
-      </c>
+      <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PCVX</t>
+          <t>VYLR</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>KNSA</t>
-        </is>
-      </c>
+      <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>XFLH</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>LAUR</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>PENG</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>LIN</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>PFXNZ</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>LOCO</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>PLGO</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>LOPE</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>PLMR</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>LYFT</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>PRDO</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>MANH</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>PYPL</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>QQQX</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>MDLZ</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>RILYG</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>MEDP</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>RTSN</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>MKTX</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>RUSHB</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>MMSI</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>RVSB</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>MWYN</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>SAFT</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>NAVN</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>SAMG</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>NCPL</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>SBAC</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>NRDS</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>SCHL</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>NSIT</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>SEZL</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>NTAP</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>SGC</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>NTWK</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>SHPH</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>OCTV</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>SIBN</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>ODD</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>SJ</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>OLLI</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>SKWD</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>OSW</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>SKYA</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>OTEX</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>SMPL</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>SMTI</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>PBYI</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>SNFCA</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>PCTY</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>SOTK</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>PCYO</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>SPT</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>PNTG</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>SSTI</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>PPLC</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>STRA</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>PRHI</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>SWKHL</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>PRVA</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>SWRD</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>PTLO</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>TECH</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>RCEL</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>TLN</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>RELY</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>TRMB</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>RGC</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>RPAY</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>VYLR</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>RPD</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>YDES</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>RRGB</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>SHOP</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>SLDE</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr"/>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>SPSC</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>SSNC</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr"/>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>STLN</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>STRC</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>STRF</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>TASK</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>TBCH</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>TEAM</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>TRI</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>VSXY</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>WLTH</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D149"/>
+  <dimension ref="A1:D230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,48 +441,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AERO</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BKYI</t>
+          <t>AMSF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BIII</t>
+          <t>JCSE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>ACGL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CABR</t>
+          <t>ASTH</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CFFI</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AFYA</t>
+          <t>ACHC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -493,14 +489,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DH</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ALLT</t>
+          <t>ACIC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -511,74 +503,58 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ENGS</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>DAKT</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NATH</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DAKT</t>
+          <t>GTM</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RGC</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>IOTR</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>VAI</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>ADUS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FOIL</t>
+          <t>ISPR</t>
         </is>
       </c>
     </row>
@@ -586,13 +562,13 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>AFYA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>JZ</t>
         </is>
       </c>
     </row>
@@ -600,13 +576,13 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>AGYS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>INTJ</t>
+          <t>LMAT</t>
         </is>
       </c>
     </row>
@@ -614,13 +590,13 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IOTR</t>
+          <t>LZ</t>
         </is>
       </c>
     </row>
@@ -628,13 +604,13 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>AMPH</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>MELI</t>
         </is>
       </c>
     </row>
@@ -642,13 +618,13 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ARX</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>MGPI</t>
         </is>
       </c>
     </row>
@@ -656,13 +632,13 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ARXS</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>MLKN</t>
         </is>
       </c>
     </row>
@@ -670,13 +646,13 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ASBH</t>
+          <t>ANGI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NDLS</t>
+          <t>ODFL</t>
         </is>
       </c>
     </row>
@@ -684,13 +660,13 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ATLCL</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>OFIX</t>
         </is>
       </c>
     </row>
@@ -698,7 +674,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ATLCZ</t>
+          <t>APEI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -712,13 +688,13 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ATLO</t>
+          <t>APPF</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OSG</t>
+          <t>OSW</t>
         </is>
       </c>
     </row>
@@ -726,13 +702,13 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PGNY</t>
+          <t>PDD</t>
         </is>
       </c>
     </row>
@@ -740,13 +716,13 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BCML</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PWRL</t>
+          <t>PGNY</t>
         </is>
       </c>
     </row>
@@ -754,13 +730,13 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>ARHS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>PLAY</t>
         </is>
       </c>
     </row>
@@ -768,13 +744,13 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BLMN</t>
+          <t>ARQT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SOLS</t>
+          <t>PODD</t>
         </is>
       </c>
     </row>
@@ -782,67 +758,91 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BMBL</t>
+          <t>ARXS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PPLC</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BPRN</t>
+          <t>ASO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>QDEL</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>ATLCZ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SOLS</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>ATLO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>STFS</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>ATRC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TDAY</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>AUPH</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TRIP</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -852,7 +852,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -862,7 +862,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CBNK</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -872,7 +872,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -882,7 +882,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -892,7 +892,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -902,7 +902,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>COLM</t>
+          <t>BRBR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -912,7 +912,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>BRCB</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -922,7 +922,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>BRLT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -932,7 +932,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CPHC</t>
+          <t>BSET</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -942,7 +942,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CPOP</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -952,7 +952,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -962,7 +962,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>BTSG</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -972,7 +972,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>BVFL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -982,7 +982,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -992,7 +992,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DAVE</t>
+          <t>BWMN</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1002,7 +1002,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1022,7 +1022,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>CAKE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1032,7 +1032,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>CAQ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1042,7 +1042,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1052,7 +1052,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>CBLL</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>CBNK</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1082,7 +1082,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EZPW</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1092,7 +1092,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FACT</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1102,7 +1102,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>CENT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1112,7 +1112,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FCBC</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1122,7 +1122,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FDBC</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1132,7 +1132,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FLYE</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1142,7 +1142,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>CHAD</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1152,7 +1152,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FOSL</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1162,7 +1162,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FRPT</t>
+          <t>CHRD</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1172,7 +1172,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>CHYM</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1182,7 +1182,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GAINI</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1192,7 +1192,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1202,7 +1202,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1212,7 +1212,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1222,7 +1222,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1232,7 +1232,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HOWL</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1242,7 +1242,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1252,7 +1252,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HWKN</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1262,7 +1262,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1272,7 +1272,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1282,7 +1282,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IIIV</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>CVSA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1302,7 +1302,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1312,7 +1312,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1322,7 +1322,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1332,7 +1332,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IPXG</t>
+          <t>DLO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1342,7 +1342,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1352,7 +1352,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JCSE</t>
+          <t>DMRC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1362,7 +1362,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1382,7 +1382,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1392,7 +1392,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>KMRK</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1402,7 +1402,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>EDHL</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1422,7 +1422,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1442,7 +1442,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1452,7 +1452,7 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LOPE</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1462,7 +1462,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>ENSC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1472,7 +1472,7 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1482,7 +1482,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1492,7 +1492,7 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MMSI</t>
+          <t>EVCM</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -1502,7 +1502,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1522,7 +1522,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -1532,7 +1532,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>NAVN</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -1542,7 +1542,7 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>NKSH</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1552,7 +1552,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>FCBC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1562,7 +1562,7 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>NTRSO</t>
+          <t>FIZZ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1572,7 +1572,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>FRSH</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1582,7 +1582,7 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>NXPL</t>
+          <t>FTDR</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -1592,7 +1592,7 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>OFRM</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -1602,7 +1602,7 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>OLB</t>
+          <t>FWRG</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -1612,7 +1612,7 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -1622,7 +1622,7 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>OPLN</t>
+          <t>GDRX</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -1632,7 +1632,7 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>GEGGL</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>OXLCZ</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -1652,7 +1652,7 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PAHC</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -1662,7 +1662,7 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PCRX</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -1672,7 +1672,7 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PEBK</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -1682,7 +1682,7 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PICS</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -1692,7 +1692,7 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -1702,7 +1702,7 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -1712,7 +1712,7 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PRDO</t>
+          <t>HELE</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -1722,7 +1722,7 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PRME</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -1732,7 +1732,7 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -1742,7 +1742,7 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PXS</t>
+          <t>HUIZ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -1752,7 +1752,7 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>HWKN</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -1762,7 +1762,7 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>RGCO</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -1772,7 +1772,7 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>RNW</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -1782,7 +1782,7 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -1792,7 +1792,7 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>IIIV</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -1802,7 +1802,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>RTSN</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -1812,7 +1812,7 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>INTR</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -1822,7 +1822,7 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>RYZ</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -1832,7 +1832,7 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>IOSP</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -1842,7 +1842,7 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SAIH</t>
+          <t>IPAR</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -1852,7 +1852,7 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SAMG</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -1862,7 +1862,7 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SCSC</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -1872,7 +1872,7 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SGC</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -1882,7 +1882,7 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SKWD</t>
+          <t>JOYY</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -1892,7 +1892,7 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>JVA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -1902,7 +1902,7 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -1912,7 +1912,7 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SMXT</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -1922,7 +1922,7 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -1932,7 +1932,7 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>KMTS</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -1942,7 +1942,7 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>KNSA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -1952,7 +1952,7 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>STNE</t>
+          <t>KOD</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -1962,7 +1962,7 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SUJA</t>
+          <t>LAUR</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SUNB</t>
+          <t>LFCR</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -1982,7 +1982,7 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TCRT</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -1992,7 +1992,7 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -2002,7 +2002,7 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TRNZ</t>
+          <t>LOGI</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2012,7 +2012,7 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>VSXY</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2032,11 +2032,821 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>YSWY</t>
+          <t>MAZE</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>MDLZ</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>MEDP</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>MEOH</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>MMSI</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>MNDY</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>MNRO</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>MNST</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>MORN</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>MRNA</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>MRSH</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>MWYN</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>NATH</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>NAVN</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>NCNO</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>NDAQ</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>NIQ</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>NRDS</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>NTRSO</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>NWE</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>NWS</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>NWSA</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>OFRM</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>OFS</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>OLLI</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>ONC</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>OPCH</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>ORIQ</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>ORLY</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>OTEX</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>OXLCM</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>PEGA</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>PICS</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>PLGO</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>PRCH</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>PRDO</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>PRVA</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>PTC</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>PTLO</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>PTON</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr"/>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>QNBC</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>RCEL</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>RELY</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>ROP</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>ROST</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>RPAY</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr"/>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>RPC</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>RPRX</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr"/>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>RRGB</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr"/>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>RTSN</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr"/>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>RVSB</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr"/>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>SAIC</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr"/>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>SGRY</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr"/>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>SHOO</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr"/>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr"/>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>SIBN</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr"/>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SKWD</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr"/>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>SKYA</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr"/>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>SLDE</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr"/>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>SNFCA</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr"/>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>SPSC</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr"/>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr"/>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>SSNC</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr"/>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>SSTI</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr"/>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>STNE</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr"/>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>STRA</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr"/>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>SYNA</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr"/>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>SZZL</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr"/>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>TEAM</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr"/>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>TRI</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr"/>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr"/>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr"/>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>UTHR</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr"/>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>VAI</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr"/>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>XZO</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr"/>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>YSWY</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D230"/>
+  <dimension ref="A1:D222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,11 +439,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BRZE</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>ABNB</t>
@@ -452,25 +448,21 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AMSF</t>
+          <t>AER</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>JCSE</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ACGL</t>
+          <t>ACHC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ASTH</t>
+          <t>ATAT</t>
         </is>
       </c>
     </row>
@@ -478,13 +470,13 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACHC</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CASY</t>
+          <t>AZN</t>
         </is>
       </c>
     </row>
@@ -492,13 +484,13 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>COCO</t>
+          <t>CASY</t>
         </is>
       </c>
     </row>
@@ -506,13 +498,13 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DAKT</t>
+          <t>CHDN</t>
         </is>
       </c>
     </row>
@@ -520,13 +512,13 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>ADUS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>CROX</t>
         </is>
       </c>
     </row>
@@ -534,13 +526,13 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IOTR</t>
+          <t>CSX</t>
         </is>
       </c>
     </row>
@@ -548,13 +540,13 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ADUS</t>
+          <t>AGYS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ISPR</t>
+          <t>ENSG</t>
         </is>
       </c>
     </row>
@@ -562,13 +554,13 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AFYA</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JZ</t>
+          <t>EXC</t>
         </is>
       </c>
     </row>
@@ -576,13 +568,13 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AGYS</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LMAT</t>
+          <t>FLX</t>
         </is>
       </c>
     </row>
@@ -590,13 +582,13 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>FSV</t>
         </is>
       </c>
     </row>
@@ -604,13 +596,13 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>APEI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
@@ -618,13 +610,13 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>APOG</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>KWY</t>
         </is>
       </c>
     </row>
@@ -632,13 +624,13 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>APPF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MLKN</t>
+          <t>LNT</t>
         </is>
       </c>
     </row>
@@ -646,7 +638,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -660,7 +652,7 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ARHS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -674,13 +666,13 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>ARLP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OMCL</t>
+          <t>OXSQ</t>
         </is>
       </c>
     </row>
@@ -688,13 +680,13 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>APPF</t>
+          <t>ARQT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OSW</t>
+          <t>PECO</t>
         </is>
       </c>
     </row>
@@ -702,13 +694,13 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>ASBH</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>PWRL</t>
         </is>
       </c>
     </row>
@@ -716,13 +708,13 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>ASO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PGNY</t>
+          <t>QDEL</t>
         </is>
       </c>
     </row>
@@ -730,13 +722,13 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>ATEC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>SOLS</t>
         </is>
       </c>
     </row>
@@ -744,13 +736,13 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>ATRC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PODD</t>
+          <t>STFS</t>
         </is>
       </c>
     </row>
@@ -758,13 +750,13 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ARXS</t>
+          <t>AUDC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PPLC</t>
+          <t>TCMD</t>
         </is>
       </c>
     </row>
@@ -772,77 +764,57 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>AUPH</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>QDEL</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ATLCZ</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>SOLS</t>
-        </is>
-      </c>
+      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ATLO</t>
+          <t>AVTR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>STFS</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>BCML</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>TDAY</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>TRIP</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -852,7 +824,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>BRBR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -862,7 +834,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>BSVN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -872,7 +844,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -882,7 +854,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>BTSG</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -892,7 +864,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>BVS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -902,7 +874,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BRBR</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -912,7 +884,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -922,7 +894,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BRLT</t>
+          <t>BZUN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -932,7 +904,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -942,7 +914,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>CAKE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -952,7 +924,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -962,7 +934,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BTSG</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -972,7 +944,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BVFL</t>
+          <t>CBLL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -982,7 +954,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>CBRL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -992,7 +964,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1002,7 +974,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1012,7 +984,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>CDZI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1022,7 +994,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1032,7 +1004,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CAQ</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1042,7 +1014,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>CHAD</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1052,7 +1024,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CBLL</t>
+          <t>CHRD</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1062,7 +1034,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CBNK</t>
+          <t>CHYM</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1072,7 +1044,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1082,7 +1054,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>CMRC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1092,7 +1064,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1102,7 +1074,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CENT</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1112,7 +1084,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1122,7 +1094,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1132,7 +1104,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1142,7 +1114,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1152,7 +1124,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>DAKT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1162,7 +1134,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CHRD</t>
+          <t>DAVE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1172,7 +1144,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CHYM</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1182,7 +1154,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1192,7 +1164,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1202,7 +1174,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>DLO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1212,7 +1184,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1222,7 +1194,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>DMRC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1232,7 +1204,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1242,7 +1214,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>DSGR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1252,7 +1224,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1262,7 +1234,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1272,7 +1244,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1282,7 +1254,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1292,7 +1264,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1302,7 +1274,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1312,7 +1284,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1322,7 +1294,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1332,7 +1304,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DLO</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1342,7 +1314,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1352,7 +1324,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>EXFY</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1362,7 +1334,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1372,7 +1344,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1382,7 +1354,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>EZPW</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1392,7 +1364,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1402,7 +1374,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>FRSH</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1412,7 +1384,7 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>FTDR</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1422,7 +1394,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1432,7 +1404,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>GABC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1442,7 +1414,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>GDRX</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1452,7 +1424,7 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1462,7 +1434,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ENSC</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1472,7 +1444,7 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1482,7 +1454,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1492,7 +1464,7 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EVCM</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -1502,7 +1474,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -1512,7 +1484,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1522,7 +1494,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>HOWL</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -1532,7 +1504,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>HPK</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -1542,7 +1514,7 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1552,7 +1524,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FCBC</t>
+          <t>HTFL</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1562,7 +1534,7 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FIZZ</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1572,7 +1544,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1582,7 +1554,7 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -1592,7 +1564,7 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>IGAC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -1602,7 +1574,7 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FWRG</t>
+          <t>III</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -1612,7 +1584,7 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>IIIV</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -1622,7 +1594,7 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GDRX</t>
+          <t>INGN</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -1632,7 +1604,7 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GEGGL</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -1642,7 +1614,7 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -1652,7 +1624,7 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>IOSP</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -1662,7 +1634,7 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -1672,7 +1644,7 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>IPAR</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -1682,7 +1654,7 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>IRMD</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -1692,7 +1664,7 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -1702,7 +1674,7 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>JCAP</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -1712,7 +1684,7 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>HELE</t>
+          <t>KOD</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -1722,7 +1694,7 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -1732,7 +1704,7 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -1742,7 +1714,7 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HUIZ</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -1752,7 +1724,7 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HWKN</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -1762,7 +1734,7 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>LOCO</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -1772,7 +1744,7 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ICFI</t>
+          <t>LOGI</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -1782,7 +1754,7 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -1792,7 +1764,7 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>IIIV</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -1802,7 +1774,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -1812,7 +1784,7 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -1822,7 +1794,7 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>MAZE</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -1832,7 +1804,7 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -1842,7 +1814,7 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>IPAR</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -1852,7 +1824,7 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>MMSI</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -1862,7 +1834,7 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>MNDY</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -1872,7 +1844,7 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -1882,7 +1854,7 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>MORN</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -1892,7 +1864,7 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>JVA</t>
+          <t>MQ</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -1902,7 +1874,7 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -1912,7 +1884,7 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -1922,7 +1894,7 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>NATH</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -1932,7 +1904,7 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>KMTS</t>
+          <t>NAUT</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -1942,7 +1914,7 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>KNSA</t>
+          <t>NAVN</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -1952,7 +1924,7 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>NCNO</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -1962,7 +1934,7 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -1972,7 +1944,7 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>LFCR</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -1982,7 +1954,7 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -1992,7 +1964,7 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>NSIT</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -2002,7 +1974,7 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2012,7 +1984,7 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2022,7 +1994,7 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2032,7 +2004,7 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2042,7 +2014,7 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>NXPL</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2052,7 +2024,7 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>OCTV</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2062,7 +2034,7 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>ODD</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2072,7 +2044,7 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MMSI</t>
+          <t>OFRM</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2082,7 +2054,7 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>MNDY</t>
+          <t>OLB</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2092,7 +2064,7 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>ONC</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2102,7 +2074,7 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>OPLN</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2112,7 +2084,7 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>OPRT</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2122,7 +2094,7 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -2132,7 +2104,7 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>OTAI</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -2142,7 +2114,7 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -2152,7 +2124,7 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2162,7 +2134,7 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>PAGP</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -2172,7 +2144,7 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>NAVN</t>
+          <t>PAHC</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -2182,7 +2154,7 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>NCNO</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -2192,7 +2164,7 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -2202,7 +2174,7 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>PMTS</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -2212,7 +2184,7 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>NRDS</t>
+          <t>PODD</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -2222,7 +2194,7 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>NTRSO</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -2232,7 +2204,7 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>PRGS</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -2242,7 +2214,7 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>PRME</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -2252,7 +2224,7 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>PRVA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -2262,7 +2234,7 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>PSIX</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -2272,7 +2244,7 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>OFRM</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -2282,7 +2254,7 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>OFS</t>
+          <t>PTLE</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -2292,7 +2264,7 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -2302,7 +2274,7 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ONC</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -2312,7 +2284,7 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>RCEL</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -2322,7 +2294,7 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ORIQ</t>
+          <t>RCKY</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -2332,7 +2304,7 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -2342,7 +2314,7 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>REF</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -2352,7 +2324,7 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>OXLCM</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -2362,7 +2334,7 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>RELY</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -2372,7 +2344,7 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>RGC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -2382,7 +2354,7 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PICS</t>
+          <t>RGCO</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -2392,7 +2364,7 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PLGO</t>
+          <t>ROOT</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -2402,7 +2374,7 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>ROST</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -2412,7 +2384,7 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PRDO</t>
+          <t>RPC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -2422,7 +2394,7 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PRVA</t>
+          <t>RPRX</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -2432,7 +2404,7 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>RTSN</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -2442,7 +2414,7 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PTLO</t>
+          <t>RVSB</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -2452,7 +2424,7 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PTON</t>
+          <t>RYZ</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -2462,7 +2434,7 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -2472,7 +2444,7 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>SBAC</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -2482,7 +2454,7 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>SEZL</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -2492,7 +2464,7 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -2502,7 +2474,7 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>SIBN</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -2512,7 +2484,7 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>RELY</t>
+          <t>SIGI</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -2522,7 +2494,7 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>SJ</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -2532,7 +2504,7 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ROST</t>
+          <t>SKIN</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -2542,7 +2514,7 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>RPAY</t>
+          <t>SKYA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -2552,7 +2524,7 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>SLN</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -2562,7 +2534,7 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>SMPL</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -2572,7 +2544,7 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>RRGB</t>
+          <t>SNFCA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -2582,7 +2554,7 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>RTSN</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -2592,7 +2564,7 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>SPT</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -2602,7 +2574,7 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>SSTI</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -2612,7 +2584,7 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SGRY</t>
+          <t>SUNB</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -2622,7 +2594,7 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SHOO</t>
+          <t>SYNA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -2632,7 +2604,7 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>TASK</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -2642,7 +2614,7 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>TCRT</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -2652,7 +2624,7 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SKWD</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -2662,7 +2634,7 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -2672,7 +2644,7 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>TLN</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -2682,7 +2654,7 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>SNFCA</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -2692,7 +2664,7 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -2702,7 +2674,7 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -2712,7 +2684,7 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>UTHR</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -2722,7 +2694,7 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>SSTI</t>
+          <t>VYLR</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -2732,7 +2704,7 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>STNE</t>
+          <t>WLTH</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -2742,7 +2714,7 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>STRA</t>
+          <t>WSBCO</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -2752,7 +2724,7 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>SYNA</t>
+          <t>XZO</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -2762,91 +2734,11 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>SZZL</t>
+          <t>YMAT</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr"/>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>TEAM</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr"/>
-      <c r="D223" t="inlineStr"/>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr"/>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>TRI</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr"/>
-      <c r="D224" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr"/>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>TRMB</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr"/>
-      <c r="D225" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr"/>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr"/>
-      <c r="D226" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr"/>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>UTHR</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr"/>
-      <c r="D227" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr"/>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>VAI</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr"/>
-      <c r="D228" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr"/>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>XZO</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr"/>
-      <c r="D229" t="inlineStr"/>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr"/>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>YSWY</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr"/>
-      <c r="D230" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D222"/>
+  <dimension ref="A1:D251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,13 +442,13 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>AMSF</t>
         </is>
       </c>
     </row>
@@ -456,13 +456,13 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ACHC</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ATAT</t>
+          <t>CASY</t>
         </is>
       </c>
     </row>
@@ -470,13 +470,13 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>CSX</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CASY</t>
+          <t>FLX</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>GIII</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CROX</t>
+          <t>GPGI</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>IOTR</t>
         </is>
       </c>
     </row>
@@ -540,13 +540,13 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AGYS</t>
+          <t>AFYA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ENSG</t>
+          <t>KLTR</t>
         </is>
       </c>
     </row>
@@ -554,13 +554,13 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>LCNB</t>
         </is>
       </c>
     </row>
@@ -568,13 +568,13 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>AGYS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FLX</t>
+          <t>LIF</t>
         </is>
       </c>
     </row>
@@ -582,13 +582,13 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>ALLT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FSV</t>
+          <t>MGPI</t>
         </is>
       </c>
     </row>
@@ -596,13 +596,13 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>NXGL</t>
         </is>
       </c>
     </row>
@@ -610,13 +610,13 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KWY</t>
+          <t>ODFL</t>
         </is>
       </c>
     </row>
@@ -624,13 +624,13 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>APPF</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>OSG</t>
         </is>
       </c>
     </row>
@@ -638,13 +638,13 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>AMPH</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>PODD</t>
         </is>
       </c>
     </row>
@@ -652,13 +652,13 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OFIX</t>
+          <t>POOL</t>
         </is>
       </c>
     </row>
@@ -666,13 +666,13 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ARLP</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OXSQ</t>
+          <t>REYN</t>
         </is>
       </c>
     </row>
@@ -680,13 +680,13 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>ANIK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>STFS</t>
         </is>
       </c>
     </row>
@@ -694,13 +694,13 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ASBH</t>
+          <t>AOUT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PWRL</t>
+          <t>TRIP</t>
         </is>
       </c>
     </row>
@@ -708,63 +708,47 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>APEI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>QDEL</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ATEC</t>
+          <t>APOG</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>SOLS</t>
-        </is>
-      </c>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>STFS</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>ARHS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TCMD</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>ATLO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -774,7 +758,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>AUPH</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -784,7 +768,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -794,7 +778,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BCML</t>
+          <t>AVTR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -804,7 +788,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -814,7 +798,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>BANF</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -824,7 +808,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BRBR</t>
+          <t>BCML</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -834,7 +818,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>BFST</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -844,7 +828,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -854,7 +838,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BTSG</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -864,7 +848,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BVS</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -874,7 +858,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -884,7 +868,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>BPRN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -894,7 +878,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -904,7 +888,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>BRCB</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -914,7 +898,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -924,7 +908,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>BSET</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -934,7 +918,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>BSVN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -944,7 +928,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CBLL</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -954,7 +938,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>BVS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -964,7 +948,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -974,7 +958,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>BZUN</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -984,7 +968,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CDZI</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -994,7 +978,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1004,7 +988,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CBNK</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1014,7 +998,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>CBRL</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1024,7 +1008,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CHRD</t>
+          <t>CCNE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1034,7 +1018,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CHYM</t>
+          <t>CENTA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1044,7 +1028,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1054,7 +1038,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CMRC</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1064,7 +1048,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1074,7 +1058,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>CHAD</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1084,7 +1068,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1094,7 +1078,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1104,7 +1088,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>CLAR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1114,7 +1098,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1124,7 +1108,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DAKT</t>
+          <t>CNXC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1134,7 +1118,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DAVE</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1144,7 +1128,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>CPIX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1154,7 +1138,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1164,7 +1148,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1174,7 +1158,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DLO</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1184,7 +1168,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1194,7 +1178,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1204,7 +1188,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1214,7 +1198,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>CVSA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1224,7 +1208,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>CYRX</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1234,7 +1218,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>DAVE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1244,7 +1228,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1254,7 +1238,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1264,7 +1248,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1274,7 +1258,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>DMAC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1284,7 +1268,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>DMLP</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1294,7 +1278,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1304,7 +1288,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1314,7 +1298,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>DSGR</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1324,7 +1308,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EXFY</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1334,7 +1318,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1344,7 +1328,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>DUKU</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1354,7 +1338,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EZPW</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1364,7 +1348,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1374,7 +1358,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1384,7 +1368,7 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1394,7 +1378,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>ENSC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1404,7 +1388,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GABC</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1414,7 +1398,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GDRX</t>
+          <t>ESLT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1424,7 +1408,7 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1434,7 +1418,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>EVAX</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1444,7 +1428,7 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>EVER</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1454,7 +1438,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1464,7 +1448,7 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -1474,7 +1458,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -1484,7 +1468,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1494,7 +1478,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HOWL</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -1504,7 +1488,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -1514,7 +1498,7 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>FIZZ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1524,7 +1508,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>FLYW</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1534,7 +1518,7 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>FNKO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1544,7 +1528,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>FNLC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1554,7 +1538,7 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>FRSH</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -1564,7 +1548,7 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>IGAC</t>
+          <t>FSV</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -1574,7 +1558,7 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>FTDR</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -1584,7 +1568,7 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>IIIV</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -1594,7 +1578,7 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>GDRX</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -1604,7 +1588,7 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -1614,7 +1598,7 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -1624,7 +1608,7 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -1634,7 +1618,7 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -1644,7 +1628,7 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>IPAR</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -1654,7 +1638,7 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>IRMD</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -1664,7 +1648,7 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -1674,7 +1658,7 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>JCAP</t>
+          <t>HBNC</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -1684,7 +1668,7 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -1694,7 +1678,7 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -1704,7 +1688,7 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>HPK</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -1714,7 +1698,7 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>HQY</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -1724,7 +1708,7 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -1734,7 +1718,7 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LOCO</t>
+          <t>HTFL</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -1744,7 +1728,7 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -1754,7 +1738,7 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -1764,7 +1748,7 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -1774,7 +1758,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -1784,7 +1768,7 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -1794,7 +1778,7 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>III</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -1804,7 +1788,7 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>IIIV</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -1814,7 +1798,7 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>INGN</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -1824,7 +1808,7 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MMSI</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -1834,7 +1818,7 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MNDY</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -1844,7 +1828,7 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>IRMD</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -1854,7 +1838,7 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>IRON</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -1864,7 +1848,7 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -1874,7 +1858,7 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -1884,7 +1868,7 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -1894,7 +1878,7 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -1904,7 +1888,7 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>KIDS</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -1914,7 +1898,7 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>NAVN</t>
+          <t>KINS</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -1924,7 +1908,7 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>NCNO</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -1934,7 +1918,7 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -1944,7 +1928,7 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -1954,7 +1938,7 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -1964,7 +1948,7 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -1974,7 +1958,7 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>LMAT</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -1984,7 +1968,7 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -1994,7 +1978,7 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2004,7 +1988,7 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2014,7 +1998,7 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NXPL</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2024,7 +2008,7 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>MANE</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2034,7 +2018,7 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2044,7 +2028,7 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>OFRM</t>
+          <t>MAT</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2054,7 +2038,7 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>OLB</t>
+          <t>MICC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2064,7 +2048,7 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ONC</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2074,7 +2058,7 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>OPLN</t>
+          <t>MMSI</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2084,7 +2068,7 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>MNDY</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2094,7 +2078,7 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -2104,7 +2088,7 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>OTAI</t>
+          <t>MORN</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -2114,7 +2098,7 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>MQ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -2124,7 +2108,7 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2134,7 +2118,7 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>MXCT</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -2144,7 +2128,7 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PAHC</t>
+          <t>MYGN</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -2154,7 +2138,7 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>MZTI</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -2164,7 +2148,7 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>NATH</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -2174,7 +2158,7 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PMTS</t>
+          <t>NAUT</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -2184,7 +2168,7 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PODD</t>
+          <t>NAVN</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -2194,7 +2178,7 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>NCNO</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -2204,7 +2188,7 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -2214,7 +2198,7 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PRME</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -2224,7 +2208,7 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PRVA</t>
+          <t>NECB</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -2234,7 +2218,7 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PSIX</t>
+          <t>NRDS</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -2244,7 +2228,7 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>NTRSO</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -2254,7 +2238,7 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PTLE</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -2264,7 +2248,7 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -2274,7 +2258,7 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -2284,7 +2268,7 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -2294,7 +2278,7 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>RCKY</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -2304,7 +2288,7 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>OCCIM</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -2314,7 +2298,7 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>REF</t>
+          <t>OFS</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -2324,7 +2308,7 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>OMCL</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -2334,7 +2318,7 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>RELY</t>
+          <t>OPRT</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -2344,7 +2328,7 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>RGC</t>
+          <t>ORIC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -2354,7 +2338,7 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>RGCO</t>
+          <t>OSPN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -2364,7 +2348,7 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ROOT</t>
+          <t>OSW</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -2374,7 +2358,7 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ROST</t>
+          <t>OTAI</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -2384,7 +2368,7 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -2394,7 +2378,7 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>OTTR</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -2404,7 +2388,7 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>RTSN</t>
+          <t>OVBC</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -2414,7 +2398,7 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>PAGP</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -2424,7 +2408,7 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>RYZ</t>
+          <t>PAHC</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -2434,7 +2418,7 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -2444,7 +2428,7 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SBAC</t>
+          <t>PBYI</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -2454,7 +2438,7 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SEZL</t>
+          <t>PCRX</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -2464,7 +2448,7 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -2474,7 +2458,7 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -2484,7 +2468,7 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SIGI</t>
+          <t>PGNY</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -2494,7 +2478,7 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SJ</t>
+          <t>PLGO</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -2504,7 +2488,7 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SKIN</t>
+          <t>PLMR</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -2514,7 +2498,7 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>PLUS</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -2524,7 +2508,7 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SLN</t>
+          <t>PMTS</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -2534,7 +2518,7 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>SMPL</t>
+          <t>POWW</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -2544,7 +2528,7 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>SNFCA</t>
+          <t>PRGS</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -2554,7 +2538,7 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>PRTH</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -2564,7 +2548,7 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>PRVA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -2574,7 +2558,7 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SSTI</t>
+          <t>PTEN</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -2584,7 +2568,7 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SUNB</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -2594,7 +2578,7 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SYNA</t>
+          <t>QDEL</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -2604,7 +2588,7 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>TASK</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -2614,7 +2598,7 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>TCRT</t>
+          <t>RCEL</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -2624,7 +2608,7 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -2634,7 +2618,7 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -2644,7 +2628,7 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>ROOT</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -2654,7 +2638,7 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -2664,7 +2648,7 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>RPAY</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -2674,7 +2658,7 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>RPC</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -2684,7 +2668,7 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>UTHR</t>
+          <t>RPD</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -2694,7 +2678,7 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>VYLR</t>
+          <t>RPRX</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -2704,7 +2688,7 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>WLTH</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -2714,7 +2698,7 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>WSBCO</t>
+          <t>RYZ</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -2724,7 +2708,7 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>XZO</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -2734,11 +2718,301 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>YMAT</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr"/>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>SCHL</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr"/>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>SEIC</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr"/>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>SIBN</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr"/>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>SIGI</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr"/>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>SLDE</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr"/>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>SLN</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr"/>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>SMXT</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr"/>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>SPSC</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr"/>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr"/>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>SSNC</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr"/>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>STGW</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr"/>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>STLN</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr"/>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>SYNA</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr"/>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>TASK</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr"/>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>TCPC</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr"/>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>TCRT</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr"/>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>TEAM</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr"/>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>TENB</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr"/>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>TRI</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr"/>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr"/>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>TRXB</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr"/>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr"/>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>UTHR</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr"/>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>VAI</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr"/>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>VSXY</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr"/>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>WLTH</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr"/>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>WTW</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr"/>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>XZO</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr"/>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>YSWY</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D251"/>
+  <dimension ref="A1:D188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,111 +439,175 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>ACGL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CASY</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>AGNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACIW</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ACIC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CSX</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>AMSF</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ACIW</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CASY</t>
-        </is>
-      </c>
-    </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADBE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>ADUS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ENSG</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>BRBR</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADP</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>AGIO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FRPT</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>CHNR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ADSK</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AGYS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GIII</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DPZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AEP</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ANIK</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GPGI</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>FLX</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ADSK</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>GIII</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ADUS</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>GPGI</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ALRM</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AEP</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>APEI</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HONA</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IOTR</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AMCR</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AFYA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>APOG</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>IPAR</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>KLTR</t>
@@ -551,2468 +615,2350 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AMGN</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AGIO</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>ARLP</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>KWY</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LCNB</t>
+          <t>LIF</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AMPL</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AGYS</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>ASBP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ODFL</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LIF</t>
+          <t>MGPI</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ANDG</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ALLT</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>ATLCZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PECO</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>NXGL</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ANGI</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ALRM</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>ATOS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>POOL</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NXGL</t>
+          <t>PODD</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>APPN</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMCR</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>AUPH</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PTEN</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>REYN</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AMGN</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>AZN</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TILE</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OSG</t>
+          <t>SHOE</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ARHS</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PODD</t>
+          <t>STFS</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ASBH</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>BREZ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>TCMD</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ASO</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>REYN</t>
+          <t>TRIB</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ATLCL</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ANIK</t>
+          <t>BSET</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>STFS</t>
+          <t>TRIP</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ATLO</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AOUT</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>TRIP</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AVBC</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>BUUU</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AVPT</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>BVFL</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BANF</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BCAL</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>BYRN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BCML</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ATLO</t>
+          <t>BZUN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BCPC</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BFST</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BIIB</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>CBNK</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BL</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>CBRL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BLKB</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BANF</t>
+          <t>CDZI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BPRN</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BCML</t>
+          <t>CENT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BFST</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BRCB</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BSVN</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BSY</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BVS</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BOW</t>
+          <t>COLM</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CBFV</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BPRN</t>
+          <t>CPIX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CCEP</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CCNE</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>CVSA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CCNEP</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CENTA</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>DGICA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CHCO</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>DHCNL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CHKP</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BVS</t>
+          <t>DIBS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CINF</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CLAR</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>DRDB</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CNXC</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CRAC</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CBNK</t>
+          <t>EPSN</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CRAI</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CSGP</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CCNE</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CTAS</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CENTA</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CVLT</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>EYE</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CWST</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DAKT</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>FIZZ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>FLYW</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>DBX</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>FNKO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>DLTR</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CLAR</t>
+          <t>FNLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>DMAA</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>DOCU</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>FRSH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>DSGR</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>FVN</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>DUKU</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CPIX</t>
+          <t>GABC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ECCU</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>GDRX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>EDHL</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>EFOR</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>EFSI</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>EGBN</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>EMBC</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ENGS</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>HUIZ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>EVCM</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CYRX</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>EVER</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DAVE</t>
+          <t>IIIV</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>EVRG</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>IRON</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>EXC</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>EXLS</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>JVA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DMAC</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>FDBC</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DMLP</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>FERAU</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>KTWO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>FMAO</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>LIVN</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>FORR</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>LMAT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>FRBA</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>FSV</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DUKU</t>
+          <t>MANE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>FTDR</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>GCL</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>MICC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>GDYN</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>GMAB</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>MQ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ENSC</t>
+          <t>NKSH</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>GRDX</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>NSIT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>GTM</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ESLT</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>HAS</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>HBNC</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EVAX</t>
+          <t>OCCIM</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>HCKT</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EVER</t>
+          <t>OFIX</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>HLP</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>OPLN</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>HQY</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>OSW</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>HURN</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>OTAI</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>HWKN</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>OTTR</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>HYNE</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>PAGP</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>IBEX</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>PEGA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ICFI</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FIZZ</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr"/>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ICLR</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>PEPG</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>PGNY</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>INGN</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>FNLC</t>
+          <t>PLUS</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>INTA</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>FSV</t>
+          <t>PPLC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ISRG</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>PRDO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>JAKK</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>PRGS</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>JKHY</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GDRX</t>
+          <t>PTON</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>KDP</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>RGCO</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>KINS</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>ROOT</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr"/>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>KMTS</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>RPC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr"/>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>LCNB</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>RPRX</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>LIN</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>RWAYI</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>LKFT</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>RWAYL</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>LNT</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>HBNC</t>
+          <t>SAMG</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>LOPE</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>SCHL</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>LSBK</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>SIBN</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>LZ</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HQY</t>
+          <t>SOMN</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr"/>
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>MDLZ</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>STGW</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>MKTX</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>STLN</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr"/>
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>MMSI</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>TASK</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>MNDY</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>TBCH</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>MORN</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ICFI</t>
+          <t>TCPC</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>MRSH</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>TCRT</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>MTC</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr"/>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>MWYN</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>TRAD</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>MYGN</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>IIIV</t>
+          <t>TRAX</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr"/>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>MZTI</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>TRXB</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr"/>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>NAVN</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>VAI</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr"/>
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>NCNO</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>WLTH</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>IRMD</t>
-        </is>
-      </c>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>NCPL</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr"/>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>IRON</t>
-        </is>
-      </c>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>NDAQ</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr"/>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>JKHY</t>
-        </is>
-      </c>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>NECB</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr"/>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>JRSH</t>
-        </is>
-      </c>
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>NRDS</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr"/>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>KDP</t>
-        </is>
-      </c>
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>NTSK</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr"/>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>KGEI</t>
-        </is>
-      </c>
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>NTWK</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>KIDS</t>
-        </is>
-      </c>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>NWSA</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>KINS</t>
-        </is>
-      </c>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>OLED</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>KMB</t>
-        </is>
-      </c>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>OMCL</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr"/>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>KRT</t>
-        </is>
-      </c>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ORLY</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr"/>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>LIN</t>
-        </is>
-      </c>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>OSPN</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr"/>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>LIND</t>
-        </is>
-      </c>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>OTEX</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr"/>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>LKFT</t>
-        </is>
-      </c>
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>OVBC</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr"/>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>LMAT</t>
-        </is>
-      </c>
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>PAA</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr"/>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>LNT</t>
-        </is>
-      </c>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>PAHC</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr"/>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>LOPE</t>
-        </is>
-      </c>
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr"/>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>LQDT</t>
-        </is>
-      </c>
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>PBYI</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr"/>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>LZ</t>
-        </is>
-      </c>
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr"/>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>MANE</t>
-        </is>
-      </c>
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr"/>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>MANH</t>
-        </is>
-      </c>
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>PLBC</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr"/>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>MAT</t>
-        </is>
-      </c>
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>PLGO</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr"/>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>MICC</t>
-        </is>
-      </c>
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>PLMR</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr"/>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>MKTX</t>
-        </is>
-      </c>
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>POWW</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr"/>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>MMSI</t>
-        </is>
-      </c>
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>QNBC</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr"/>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>MNDY</t>
-        </is>
-      </c>
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>RCEL</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr"/>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>MNST</t>
-        </is>
-      </c>
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>RCKY</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr"/>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>MORN</t>
-        </is>
-      </c>
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>REF</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr"/>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr"/>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>MRSH</t>
-        </is>
-      </c>
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ROKU</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr"/>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>MXCT</t>
-        </is>
-      </c>
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>ROP</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr"/>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>MYGN</t>
-        </is>
-      </c>
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>RPAY</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr"/>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>MZTI</t>
-        </is>
-      </c>
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>RPD</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr"/>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>NATH</t>
-        </is>
-      </c>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>SAIC</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr"/>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>NAUT</t>
-        </is>
-      </c>
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr"/>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>NAVN</t>
-        </is>
-      </c>
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>SBFG</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr"/>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>NCNO</t>
-        </is>
-      </c>
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>SDHIU</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr"/>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>NCPL</t>
-        </is>
-      </c>
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>SEIC</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr"/>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>NDAQ</t>
-        </is>
-      </c>
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr"/>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>NECB</t>
-        </is>
-      </c>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>SGRY</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr"/>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>NRDS</t>
-        </is>
-      </c>
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>SIGI</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr"/>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>NTRSO</t>
-        </is>
-      </c>
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>SKWD</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr"/>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>NTSK</t>
-        </is>
-      </c>
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>SLDE</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr"/>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>NTWK</t>
-        </is>
-      </c>
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>SMPL</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr"/>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>NWE</t>
-        </is>
-      </c>
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>SPSC</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr"/>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>NWS</t>
-        </is>
-      </c>
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr"/>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>NWSA</t>
-        </is>
-      </c>
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>SSNC</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr"/>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>OCCIM</t>
-        </is>
-      </c>
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>SUNB</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr"/>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>OFS</t>
-        </is>
-      </c>
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>TONT</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr"/>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>OMCL</t>
-        </is>
-      </c>
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>TRI</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr"/>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>OPRT</t>
-        </is>
-      </c>
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr"/>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>ORIC</t>
-        </is>
-      </c>
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>TRS</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr"/>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>OSPN</t>
-        </is>
-      </c>
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr"/>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>OSW</t>
-        </is>
-      </c>
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>UTHR</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr"/>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>OTAI</t>
-        </is>
-      </c>
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>WTW</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr"/>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>OTEX</t>
-        </is>
-      </c>
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>XZO</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr"/>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>OTTR</t>
-        </is>
-      </c>
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>YSWY</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr"/>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>OVBC</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr"/>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>PAGP</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr"/>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>PAHC</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr"/>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>PAYX</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr"/>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>PBYI</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr"/>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>PCRX</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr"/>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>PCTY</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr"/>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr"/>
-      <c r="D196" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr"/>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>PGNY</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr"/>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>PLGO</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr"/>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>PLMR</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr"/>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>PLUS</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr"/>
-      <c r="D200" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr"/>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>PMTS</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr"/>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>POWW</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr"/>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>PRGS</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr"/>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>PRTH</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr"/>
-      <c r="D204" t="inlineStr"/>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr"/>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>PRVA</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr"/>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>PTEN</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr"/>
-      <c r="D206" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr"/>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>PYPL</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr"/>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>QDEL</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr"/>
-      <c r="D208" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr"/>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>QNBC</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr"/>
-      <c r="D209" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr"/>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>RCEL</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr"/>
-      <c r="D210" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr"/>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>REGN</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr"/>
-      <c r="D211" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr"/>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>ROKU</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr"/>
-      <c r="D212" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr"/>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>ROOT</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr"/>
-      <c r="D213" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr"/>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>ROP</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr"/>
-      <c r="D214" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr"/>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>RPAY</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr"/>
-      <c r="D215" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr"/>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>RPC</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr"/>
-      <c r="D216" t="inlineStr"/>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr"/>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>RPD</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr"/>
-      <c r="D217" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr"/>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>RPRX</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr"/>
-      <c r="D218" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr"/>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>RUSHB</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr"/>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>RYZ</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr"/>
-      <c r="D220" t="inlineStr"/>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr"/>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>SAIC</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr"/>
-      <c r="D221" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr"/>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>SBUX</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr"/>
-      <c r="D222" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr"/>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>SCHL</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr"/>
-      <c r="D223" t="inlineStr"/>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr"/>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>SEIC</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr"/>
-      <c r="D224" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr"/>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>SIBN</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr"/>
-      <c r="D225" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr"/>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>SIGI</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr"/>
-      <c r="D226" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr"/>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>SLDE</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr"/>
-      <c r="D227" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr"/>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>SLN</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr"/>
-      <c r="D228" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr"/>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>SMXT</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr"/>
-      <c r="D229" t="inlineStr"/>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr"/>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>SPSC</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr"/>
-      <c r="D230" t="inlineStr"/>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr"/>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>SPT</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr"/>
-      <c r="D231" t="inlineStr"/>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr"/>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>SSNC</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr"/>
-      <c r="D232" t="inlineStr"/>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr"/>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>STGW</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr"/>
-      <c r="D233" t="inlineStr"/>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr"/>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>STLN</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr"/>
-      <c r="D234" t="inlineStr"/>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr"/>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>SYNA</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr"/>
-      <c r="D235" t="inlineStr"/>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr"/>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>TASK</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr"/>
-      <c r="D236" t="inlineStr"/>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr"/>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>TCPC</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr"/>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr"/>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>TCRT</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr"/>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr"/>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>TEAM</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" t="inlineStr"/>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr"/>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>TENB</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr"/>
-      <c r="D240" t="inlineStr"/>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr"/>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>TRI</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr"/>
-      <c r="D241" t="inlineStr"/>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr"/>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>TRMB</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr"/>
-      <c r="D242" t="inlineStr"/>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr"/>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>TRXB</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr"/>
-      <c r="D243" t="inlineStr"/>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr"/>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr"/>
-      <c r="D244" t="inlineStr"/>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr"/>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>UTHR</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr"/>
-      <c r="D245" t="inlineStr"/>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr"/>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>VAI</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr"/>
-      <c r="D246" t="inlineStr"/>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr"/>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>VSXY</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr"/>
-      <c r="D247" t="inlineStr"/>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr"/>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>WLTH</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr"/>
-      <c r="D248" t="inlineStr"/>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr"/>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>WTW</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr"/>
-      <c r="D249" t="inlineStr"/>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr"/>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>XZO</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr"/>
-      <c r="D250" t="inlineStr"/>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr"/>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>YSWY</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr"/>
-      <c r="D251" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D188"/>
+  <dimension ref="A1:D127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,100 +441,100 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>AGBK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ACGL</t>
+          <t>ABLV</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CASY</t>
+          <t>BHST</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AGNT</t>
+          <t>AQB</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>AGYS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>ADAMI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>BVC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AMSF</t>
+          <t>ASR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>AIIR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADUS</t>
+          <t>ADMA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ENSG</t>
+          <t>COCO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BRBR</t>
+          <t>CELH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>AIXI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>AFYA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FRPT</t>
+          <t>EJH</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CHNR</t>
+          <t>LFS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AGYS</t>
+          <t>AHG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -544,41 +544,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DPZ</t>
+          <t>NXPI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ANIK</t>
+          <t>AMRO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>GRFS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FLX</t>
+          <t>OSG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>ANIK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -588,107 +588,107 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>PLBY</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>ATLCZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IPAR</t>
+          <t>KWY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KLTR</t>
+          <t>PODD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ARLP</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KWY</t>
+          <t>MIDD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LIF</t>
+          <t>PTEN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>ARHS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ASBP</t>
+          <t>AVTR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>PECO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>RGC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>ARLP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ATLCZ</t>
+          <t>BETR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>PEPG</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NXGL</t>
+          <t>SOLS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>ARX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ATOS</t>
+          <t>BMBL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -698,135 +698,107 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PODD</t>
+          <t>TCMD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>AVBC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PTEN</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>REYN</t>
-        </is>
-      </c>
+          <t>SBAC</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BCPC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AZN</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>TILE</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>SHOE</t>
-        </is>
-      </c>
+          <t>BVFL</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>BDCI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BOW</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>STFS</t>
-        </is>
-      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ASBH</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BREZ</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>TCMD</t>
-        </is>
-      </c>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>BOLT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>CASY</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>TRIB</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ATLCL</t>
+          <t>BOTJ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>TRIP</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ATLO</t>
+          <t>BPRN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>CBRL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -835,12 +807,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AVBC</t>
+          <t>BRBI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BUUU</t>
+          <t>CDZI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -849,12 +821,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>BRCB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BVFL</t>
+          <t>CENT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -863,12 +835,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BANF</t>
+          <t>BSET</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -877,12 +849,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCAL</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -891,12 +863,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCML</t>
+          <t>BUUU</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>CHAD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -905,12 +877,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCPC</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>COFS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -919,12 +891,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BFST</t>
+          <t>CBFV</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>CPIX</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -933,12 +905,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>CBNK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CBNK</t>
+          <t>CWST</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -947,12 +919,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>CCNE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -961,12 +933,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CDZI</t>
+          <t>DIBS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -975,12 +947,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BPRN</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CENT</t>
+          <t>DMAC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -989,12 +961,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -1003,12 +975,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>CENTA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>DRDB</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -1017,12 +989,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -1031,12 +1003,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1045,12 +1017,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BVS</t>
+          <t>CHRD</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>COLM</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1059,12 +1031,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CBFV</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CPIX</t>
+          <t>ENTX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1073,12 +1045,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -1087,12 +1059,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CCNE</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -1101,12 +1073,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CCNEP</t>
+          <t>CVSA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -1115,12 +1087,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>CZFS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>FNLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1129,12 +1101,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CENTA</t>
+          <t>CZNC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DGICA</t>
+          <t>FRSH</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -1143,12 +1115,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CHCO</t>
+          <t>DAKT</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DHCNL</t>
+          <t>FUNC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1157,12 +1129,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DIBS</t>
+          <t>GAING</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1171,12 +1143,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>DCOM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>GAINI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1185,12 +1157,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CLAR</t>
+          <t>DHCNL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DRDB</t>
+          <t>GAINZ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1199,12 +1171,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>EDHL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1213,12 +1185,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1227,12 +1199,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CRAC</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EPSN</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1241,12 +1213,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1255,12 +1227,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>EPSN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1269,12 +1241,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>ERIC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1283,12 +1255,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>HEPS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1297,12 +1269,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>FCNCA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EYE</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1311,12 +1283,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CWST</t>
+          <t>FDBC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>HOWL</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1325,12 +1297,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DAKT</t>
+          <t>FLYW</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FIZZ</t>
+          <t>HPK</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1339,12 +1311,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DAVE</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>HUIZ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1353,12 +1325,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>FORR</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>ICG</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1367,12 +1339,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>FRBA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FNLC</t>
+          <t>INGN</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1381,12 +1353,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DMAA</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>IOSP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1395,12 +1367,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1409,12 +1381,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>GLBE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FVN</t>
+          <t>IPXG</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1423,12 +1395,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DUKU</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GABC</t>
+          <t>IRON</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1437,12 +1409,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ECCU</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GDRX</t>
+          <t>JCSE</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1451,12 +1423,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>HBNC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>JOYY</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1465,12 +1437,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>HCSG</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>JYD</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1479,12 +1451,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>KMTS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1493,12 +1465,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>HQY</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1507,12 +1479,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1521,12 +1493,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>HTFL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HUIZ</t>
+          <t>MANE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1535,12 +1507,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EVCM</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1549,12 +1521,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EVER</t>
+          <t>HYNE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IIIV</t>
+          <t>MAZE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1563,12 +1535,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>MBRX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1577,12 +1549,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1591,12 +1563,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JVA</t>
+          <t>MMTX</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1605,12 +1577,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1619,12 +1591,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FDBC</t>
+          <t>INTR</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1633,12 +1605,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FERAU</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>KTWO</t>
+          <t>MYGN</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1647,12 +1619,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LIVN</t>
+          <t>NAVN</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1661,12 +1633,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FORR</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LMAT</t>
+          <t>NPAC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1675,12 +1647,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>NRIX</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1689,12 +1661,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FRBA</t>
+          <t>LCNB</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>NWFL</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1703,12 +1675,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FSV</t>
+          <t>LGND</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>ONBPP</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1717,12 +1689,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>ONC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1731,12 +1703,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>MGYR</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MICC</t>
+          <t>OTAI</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1745,12 +1717,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>OTLY</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1759,12 +1731,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>MORN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>OXLCZ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1773,12 +1745,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MWYN</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NKSH</t>
+          <t>PAX</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1787,12 +1759,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>NATH</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>PCRX</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1801,12 +1773,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>NAUT</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>PICS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1815,12 +1787,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>NBTB</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>PMTS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1829,12 +1801,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HBNC</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>OCCIM</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1843,12 +1815,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>OFIX</t>
+          <t>PRGS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1857,12 +1829,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>NSIT</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>OPLN</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1871,12 +1843,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>HQY</t>
+          <t>NSSC</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>OSW</t>
+          <t>PTLE</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -1885,12 +1857,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>NTRSO</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>OTAI</t>
+          <t>RCEL</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -1899,12 +1871,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>HWKN</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>OTTR</t>
+          <t>REBN</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1913,12 +1885,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>HYNE</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>RELY</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -1927,12 +1899,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>REVB</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -1941,12 +1913,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ICFI</t>
+          <t>OABI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>RIGL</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1955,12 +1927,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>OCTV</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PEPG</t>
+          <t>RVSB</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1969,12 +1941,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>OMCL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PGNY</t>
+          <t>RWAYI</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1983,12 +1955,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>ORIC</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1997,12 +1969,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>OSPN</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -2011,12 +1983,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PPLC</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -2025,12 +1997,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>OVBC</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PRDO</t>
+          <t>SKYA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -2039,12 +2011,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2053,12 +2025,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>PAGP</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PTON</t>
+          <t>TBCH</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2067,12 +2039,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>POWW</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2081,12 +2053,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>KIDS</t>
+          <t>PRDO</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RGCO</t>
+          <t>TRAX</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2095,12 +2067,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>KINS</t>
+          <t>PRME</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ROOT</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2109,12 +2081,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>KMTS</t>
+          <t>PSIG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>UTHR</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2123,12 +2095,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>LCNB</t>
+          <t>QLYS</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>VSXY</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2137,12 +2109,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RWAYI</t>
+          <t>YSWY</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2151,814 +2123,132 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>LKFT</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>RWAYL</t>
-        </is>
-      </c>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>LNT</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>SAMG</t>
-        </is>
-      </c>
+          <t>REF</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>LOGI</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>SBUX</t>
-        </is>
-      </c>
+          <t>ROP</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>LOPE</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>SCHL</t>
-        </is>
-      </c>
+          <t>RPAY</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>LSBK</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>SIBN</t>
-        </is>
-      </c>
+          <t>RPD</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>LZ</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>SOMN</t>
-        </is>
-      </c>
+          <t>RPRX</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MDLZ</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>STGW</t>
-        </is>
-      </c>
+          <t>SBFG</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MKTX</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>STLN</t>
-        </is>
-      </c>
+          <t>SIGI</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MMSI</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>TASK</t>
-        </is>
-      </c>
+          <t>SLDE</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MNDY</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>TBCH</t>
-        </is>
-      </c>
+          <t>SWKHL</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MORN</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>TCPC</t>
-        </is>
-      </c>
+          <t>TACO</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MRSH</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>TCRT</t>
-        </is>
-      </c>
+          <t>TENB</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MTC</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>TENB</t>
-        </is>
-      </c>
+          <t>TLS</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>MWYN</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>TRAD</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>MYGN</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>TRAX</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>MZTI</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>TRXB</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>NAVN</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>VAI</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>NCNO</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>WLTH</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>NCPL</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>NDAQ</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>NECB</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>NRDS</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>NTSK</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>NTWK</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>NWSA</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>OMCL</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>ORLY</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>OSPN</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>OTEX</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>OVBC</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
-      <c r="C145" t="inlineStr"/>
-      <c r="D145" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>PAA</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>PAHC</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>PAYX</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>PBYI</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
-      <c r="C149" t="inlineStr"/>
-      <c r="D149" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>PCB</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
-      <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>PCTY</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr"/>
-      <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>PLBC</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr"/>
-      <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>PLGO</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr"/>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>PLMR</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr"/>
-      <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>POWW</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr"/>
-      <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>QNBC</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr"/>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>RCEL</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr"/>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>RCKY</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr"/>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>REF</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr"/>
-      <c r="C159" t="inlineStr"/>
-      <c r="D159" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>REGN</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr"/>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>ROKU</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr"/>
-      <c r="C161" t="inlineStr"/>
-      <c r="D161" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>ROP</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr"/>
-      <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>RPAY</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr"/>
-      <c r="C163" t="inlineStr"/>
-      <c r="D163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>RPD</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr"/>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>SAIC</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr"/>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>SBC</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr"/>
-      <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>SBFG</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr"/>
-      <c r="C167" t="inlineStr"/>
-      <c r="D167" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>SDHIU</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr"/>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>SEIC</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr"/>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>SEZL</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr"/>
-      <c r="C170" t="inlineStr"/>
-      <c r="D170" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>SGRY</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr"/>
-      <c r="C171" t="inlineStr"/>
-      <c r="D171" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>SIGI</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr"/>
-      <c r="C172" t="inlineStr"/>
-      <c r="D172" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>SKWD</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr"/>
-      <c r="C173" t="inlineStr"/>
-      <c r="D173" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>SLDE</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr"/>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>SMPL</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr"/>
-      <c r="C175" t="inlineStr"/>
-      <c r="D175" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>SPSC</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr"/>
-      <c r="C176" t="inlineStr"/>
-      <c r="D176" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>SPT</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr"/>
-      <c r="C177" t="inlineStr"/>
-      <c r="D177" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>SSNC</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr"/>
-      <c r="C178" t="inlineStr"/>
-      <c r="D178" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>SUNB</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr"/>
-      <c r="C179" t="inlineStr"/>
-      <c r="D179" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>TONT</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr"/>
-      <c r="C180" t="inlineStr"/>
-      <c r="D180" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>TRI</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr"/>
-      <c r="C181" t="inlineStr"/>
-      <c r="D181" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>TRMB</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr"/>
-      <c r="C182" t="inlineStr"/>
-      <c r="D182" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>TRS</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr"/>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr"/>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>UTHR</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr"/>
-      <c r="C185" t="inlineStr"/>
-      <c r="D185" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>WTW</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr"/>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>XZO</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr"/>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>YSWY</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr"/>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D127"/>
+  <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,7 +863,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BUUU</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>CBFV</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -891,7 +891,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CBFV</t>
+          <t>CBNK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -905,7 +905,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CBNK</t>
+          <t>CCNE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -919,7 +919,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CCNE</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -933,7 +933,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>CENTA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -975,7 +975,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CENTA</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -989,7 +989,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>CHRD</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1017,7 +1017,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CHRD</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1031,7 +1031,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1059,7 +1059,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>CVSA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1073,7 +1073,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>CZFS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1087,7 +1087,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CZFS</t>
+          <t>CZNC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CZNC</t>
+          <t>DAKT</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1115,7 +1115,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DAKT</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1129,7 +1129,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>DCOM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DCOM</t>
+          <t>DHCNL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1157,7 +1157,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DHCNL</t>
+          <t>EDHL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1185,7 +1185,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1199,7 +1199,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1213,7 +1213,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>EPSN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1227,7 +1227,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EPSN</t>
+          <t>ERIC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ERIC</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1255,7 +1255,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>FCNCA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1269,7 +1269,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FCNCA</t>
+          <t>FDBC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FDBC</t>
+          <t>FLYW</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1297,7 +1297,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1311,7 +1311,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>FORR</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1325,7 +1325,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FORR</t>
+          <t>FRBA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FRBA</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1353,7 +1353,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>GLBE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GLBE</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1409,7 +1409,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>HBNC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1423,7 +1423,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HBNC</t>
+          <t>HCSG</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1437,7 +1437,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HCSG</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1451,7 +1451,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>HQY</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1465,7 +1465,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HQY</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1479,7 +1479,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>HTFL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1493,7 +1493,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1507,7 +1507,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>HYNE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>HYNE</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1535,7 +1535,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1549,7 +1549,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ICFI</t>
+          <t>III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1563,7 +1563,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>INTR</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1591,7 +1591,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1605,7 +1605,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1633,7 +1633,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1647,7 +1647,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>LCNB</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>LCNB</t>
+          <t>LGND</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1675,7 +1675,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1689,7 +1689,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>MGYR</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1703,7 +1703,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MGYR</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>MORN</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1731,7 +1731,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>MWYN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>NATH</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>NAUT</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1773,7 +1773,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>NBTB</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1787,7 +1787,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NBTB</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NICE</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1815,7 +1815,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>NSIT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1829,7 +1829,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>NSSC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1843,7 +1843,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>NSSC</t>
+          <t>NTRSO</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>NTRSO</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1871,7 +1871,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1885,7 +1885,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>OABI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1913,7 +1913,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>OABI</t>
+          <t>OCTV</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1927,7 +1927,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>OMCL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>OMCL</t>
+          <t>ORIC</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1955,7 +1955,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ORIC</t>
+          <t>OSPN</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -1969,7 +1969,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -1983,7 +1983,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>OVBC</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -1997,7 +1997,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>OVBC</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2011,7 +2011,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>PAGP</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2025,7 +2025,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>POWW</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2039,7 +2039,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>POWW</t>
+          <t>PRDO</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2053,7 +2053,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PRDO</t>
+          <t>PRME</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2067,7 +2067,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PRME</t>
+          <t>PSIG</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2081,7 +2081,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PSIG</t>
+          <t>QLYS</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2095,7 +2095,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2109,7 +2109,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>REF</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -2133,7 +2133,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>REF</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -2143,7 +2143,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>RPAY</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -2153,7 +2153,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RPAY</t>
+          <t>RPD</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -2163,7 +2163,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>RPRX</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -2173,7 +2173,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>SBFG</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -2183,7 +2183,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SBFG</t>
+          <t>SIGI</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SIGI</t>
+          <t>SLDE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -2203,7 +2203,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>SWKHL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -2213,7 +2213,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -2223,7 +2223,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -2233,22 +2233,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>TLS</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>TLS</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D304"/>
+  <dimension ref="A1:D235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,94 +441,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRLT</t>
+          <t>AEYE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ABLV</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>RENT</t>
-        </is>
-      </c>
+          <t>ACT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ALKS</t>
+          <t>ALGN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FNWD</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ACNB</t>
+          <t>ACU</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AQB</t>
+          <t>AMSF</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FORTY</t>
+          <t>JCSE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADAMI</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ARXS</t>
+          <t>BGSI</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SGRY</t>
+          <t>KELYB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BDTX</t>
+          <t>BMGL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XNCR</t>
+          <t>POM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BHST</t>
+          <t>CARR</t>
         </is>
       </c>
     </row>
@@ -536,13 +532,13 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADUS</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BVC</t>
+          <t>CASH</t>
         </is>
       </c>
     </row>
@@ -550,13 +546,13 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>ALLT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CLBT</t>
+          <t>CCB</t>
         </is>
       </c>
     </row>
@@ -564,7 +560,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>AMAL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -578,13 +574,13 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DORM</t>
+          <t>DHCNI</t>
         </is>
       </c>
     </row>
@@ -592,13 +588,13 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AGYS</t>
+          <t>AMRO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FELE</t>
+          <t>EJH</t>
         </is>
       </c>
     </row>
@@ -606,13 +602,13 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AISP</t>
+          <t>AMRX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FLX</t>
+          <t>ELUT</t>
         </is>
       </c>
     </row>
@@ -620,13 +616,13 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ALGN</t>
+          <t>ANIK</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GRFS</t>
+          <t>FLX</t>
         </is>
       </c>
     </row>
@@ -634,13 +630,13 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ALLT</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HLMN</t>
+          <t>IMCR</t>
         </is>
       </c>
     </row>
@@ -648,13 +644,13 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>ARHS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HONA</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
@@ -662,13 +658,13 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AMAL</t>
+          <t>ARLP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HTZ</t>
+          <t>KLRA</t>
         </is>
       </c>
     </row>
@@ -676,13 +672,13 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>ARQT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KLRA</t>
+          <t>LIF</t>
         </is>
       </c>
     </row>
@@ -690,13 +686,13 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AMRO</t>
+          <t>ARXS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>KXIN</t>
+          <t>NXPI</t>
         </is>
       </c>
     </row>
@@ -704,13 +700,13 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>ASTL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LIF</t>
+          <t>NYAX</t>
         </is>
       </c>
     </row>
@@ -718,13 +714,13 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AMSF</t>
+          <t>ATLCL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>OIO</t>
         </is>
       </c>
     </row>
@@ -732,13 +728,13 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>AUDC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NYAX</t>
+          <t>OKYO</t>
         </is>
       </c>
     </row>
@@ -746,13 +742,13 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>AUPH</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>OMH</t>
+          <t>OSW</t>
         </is>
       </c>
     </row>
@@ -760,13 +756,13 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>OSG</t>
+          <t>PWRL</t>
         </is>
       </c>
     </row>
@@ -774,13 +770,13 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ARLP</t>
+          <t>AVBH</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>OSW</t>
+          <t>RSVR</t>
         </is>
       </c>
     </row>
@@ -788,13 +784,13 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ARX</t>
+          <t>BANR</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>SOLS</t>
         </is>
       </c>
     </row>
@@ -802,13 +798,13 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>BCAL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PMA</t>
+          <t>STAA</t>
         </is>
       </c>
     </row>
@@ -816,13 +812,13 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ASST</t>
+          <t>BETR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PSMT</t>
+          <t>TCBK</t>
         </is>
       </c>
     </row>
@@ -830,13 +826,13 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PTEN</t>
+          <t>TREE</t>
         </is>
       </c>
     </row>
@@ -844,13 +840,13 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PWRL</t>
+          <t>VMRK</t>
         </is>
       </c>
     </row>
@@ -858,91 +854,67 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>BOTJ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>SBAC</t>
-        </is>
-      </c>
+      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AVBC</t>
+          <t>BPRN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>SNWV</t>
-        </is>
-      </c>
+      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>BRCB</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>SOLS</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BBSI</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>STAA</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BCAL</t>
+          <t>BSET</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TNGX</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BCPC</t>
+          <t>BSIN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>TREE</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BOLT</t>
+          <t>BSRR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -952,7 +924,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BOTJ</t>
+          <t>BSVN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -962,7 +934,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BOW</t>
+          <t>BUSE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -972,7 +944,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BPRN</t>
+          <t>BVC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -982,7 +954,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>BVS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -992,7 +964,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BSIN</t>
+          <t>BWFG</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1002,7 +974,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BSRR</t>
+          <t>BWMN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -1012,7 +984,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>CASS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1022,7 +994,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BUSE</t>
+          <t>CATY</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1032,7 +1004,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BVS</t>
+          <t>CCID</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1042,7 +1014,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BWFG</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1052,7 +1024,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1062,7 +1034,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1072,7 +1044,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1082,7 +1054,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CAC</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1092,7 +1064,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1102,7 +1074,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CAPS</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1112,7 +1084,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CATY</t>
+          <t>CNXC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1122,7 +1094,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>CRSR</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1132,7 +1104,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CBNK</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1142,7 +1114,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CBU</t>
+          <t>CTKB</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1152,7 +1124,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CCBG</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1162,7 +1134,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CCNE</t>
+          <t>CVBF</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1172,7 +1144,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1182,7 +1154,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>CYRX</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1192,7 +1164,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>CZFS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1202,7 +1174,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CENT</t>
+          <t>DAKT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1212,7 +1184,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CENTA</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1222,7 +1194,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1232,7 +1204,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1242,7 +1214,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>DMRC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1252,7 +1224,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1262,7 +1234,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1272,7 +1244,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CHCO</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1282,7 +1254,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1292,7 +1264,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CIVB</t>
+          <t>ERIC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1302,7 +1274,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1312,7 +1284,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CNOB</t>
+          <t>EWBC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1322,7 +1294,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1332,7 +1304,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>COFS</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1342,7 +1314,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>EXYN</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1352,7 +1324,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>FBIZ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1362,7 +1334,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CRSR</t>
+          <t>FCBM</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1372,7 +1344,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>FCNCA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1382,7 +1354,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>FFBC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1392,7 +1364,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1402,7 +1374,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1412,7 +1384,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>FMBH</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1422,7 +1394,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CZFS</t>
+          <t>FNKO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1432,7 +1404,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CZNC</t>
+          <t>FRME</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1442,7 +1414,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DAKT</t>
+          <t>FSSL</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1452,7 +1424,7 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>FTDR</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1462,7 +1434,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DCOM</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1472,7 +1444,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DIBS</t>
+          <t>FUNC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1482,7 +1454,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>FVNNU</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1492,7 +1464,7 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DMAC</t>
+          <t>GAINI</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1502,7 +1474,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DMLP</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1512,7 +1484,7 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>GDRX</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1522,7 +1494,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1532,7 +1504,7 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -1542,7 +1514,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EBC</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -1552,7 +1524,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>GRFS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1562,7 +1534,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ELMT</t>
+          <t>GSBC</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -1572,7 +1544,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -1582,7 +1554,7 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ENSG</t>
+          <t>HAFC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1592,7 +1564,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ENTX</t>
+          <t>HBT</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1602,7 +1574,7 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ERIC</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1612,7 +1584,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ESLA</t>
+          <t>HCSG</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1622,7 +1594,7 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ESLT</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -1632,7 +1604,7 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -1642,7 +1614,7 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EVCM</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -1652,7 +1624,7 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>HQY</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -1662,7 +1634,7 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>HTFL</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -1672,7 +1644,7 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>HWBK</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -1682,7 +1654,7 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>HWKN</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -1692,7 +1664,7 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EXYN</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -1702,7 +1674,7 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>FBIZ</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -1712,7 +1684,7 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>FCBC</t>
+          <t>III</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -1722,7 +1694,7 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FCNCA</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -1732,7 +1704,7 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>FDBC</t>
+          <t>IMC</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -1742,7 +1714,7 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>FFBC</t>
+          <t>IMKTA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -1752,7 +1724,7 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FISI</t>
+          <t>INDB</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -1762,7 +1734,7 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -1772,7 +1744,7 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -1782,7 +1754,7 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>IOSP</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -1792,7 +1764,7 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>FMBH</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -1802,7 +1774,7 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>FMNB</t>
+          <t>IRON</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -1812,7 +1784,7 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>JBDI</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -1822,7 +1794,7 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>FNLC</t>
+          <t>JOUT</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -1832,7 +1804,7 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>FRAF</t>
+          <t>JYD</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -1842,7 +1814,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FRBA</t>
+          <t>KELYA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -1852,7 +1824,7 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>FSSL</t>
+          <t>KIDS</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -1862,7 +1834,7 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>KINS</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -1872,7 +1844,7 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>FUNC</t>
+          <t>KMRK</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -1882,7 +1854,7 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>GABC</t>
+          <t>KMTS</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -1892,7 +1864,7 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>GAING</t>
+          <t>KPLT</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -1902,7 +1874,7 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>GAINI</t>
+          <t>KRNT</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -1912,7 +1884,7 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>GAINZ</t>
+          <t>KRRO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -1922,7 +1894,7 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>LCNB</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -1932,7 +1904,7 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>LGND</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -1942,7 +1914,7 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -1952,7 +1924,7 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>LMAT</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -1962,7 +1934,7 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -1972,7 +1944,7 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>LOGI</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -1982,7 +1954,7 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -1992,7 +1964,7 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>GLBE</t>
+          <t>LSBK</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -2002,7 +1974,7 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -2012,7 +1984,7 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MAZE</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -2022,7 +1994,7 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>MBWM</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -2032,7 +2004,7 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>MGRC</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -2042,7 +2014,7 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>HAFC</t>
+          <t>MIDD</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2052,7 +2024,7 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>MLKN</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2062,7 +2034,7 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>MOBI</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2072,7 +2044,7 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>HBNC</t>
+          <t>MQ</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2082,7 +2054,7 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>MTC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2092,7 +2064,7 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>HIFS</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2102,7 +2074,7 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>MXCT</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2112,7 +2084,7 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>MYGN</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2122,7 +2094,7 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>NBBK</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2132,7 +2104,7 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>NBTB</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2142,7 +2114,7 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>NECB</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2152,7 +2124,7 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>NMFCZ</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2162,7 +2134,7 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>HWKN</t>
+          <t>NRIX</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -2172,7 +2144,7 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>HYNE</t>
+          <t>NSSC</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -2182,7 +2154,7 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>NTRSO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -2192,7 +2164,7 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>IBCP</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2202,7 +2174,7 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -2212,7 +2184,7 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ICFI</t>
+          <t>NWFL</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -2222,7 +2194,7 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>OBT</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -2232,7 +2204,7 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>OFIX</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -2242,7 +2214,7 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -2252,7 +2224,7 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>OPRT</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -2262,7 +2234,7 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>INDB</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -2272,7 +2244,7 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>INDP</t>
+          <t>OTAI</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -2282,7 +2254,7 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -2292,7 +2264,7 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>OVBC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -2302,7 +2274,7 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>IRLA</t>
+          <t>PBYI</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -2312,7 +2284,7 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>PDLB</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -2322,7 +2294,7 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>IRTC</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -2332,7 +2304,7 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>PFIS</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -2342,7 +2314,7 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>PFXNZ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -2352,7 +2324,7 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JCAP</t>
+          <t>PHAR</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -2362,7 +2334,7 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JCSE</t>
+          <t>PLGO</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -2372,7 +2344,7 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>PLUS</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -2382,7 +2354,7 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JMSB</t>
+          <t>PNFP</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -2392,7 +2364,7 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -2402,7 +2374,7 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -2412,7 +2384,7 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>KIDS</t>
+          <t>PRGS</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -2422,7 +2394,7 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>KMTS</t>
+          <t>PRME</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -2432,7 +2404,7 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>QCRH</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -2442,7 +2414,7 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>LCNB</t>
+          <t>QSI</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -2452,7 +2424,7 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>LFCR</t>
+          <t>RBB</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -2462,7 +2434,7 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>LFST</t>
+          <t>RCBC</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -2472,7 +2444,7 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>RCEL</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -2482,7 +2454,7 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>RDWR</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -2492,7 +2464,7 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -2502,7 +2474,7 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>LMRI</t>
+          <t>RGS</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -2512,7 +2484,7 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>RILYG</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -2522,7 +2494,7 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -2532,7 +2504,7 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>RPAY</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -2542,7 +2514,7 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>RPC</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -2552,7 +2524,7 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>MBRX</t>
+          <t>RPRX</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -2562,7 +2534,7 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>MCBS</t>
+          <t>RRBI</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -2572,7 +2544,7 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>RVSB</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -2582,7 +2554,7 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>RYZ</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -2592,7 +2564,7 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>MGRC</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -2602,7 +2574,7 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>MITK</t>
+          <t>SAGT</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -2612,7 +2584,7 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -2622,7 +2594,7 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>MMSI</t>
+          <t>SBFG</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -2632,7 +2604,7 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>SCHL</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -2642,7 +2614,7 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>MTC</t>
+          <t>SEZL</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -2652,7 +2624,7 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>MTEX</t>
+          <t>SFNC</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -2662,7 +2634,7 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>SGP</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -2672,7 +2644,7 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>MXCT</t>
+          <t>SIBN</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -2682,7 +2654,7 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>SNFCA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -2692,7 +2664,7 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>NBTB</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -2702,7 +2674,7 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>NCNO</t>
+          <t>SPT</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -2712,7 +2684,7 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>SRCE</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -2722,7 +2694,7 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>NICE</t>
+          <t>STBA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -2732,7 +2704,7 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>STRC</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -2742,7 +2714,7 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>NSSC</t>
+          <t>SUNB</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -2752,7 +2724,7 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>SWIM</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -2762,7 +2734,7 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>NTRSO</t>
+          <t>SYNA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -2772,7 +2744,7 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>SYRE</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -2782,7 +2754,7 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>NWBI</t>
+          <t>TACT</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -2792,7 +2764,7 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>TASK</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -2802,7 +2774,7 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>NWFL</t>
+          <t>TCX</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -2812,7 +2784,7 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>THFF</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -2822,7 +2794,7 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -2832,7 +2804,7 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>ONC</t>
+          <t>TOP</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -2842,7 +2814,7 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -2852,7 +2824,7 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>TRAX</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -2862,7 +2834,7 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>ORRF</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -2872,7 +2844,7 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -2882,7 +2854,7 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>OYSE</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -2892,7 +2864,7 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>TROO</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -2902,7 +2874,7 @@
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>TRS</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -2912,7 +2884,7 @@
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PBFS</t>
+          <t>WCCB</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -2922,7 +2894,7 @@
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>WLTH</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -2932,701 +2904,11 @@
       <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PCRX</t>
+          <t>XNCR</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr"/>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr"/>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>PEGA</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr"/>
-      <c r="D236" t="inlineStr"/>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr"/>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>PFBC</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr"/>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr"/>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>PLBC</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr"/>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr"/>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" t="inlineStr"/>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr"/>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>PLUS</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr"/>
-      <c r="D240" t="inlineStr"/>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr"/>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>PMTS</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr"/>
-      <c r="D241" t="inlineStr"/>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr"/>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>PNFP</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr"/>
-      <c r="D242" t="inlineStr"/>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr"/>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>PNTG</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr"/>
-      <c r="D243" t="inlineStr"/>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr"/>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>POM</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr"/>
-      <c r="D244" t="inlineStr"/>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr"/>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>POWW</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr"/>
-      <c r="D245" t="inlineStr"/>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr"/>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>PRCH</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr"/>
-      <c r="D246" t="inlineStr"/>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr"/>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>PRGS</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr"/>
-      <c r="D247" t="inlineStr"/>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr"/>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>PYPL</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr"/>
-      <c r="D248" t="inlineStr"/>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr"/>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>QCRH</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr"/>
-      <c r="D249" t="inlineStr"/>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr"/>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>QDEL</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr"/>
-      <c r="D250" t="inlineStr"/>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr"/>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>QLYS</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr"/>
-      <c r="D251" t="inlineStr"/>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr"/>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>QNBC</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr"/>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>RCBC</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr"/>
-      <c r="D253" t="inlineStr"/>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr"/>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>REF</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr"/>
-      <c r="D254" t="inlineStr"/>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr"/>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>RELY</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr"/>
-      <c r="D255" t="inlineStr"/>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr"/>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>RGS</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr"/>
-      <c r="D256" t="inlineStr"/>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr"/>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>RIGL</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr"/>
-      <c r="D257" t="inlineStr"/>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr"/>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>ROKU</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr"/>
-      <c r="D258" t="inlineStr"/>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr"/>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>ROP</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr"/>
-      <c r="D259" t="inlineStr"/>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr"/>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>RPD</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr"/>
-      <c r="D260" t="inlineStr"/>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr"/>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>RPRX</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr"/>
-      <c r="D261" t="inlineStr"/>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr"/>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>RUSHB</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr"/>
-      <c r="D262" t="inlineStr"/>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr"/>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>RVSB</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr"/>
-      <c r="D263" t="inlineStr"/>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr"/>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>RYZ</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr"/>
-      <c r="D264" t="inlineStr"/>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr"/>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>SAIC</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr"/>
-      <c r="D265" t="inlineStr"/>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr"/>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>SBCF</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr"/>
-      <c r="D266" t="inlineStr"/>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr"/>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>SBFG</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr"/>
-      <c r="D267" t="inlineStr"/>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr"/>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>SBUX</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr"/>
-      <c r="D268" t="inlineStr"/>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr"/>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>SCSC</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr"/>
-      <c r="D269" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr"/>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>SEPN</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr"/>
-      <c r="D270" t="inlineStr"/>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr"/>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>SEZL</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr"/>
-      <c r="D271" t="inlineStr"/>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr"/>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>SFNC</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr"/>
-      <c r="D272" t="inlineStr"/>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr"/>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>SGP</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr"/>
-      <c r="D273" t="inlineStr"/>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr"/>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>SIBN</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr"/>
-      <c r="D274" t="inlineStr"/>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr"/>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>SIGI</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr"/>
-      <c r="D275" t="inlineStr"/>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr"/>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>SKYA</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr"/>
-      <c r="D276" t="inlineStr"/>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr"/>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>SLDE</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr"/>
-      <c r="D277" t="inlineStr"/>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr"/>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>SLN</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr"/>
-      <c r="D278" t="inlineStr"/>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr"/>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>SONO</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr"/>
-      <c r="D279" t="inlineStr"/>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr"/>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>SPT</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr"/>
-      <c r="D280" t="inlineStr"/>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr"/>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>SRCE</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr"/>
-      <c r="D281" t="inlineStr"/>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr"/>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>SSNC</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr"/>
-      <c r="D282" t="inlineStr"/>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr"/>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>STBA</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr"/>
-      <c r="D283" t="inlineStr"/>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr"/>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>STLD</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr"/>
-      <c r="D284" t="inlineStr"/>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr"/>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>STLN</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr"/>
-      <c r="D285" t="inlineStr"/>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr"/>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>SUNB</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr"/>
-      <c r="D286" t="inlineStr"/>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr"/>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>SWKHL</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr"/>
-      <c r="D287" t="inlineStr"/>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr"/>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>SYNA</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr"/>
-      <c r="D288" t="inlineStr"/>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr"/>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>SYRE</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr"/>
-      <c r="D289" t="inlineStr"/>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr"/>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>TACT</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr"/>
-      <c r="D290" t="inlineStr"/>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr"/>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>TCMD</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr"/>
-      <c r="D291" t="inlineStr"/>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr"/>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>TENB</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr"/>
-      <c r="D292" t="inlineStr"/>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr"/>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>TILE</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr"/>
-      <c r="D293" t="inlineStr"/>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr"/>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>TLS</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr"/>
-      <c r="D294" t="inlineStr"/>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr"/>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>TRI</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr"/>
-      <c r="D295" t="inlineStr"/>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr"/>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>TRMB</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr"/>
-      <c r="D296" t="inlineStr"/>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr"/>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>TRS</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr"/>
-      <c r="D297" t="inlineStr"/>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr"/>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr"/>
-      <c r="D298" t="inlineStr"/>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr"/>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>VSXY</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr"/>
-      <c r="D299" t="inlineStr"/>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr"/>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>WAFU</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr"/>
-      <c r="D300" t="inlineStr"/>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr"/>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>WLTH</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr"/>
-      <c r="D301" t="inlineStr"/>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr"/>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>WSBCO</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr"/>
-      <c r="D302" t="inlineStr"/>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr"/>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>YMAT</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr"/>
-      <c r="D303" t="inlineStr"/>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr"/>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>YSWY</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr"/>
-      <c r="D304" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D235"/>
+  <dimension ref="A1:D268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,15 +441,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AEYE</t>
+          <t>AXIN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ACT</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>ACGL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BKYI</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>ALGN</t>
@@ -459,108 +463,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BOW</t>
+          <t>BRLT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>ACNB</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AMSF</t>
+          <t>BANR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JCSE</t>
+          <t>CLAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>ACT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BGSI</t>
+          <t>BBSI</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KELYB</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>ADAMI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BMGL</t>
+          <t>CASH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>POM</t>
+          <t>JVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>ADMA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CARR</t>
+          <t>CCB</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>ADUS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>CIGI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PACB</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ALLT</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CCB</t>
+          <t>CNDT</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>POM</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AMAL</t>
+          <t>AEYE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -571,30 +587,38 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PRME</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>AFRI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DHCNI</t>
+          <t>CVSA</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SDHIU</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMRO</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EJH</t>
+          <t>DGNX</t>
         </is>
       </c>
     </row>
@@ -602,13 +626,13 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>AGYS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ELUT</t>
+          <t>DHCNI</t>
         </is>
       </c>
     </row>
@@ -616,13 +640,13 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ANIK</t>
+          <t>ALKS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FLX</t>
+          <t>ELUT</t>
         </is>
       </c>
     </row>
@@ -630,13 +654,13 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>ALLT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>IMCR</t>
+          <t>FCCO</t>
         </is>
       </c>
     </row>
@@ -644,13 +668,13 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>ALRS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>FTW</t>
         </is>
       </c>
     </row>
@@ -658,13 +682,13 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ARLP</t>
+          <t>AMAL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>KLRA</t>
+          <t>HLMN</t>
         </is>
       </c>
     </row>
@@ -672,13 +696,13 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LIF</t>
+          <t>HONA</t>
         </is>
       </c>
     </row>
@@ -686,13 +710,13 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ARXS</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
@@ -700,13 +724,13 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ASTL</t>
+          <t>ANIK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NYAX</t>
+          <t>KLTR</t>
         </is>
       </c>
     </row>
@@ -714,13 +738,13 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ATLCL</t>
+          <t>AOUT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>OIO</t>
+          <t>KRMD</t>
         </is>
       </c>
     </row>
@@ -728,13 +752,13 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>OKYO</t>
+          <t>LBRX</t>
         </is>
       </c>
     </row>
@@ -742,13 +766,13 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>AQB</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>OSW</t>
+          <t>LULU</t>
         </is>
       </c>
     </row>
@@ -756,13 +780,13 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>ARHS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PWRL</t>
+          <t>NWBI</t>
         </is>
       </c>
     </row>
@@ -770,13 +794,13 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AVBH</t>
+          <t>ARLP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>RSVR</t>
+          <t>OIO</t>
         </is>
       </c>
     </row>
@@ -784,13 +808,13 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BANR</t>
+          <t>AROW</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SOLS</t>
+          <t>PCSA</t>
         </is>
       </c>
     </row>
@@ -798,13 +822,13 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BCAL</t>
+          <t>ARQT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>STAA</t>
+          <t>PEBO</t>
         </is>
       </c>
     </row>
@@ -812,13 +836,13 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BETR</t>
+          <t>ARX</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TCBK</t>
+          <t>PECO</t>
         </is>
       </c>
     </row>
@@ -826,13 +850,13 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>ARXS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TREE</t>
+          <t>SNES</t>
         </is>
       </c>
     </row>
@@ -840,13 +864,13 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>ASND</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VMRK</t>
+          <t>SNY</t>
         </is>
       </c>
     </row>
@@ -854,17 +878,21 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BOTJ</t>
+          <t>ASRV</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TCMD</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BPRN</t>
+          <t>ASTL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -874,7 +902,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>ATEC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -884,7 +912,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>ATER</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -894,7 +922,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>ATRC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -904,7 +932,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BSIN</t>
+          <t>AUPH</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -914,7 +942,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BSRR</t>
+          <t>AVBH</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -924,7 +952,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -934,7 +962,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BUSE</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -944,7 +972,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BVC</t>
+          <t>BBT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -954,7 +982,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BVS</t>
+          <t>BDCI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -964,7 +992,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BWFG</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -974,7 +1002,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -984,7 +1012,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CASS</t>
+          <t>BLLN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -994,7 +1022,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CATY</t>
+          <t>BLZR</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1004,7 +1032,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CCID</t>
+          <t>BPRN</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1014,7 +1042,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>BSET</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1024,7 +1052,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>BSIN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1034,7 +1062,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1044,7 +1072,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>BSRR</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1054,7 +1082,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>BWFG</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1064,7 +1092,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>BWMN</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1074,7 +1102,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1084,7 +1112,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1094,7 +1122,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CRSR</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1104,7 +1132,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>CATY</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1114,7 +1142,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CTKB</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1124,7 +1152,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>CBNK</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1134,7 +1162,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CVBF</t>
+          <t>CBRL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1144,7 +1172,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>CCBG</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1154,7 +1182,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CYRX</t>
+          <t>CCID</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1164,7 +1192,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CZFS</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1174,7 +1202,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DAKT</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1184,7 +1212,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1194,7 +1222,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>CENT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1204,7 +1232,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>CENTA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1214,7 +1242,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1224,7 +1252,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1234,7 +1262,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>CHMG</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1244,7 +1272,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>CIVB</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1254,7 +1282,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>CLBT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1264,7 +1292,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ERIC</t>
+          <t>COFS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1274,7 +1302,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>COLB</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1284,7 +1312,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EWBC</t>
+          <t>CPSS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1294,7 +1322,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1304,7 +1332,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>CTKB</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1314,7 +1342,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EXYN</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1324,7 +1352,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FBIZ</t>
+          <t>CWST</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1334,7 +1362,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FCBM</t>
+          <t>CYRX</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1344,7 +1372,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FCNCA</t>
+          <t>DAKT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1354,7 +1382,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FFBC</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1364,7 +1392,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>DCOM</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1374,7 +1402,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1384,7 +1412,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FMBH</t>
+          <t>DHCNL</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1394,7 +1422,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>DMAC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1404,7 +1432,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FRME</t>
+          <t>DMRC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1414,7 +1442,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FSSL</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1424,7 +1452,7 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1434,7 +1462,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1444,7 +1472,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FUNC</t>
+          <t>ELMT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1454,7 +1482,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FVNNU</t>
+          <t>EPSN</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1464,7 +1492,7 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GAINI</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1474,7 +1502,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1484,7 +1512,7 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GDRX</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1494,7 +1522,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1504,7 +1532,7 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>FBNC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -1514,7 +1542,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>FCAP</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -1524,7 +1552,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GRFS</t>
+          <t>FCBM</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1534,7 +1562,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GSBC</t>
+          <t>FCNCA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -1544,7 +1572,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>FFBC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -1554,7 +1582,7 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>HAFC</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1564,7 +1592,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>HBT</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1574,7 +1602,7 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>FIVN</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1584,7 +1612,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>HCSG</t>
+          <t>FLYW</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1594,7 +1622,7 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -1604,7 +1632,7 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>FMBH</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -1614,7 +1642,7 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FMNB</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -1624,7 +1652,7 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>HQY</t>
+          <t>FNLC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -1634,7 +1662,7 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>FRAF</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -1644,7 +1672,7 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>HWBK</t>
+          <t>FRBA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -1654,7 +1682,7 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>HWKN</t>
+          <t>FROG</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -1664,7 +1692,7 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>FSBC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -1674,7 +1702,7 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -1684,7 +1712,7 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>FULT</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -1694,7 +1722,7 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>FVN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -1704,7 +1732,7 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>IMC</t>
+          <t>FVNNU</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -1714,7 +1742,7 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>IMKTA</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -1724,7 +1752,7 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>INDB</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -1734,7 +1762,7 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -1744,7 +1772,7 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>GRAL</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -1754,7 +1782,7 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>GSBC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -1764,7 +1792,7 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -1774,7 +1802,7 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>HAFC</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -1784,7 +1812,7 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>JBDI</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -1794,7 +1822,7 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>JOUT</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -1804,7 +1832,7 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -1814,7 +1842,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>KELYA</t>
+          <t>HCSG</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -1824,7 +1852,7 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>KIDS</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -1834,7 +1862,7 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>KINS</t>
+          <t>HMR</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -1844,7 +1872,7 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>KMRK</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -1854,7 +1882,7 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>KMTS</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -1864,7 +1892,7 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>HTFL</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -1874,7 +1902,7 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -1884,7 +1912,7 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>KRRO</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -1894,7 +1922,7 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>LCNB</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -1904,7 +1932,7 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -1914,7 +1942,7 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>ICG</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -1924,7 +1952,7 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>LMAT</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -1934,7 +1962,7 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -1944,7 +1972,7 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>INDB</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -1954,7 +1982,7 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>INDP</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -1964,7 +1992,7 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>LSBK</t>
+          <t>INGN</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -1974,7 +2002,7 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -1984,7 +2012,7 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -1994,7 +2022,7 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBWM</t>
+          <t>IRON</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -2004,7 +2032,7 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MGRC</t>
+          <t>IRTC</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -2014,7 +2042,7 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MIDD</t>
+          <t>ISBA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2024,7 +2052,7 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MLKN</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2034,7 +2062,7 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MOBI</t>
+          <t>JJSF</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2044,7 +2072,7 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2054,7 +2082,7 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>MTC</t>
+          <t>JMSB</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2064,7 +2092,7 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>JYD</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2074,7 +2102,7 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MXCT</t>
+          <t>KARO</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2084,7 +2112,7 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>KELYA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2094,7 +2122,7 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NBBK</t>
+          <t>KMRK</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2104,7 +2132,7 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>NBTB</t>
+          <t>KMTS</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2114,7 +2142,7 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>NECB</t>
+          <t>KOD</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2124,7 +2152,7 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>NMFCZ</t>
+          <t>KPLT</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2134,7 +2162,7 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>NRIX</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -2144,7 +2172,7 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NSSC</t>
+          <t>KYIV</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -2154,7 +2182,7 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>NTRSO</t>
+          <t>LCNB</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -2164,7 +2192,7 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>LEGN</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2174,7 +2202,7 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>LFST</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -2184,7 +2212,7 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>NWFL</t>
+          <t>LGND</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -2194,7 +2222,7 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>OBT</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -2204,7 +2232,7 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>OFIX</t>
+          <t>LIVN</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -2214,7 +2242,7 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -2224,7 +2252,7 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>LMRI</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -2234,7 +2262,7 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -2244,7 +2272,7 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>OTAI</t>
+          <t>LSBK</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -2254,7 +2282,7 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>MANE</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -2264,7 +2292,7 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>OVBC</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -2274,7 +2302,7 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PBYI</t>
+          <t>MBWM</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -2284,7 +2312,7 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PDLB</t>
+          <t>MCBS</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -2294,7 +2322,7 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -2304,7 +2332,7 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PFIS</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -2314,7 +2342,7 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PFXNZ</t>
+          <t>MGRT</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -2324,7 +2352,7 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PHAR</t>
+          <t>MOBI</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -2334,7 +2362,7 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PLGO</t>
+          <t>MSBI</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -2344,7 +2372,7 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>MWYN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -2354,7 +2382,7 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PNFP</t>
+          <t>MXCT</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -2364,7 +2392,7 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>MYGN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -2374,7 +2402,7 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>NAUT</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -2384,7 +2412,7 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>NBN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -2394,7 +2422,7 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PRME</t>
+          <t>NBTB</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -2404,7 +2432,7 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>QCRH</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -2414,7 +2442,7 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>QSI</t>
+          <t>NECB</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -2424,7 +2452,7 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>RBB</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -2434,7 +2462,7 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>RCBC</t>
+          <t>NMIH</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -2444,7 +2472,7 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>NRC</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -2454,7 +2482,7 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>NRIX</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -2464,7 +2492,7 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>NSIT</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -2474,7 +2502,7 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>RGS</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -2484,7 +2512,7 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>RILYG</t>
+          <t>NTRA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -2494,7 +2522,7 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -2504,7 +2532,7 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>RPAY</t>
+          <t>OCTV</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -2514,7 +2542,7 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>OFIX</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -2524,7 +2552,7 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -2534,7 +2562,7 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>RRBI</t>
+          <t>OMCL</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -2544,7 +2572,7 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>ONC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -2554,7 +2582,7 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>RYZ</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -2564,7 +2592,7 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -2574,7 +2602,7 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>SAGT</t>
+          <t>OSW</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -2584,7 +2612,7 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -2594,7 +2622,7 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SBFG</t>
+          <t>OVBC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -2604,7 +2632,7 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>OZK</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -2614,7 +2642,7 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SEZL</t>
+          <t>PDLB</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -2624,7 +2652,7 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SFNC</t>
+          <t>PHAR</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -2634,7 +2662,7 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SGP</t>
+          <t>PLSE</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -2644,7 +2672,7 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>PNRG</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -2654,7 +2682,7 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>SNFCA</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -2664,7 +2692,7 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>POWW</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -2674,7 +2702,7 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>PPLC</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -2684,7 +2712,7 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>SRCE</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -2694,7 +2722,7 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>STBA</t>
+          <t>PRCT</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -2704,7 +2732,7 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>STRC</t>
+          <t>PRGS</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -2714,7 +2742,7 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>SUNB</t>
+          <t>PRTH</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -2724,7 +2752,7 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>SWIM</t>
+          <t>PSIG</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -2734,7 +2762,7 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>SYNA</t>
+          <t>PTEN</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -2744,7 +2772,7 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>SYRE</t>
+          <t>QCRH</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -2754,7 +2782,7 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>TACT</t>
+          <t>QDEL</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -2764,7 +2792,7 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>TASK</t>
+          <t>QLYS</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -2774,7 +2802,7 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>TCX</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -2784,7 +2812,7 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>THFF</t>
+          <t>QSI</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -2794,7 +2822,7 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>RCEL</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -2804,7 +2832,7 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>TOP</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -2814,7 +2842,7 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>TOWN</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -2824,7 +2852,7 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>TRAX</t>
+          <t>RMBI</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -2834,7 +2862,7 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>RPD</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -2844,7 +2872,7 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>RRBI</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -2854,7 +2882,7 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>RWAYI</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -2864,7 +2892,7 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>TROO</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -2874,7 +2902,7 @@
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
-          <t>TRS</t>
+          <t>SBAC</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -2884,7 +2912,7 @@
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
-          <t>WCCB</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -2894,7 +2922,7 @@
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
-          <t>WLTH</t>
+          <t>SEPN</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -2904,11 +2932,341 @@
       <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr">
         <is>
-          <t>XNCR</t>
+          <t>SEZL</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr"/>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>SGHT</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr"/>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>SGMT</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr"/>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr"/>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>SHOE</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr"/>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>SHPH</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr"/>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>SIBN</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr"/>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>SKYA</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr"/>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>SLDE</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr"/>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>SPSC</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr"/>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>SRZN</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr"/>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>STAA</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr"/>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>STAK</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr"/>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>STRC</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr"/>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>SUNB</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr"/>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>SWIM</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr"/>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>SWKS</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr"/>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>SWRD</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr"/>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>SYRE</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr"/>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr"/>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>TENB</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr"/>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>TLS</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr"/>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>TRAX</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr"/>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr"/>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr"/>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>TROO</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr"/>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr"/>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>UTHR</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr"/>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>VALU</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr"/>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>WCCB</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr"/>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>XNCR</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr"/>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>XZO</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr"/>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>YORW</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr"/>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>YSWY</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D268"/>
+  <dimension ref="A1:D408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,17 +441,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AXIN</t>
+          <t>BSBK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ACGL</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BKYI</t>
+          <t>PCSA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -463,204 +463,216 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRLT</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ACNB</t>
+          <t>ABLV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BANR</t>
+          <t>ASR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CLAR</t>
+          <t>CEPO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACT</t>
+          <t>ABSI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BBSI</t>
+          <t>BANR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>COAG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADAMI</t>
+          <t>ACGL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>BBIO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JVA</t>
+          <t>DHCNI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>ACIC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CCB</t>
+          <t>BBSI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KIDS</t>
+          <t>FRAF</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADUS</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CIGI</t>
+          <t>BCBP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PACB</t>
+          <t>FVNNU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>ACNB</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CNDT</t>
+          <t>BGSI</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>POM</t>
+          <t>MAYS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AEYE</t>
+          <t>ACT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CTSO</t>
+          <t>BKU</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PRME</t>
+          <t>MFIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AFRI</t>
+          <t>ACU</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>BOTJ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SDHIU</t>
+          <t>NUWE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>ADMA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DGNX</t>
+          <t>CARG</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PTLE</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AGYS</t>
+          <t>ADUS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DHCNI</t>
+          <t>CASH</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QNBC</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ALKS</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ELUT</t>
+          <t>CHDN</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STFS</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ALLT</t>
+          <t>AEYE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FCCO</t>
+          <t>CIGI</t>
         </is>
       </c>
     </row>
@@ -668,13 +680,13 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ALRS</t>
+          <t>AFRI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FTW</t>
+          <t>CLBT</t>
         </is>
       </c>
     </row>
@@ -682,13 +694,13 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AMAL</t>
+          <t>ALKS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HLMN</t>
+          <t>COLL</t>
         </is>
       </c>
     </row>
@@ -696,13 +708,13 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>ALLT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HONA</t>
+          <t>COO</t>
         </is>
       </c>
     </row>
@@ -710,13 +722,13 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>ALMR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>CPRT</t>
         </is>
       </c>
     </row>
@@ -724,13 +736,13 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ANIK</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KLTR</t>
+          <t>DORM</t>
         </is>
       </c>
     </row>
@@ -738,13 +750,13 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AOUT</t>
+          <t>ALRS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KRMD</t>
+          <t>EVER</t>
         </is>
       </c>
     </row>
@@ -752,13 +764,13 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>AMAL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LBRX</t>
+          <t>EXE</t>
         </is>
       </c>
     </row>
@@ -766,13 +778,13 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AQB</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>EXYN</t>
         </is>
       </c>
     </row>
@@ -780,13 +792,13 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NWBI</t>
+          <t>FHB</t>
         </is>
       </c>
     </row>
@@ -794,13 +806,13 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ARLP</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>OIO</t>
+          <t>FISV</t>
         </is>
       </c>
     </row>
@@ -808,13 +820,13 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AROW</t>
+          <t>ANIK</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PCSA</t>
+          <t>FLWS</t>
         </is>
       </c>
     </row>
@@ -822,13 +834,13 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PEBO</t>
+          <t>GIII</t>
         </is>
       </c>
     </row>
@@ -836,13 +848,13 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ARX</t>
+          <t>APOG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>HBAN</t>
         </is>
       </c>
     </row>
@@ -850,13 +862,13 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ARXS</t>
+          <t>AQB</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SNES</t>
+          <t>HLMN</t>
         </is>
       </c>
     </row>
@@ -864,13 +876,13 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>ARHS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>HOPE</t>
         </is>
       </c>
     </row>
@@ -878,13 +890,13 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ASRV</t>
+          <t>ARLP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TCMD</t>
+          <t>IDN</t>
         </is>
       </c>
     </row>
@@ -892,327 +904,455 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ASTL</t>
+          <t>AROW</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>IVA</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ATEC</t>
+          <t>ARQT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>JMSB</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ATER</t>
+          <t>ASND</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>JRVR</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>ASO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>KLRA</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>ASTL</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>KRMD</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AVBH</t>
+          <t>ATEC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>KXIN</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>ATLCL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LIF</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>ATLCZ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LMAT</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BBT</t>
+          <t>ATR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LWAY</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BDCI</t>
+          <t>ATRC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>MVBF</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>AUDC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NXST</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>OSIS</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BLLN</t>
+          <t>AVBC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>PATK</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BLZR</t>
+          <t>AVBH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>PECO</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BPRN</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>PLAY</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PLUR</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BSIN</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>PRPL</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>BANF</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>QNST</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BSRR</t>
+          <t>BBT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>RARE</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BWFG</t>
+          <t>BETR</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>RBB</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>BFST</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>RSVR</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>BHRB</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SIRI</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>BLLN</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SMBC</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>BMRC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SNES</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CATY</t>
+          <t>BOBS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SYBT</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>TCBK</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CBNK</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>TCBS</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>BRLT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>TOWN</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CCBG</t>
+          <t>BSET</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>TREE</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CCID</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>XFOR</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>BSVN</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>XLAB</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>BUUU</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>YORW</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>BVS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1222,7 +1362,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CENT</t>
+          <t>BWFG</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1232,7 +1372,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CENTA</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1242,7 +1382,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CAC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1252,7 +1392,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1262,7 +1402,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CHMG</t>
+          <t>CARL</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1272,7 +1412,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CIVB</t>
+          <t>CATY</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1282,7 +1422,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CLBT</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1292,7 +1432,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>COFS</t>
+          <t>CBK</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1302,7 +1442,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>COLB</t>
+          <t>CBNK</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1312,7 +1452,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CPSS</t>
+          <t>CBRL</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1322,7 +1462,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>CBU</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1332,7 +1472,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CTKB</t>
+          <t>CCBG</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1342,7 +1482,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>CCNE</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1352,7 +1492,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CWST</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1362,7 +1502,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CYRX</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1372,7 +1512,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DAKT</t>
+          <t>CDZI</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1382,7 +1522,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>CFBK</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1392,7 +1532,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DCOM</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1402,7 +1542,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1412,7 +1552,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DHCNL</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1422,7 +1562,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DMAC</t>
+          <t>CHCO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1432,7 +1572,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1442,7 +1582,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>CHMG</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1452,7 +1592,7 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>CHRD</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1462,7 +1602,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1472,7 +1612,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ELMT</t>
+          <t>CING</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1482,7 +1622,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EPSN</t>
+          <t>CIVB</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1492,7 +1632,7 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>CLAR</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1502,7 +1642,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>CLMB</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1512,7 +1652,7 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1522,7 +1662,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>COFS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1532,7 +1672,7 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FBNC</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -1542,7 +1682,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FCAP</t>
+          <t>COLB</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -1552,7 +1692,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FCBM</t>
+          <t>COLM</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1562,7 +1702,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FCNCA</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -1572,7 +1712,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FFBC</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -1582,7 +1722,7 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1592,7 +1732,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1602,7 +1742,7 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>CTKB</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1612,7 +1752,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1622,7 +1762,7 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -1632,7 +1772,7 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>FMBH</t>
+          <t>CZFS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -1642,7 +1782,7 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FMNB</t>
+          <t>CZNC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -1652,7 +1792,7 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FNLC</t>
+          <t>CZWI</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -1662,7 +1802,7 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FRAF</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -1672,7 +1812,7 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>FRBA</t>
+          <t>DGICA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -1682,7 +1822,7 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FROG</t>
+          <t>DHCNL</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -1692,7 +1832,7 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>FSBC</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -1702,7 +1842,7 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>DOO</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -1712,7 +1852,7 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>FULT</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -1722,7 +1862,7 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FVN</t>
+          <t>DTIL</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -1732,7 +1872,7 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>FVNNU</t>
+          <t>DUKU</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -1742,7 +1882,7 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>DYOR</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -1752,7 +1892,7 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -1762,7 +1902,7 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>EBC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -1772,7 +1912,7 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>EDHL</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -1782,7 +1922,7 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GSBC</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -1792,7 +1932,7 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -1802,7 +1942,7 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>HAFC</t>
+          <t>EGHT</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -1812,7 +1952,7 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>ELMT</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -1822,7 +1962,7 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -1832,7 +1972,7 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>ENTX</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -1842,7 +1982,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>HCSG</t>
+          <t>ENVX</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -1852,7 +1992,7 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>EPSN</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -1862,7 +2002,7 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>HMR</t>
+          <t>ERIC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -1872,7 +2012,7 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -1882,7 +2022,7 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>ESLT</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -1892,7 +2032,7 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -1902,7 +2042,7 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>EWBC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -1912,7 +2052,7 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -1922,7 +2062,7 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -1932,7 +2072,7 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ICFI</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -1942,7 +2082,7 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -1952,7 +2092,7 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -1962,7 +2102,7 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>FBIZ</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -1972,7 +2112,7 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>INDB</t>
+          <t>FBLA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -1982,7 +2122,7 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>INDP</t>
+          <t>FCAP</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -1992,7 +2132,7 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>FCBM</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -2002,7 +2142,7 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>FCCO</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -2012,7 +2152,7 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>FCNCA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -2022,7 +2162,7 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>FDBC</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -2032,7 +2172,7 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>IRTC</t>
+          <t>FFBC</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -2042,7 +2182,7 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ISBA</t>
+          <t>FGBI</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2052,7 +2192,7 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>FIBK</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2062,7 +2202,7 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>JJSF</t>
+          <t>FISI</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2072,7 +2212,7 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2082,7 +2222,7 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>JMSB</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2092,7 +2232,7 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>FLYW</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2102,7 +2242,7 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>KARO</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2112,7 +2252,7 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>KELYA</t>
+          <t>FMBH</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2122,7 +2262,7 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>KMRK</t>
+          <t>FMNB</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2132,7 +2272,7 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>KMTS</t>
+          <t>FNKO</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2142,7 +2282,7 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>FNLC</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2152,7 +2292,7 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>FNWD</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2162,7 +2302,7 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>FRBA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -2172,7 +2312,7 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>KYIV</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -2182,7 +2322,7 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>LCNB</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -2192,7 +2332,7 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>LEGN</t>
+          <t>FRME</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2202,7 +2342,7 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>LFST</t>
+          <t>FRMEP</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -2212,7 +2352,7 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>FSBC</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -2222,7 +2362,7 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>FSSL</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -2232,7 +2372,7 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>LIVN</t>
+          <t>FSV</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -2242,7 +2382,7 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>FTDR</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -2252,7 +2392,7 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>LMRI</t>
+          <t>FULT</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -2262,7 +2402,7 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>FUNC</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -2272,7 +2412,7 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LSBK</t>
+          <t>FVN</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -2282,7 +2422,7 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -2292,7 +2432,7 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>GDRX</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -2302,7 +2442,7 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>MBWM</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -2312,7 +2452,7 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MCBS</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -2322,7 +2462,7 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -2332,7 +2472,7 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>GLBE</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -2342,7 +2482,7 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MGRT</t>
+          <t>GRAL</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -2352,7 +2492,7 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MOBI</t>
+          <t>GSBC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -2362,7 +2502,7 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MSBI</t>
+          <t>HAFC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -2372,7 +2512,7 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -2382,7 +2522,7 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MXCT</t>
+          <t>HBIO</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -2392,7 +2532,7 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>HBNC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -2402,7 +2542,7 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>HBT</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -2412,7 +2552,7 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>NBN</t>
+          <t>HCSG</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -2422,7 +2562,7 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>NBTB</t>
+          <t>HELE</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -2432,7 +2572,7 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>HIFS</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -2442,7 +2582,7 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>NECB</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -2452,7 +2592,7 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>NICE</t>
+          <t>HOWL</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -2462,7 +2602,7 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NMIH</t>
+          <t>HQY</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -2472,7 +2612,7 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>NRC</t>
+          <t>HTFL</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -2482,7 +2622,7 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NRIX</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -2492,7 +2632,7 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -2502,7 +2642,7 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>HWBK</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -2512,7 +2652,7 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>HYNE</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -2522,7 +2662,7 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -2532,7 +2672,7 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>IBCP</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -2542,7 +2682,7 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>OFIX</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -2552,7 +2692,7 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>ICUI</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -2562,7 +2702,7 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>OMCL</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -2572,7 +2712,7 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ONC</t>
+          <t>IMC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -2582,7 +2722,7 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>INDB</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -2592,7 +2732,7 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>INDP</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -2602,7 +2742,7 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>OSW</t>
+          <t>INGN</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -2612,7 +2752,7 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>INTG</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -2622,7 +2762,7 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>OVBC</t>
+          <t>IOSP</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -2632,7 +2772,7 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>OZK</t>
+          <t>IRON</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -2642,7 +2782,7 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PDLB</t>
+          <t>IRTC</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -2652,7 +2792,7 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PHAR</t>
+          <t>ISBA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -2662,7 +2802,7 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PLSE</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -2672,7 +2812,7 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PNRG</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -2682,7 +2822,7 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>JJSF</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -2692,7 +2832,7 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>POWW</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -2702,7 +2842,7 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PPLC</t>
+          <t>JVA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -2712,7 +2852,7 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>KARO</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -2722,7 +2862,7 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PRCT</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -2732,7 +2872,7 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>KIDS</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -2742,7 +2882,7 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PRTH</t>
+          <t>KINS</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -2752,7 +2892,7 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PSIG</t>
+          <t>KLTR</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -2762,7 +2902,7 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PTEN</t>
+          <t>KMTS</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -2772,7 +2912,7 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>QCRH</t>
+          <t>KNSA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -2782,7 +2922,7 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>QDEL</t>
+          <t>KOD</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -2792,7 +2932,7 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>KPLT</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -2802,7 +2942,7 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>KRNT</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -2812,7 +2952,7 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>QSI</t>
+          <t>KROS</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -2822,7 +2962,7 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>KRRO</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -2832,7 +2972,7 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -2842,7 +2982,7 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>KVHI</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -2852,7 +2992,7 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>RMBI</t>
+          <t>KYIV</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -2862,7 +3002,7 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>LARK</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -2872,7 +3012,7 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>RRBI</t>
+          <t>LBRX</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -2882,7 +3022,7 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>RWAYI</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -2892,7 +3032,7 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>LFST</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -2902,7 +3042,7 @@
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
-          <t>SBAC</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -2912,7 +3052,7 @@
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -2922,7 +3062,7 @@
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
-          <t>SEPN</t>
+          <t>LIVN</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -2932,7 +3072,7 @@
       <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr">
         <is>
-          <t>SEZL</t>
+          <t>LKFN</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -2942,7 +3082,7 @@
       <c r="A236" t="inlineStr"/>
       <c r="B236" t="inlineStr">
         <is>
-          <t>SGHT</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -2952,7 +3092,7 @@
       <c r="A237" t="inlineStr"/>
       <c r="B237" t="inlineStr">
         <is>
-          <t>SGMT</t>
+          <t>LLYVA</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -2962,7 +3102,7 @@
       <c r="A238" t="inlineStr"/>
       <c r="B238" t="inlineStr">
         <is>
-          <t>SGP</t>
+          <t>LLYVK</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -2972,7 +3112,7 @@
       <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr">
         <is>
-          <t>SHOE</t>
+          <t>LMRI</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -2982,7 +3122,7 @@
       <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr">
         <is>
-          <t>SHPH</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -2992,7 +3132,7 @@
       <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>LOVE</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -3002,7 +3142,7 @@
       <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -3012,7 +3152,7 @@
       <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>LSBK</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -3022,7 +3162,7 @@
       <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -3032,7 +3172,7 @@
       <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr">
         <is>
-          <t>SRZN</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -3042,7 +3182,7 @@
       <c r="A246" t="inlineStr"/>
       <c r="B246" t="inlineStr">
         <is>
-          <t>STAA</t>
+          <t>MANE</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -3052,7 +3192,7 @@
       <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr">
         <is>
-          <t>STAK</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -3062,7 +3202,7 @@
       <c r="A248" t="inlineStr"/>
       <c r="B248" t="inlineStr">
         <is>
-          <t>STRC</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -3072,7 +3212,7 @@
       <c r="A249" t="inlineStr"/>
       <c r="B249" t="inlineStr">
         <is>
-          <t>SUNB</t>
+          <t>MAZE</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -3082,7 +3222,7 @@
       <c r="A250" t="inlineStr"/>
       <c r="B250" t="inlineStr">
         <is>
-          <t>SWIM</t>
+          <t>MBWM</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -3092,7 +3232,7 @@
       <c r="A251" t="inlineStr"/>
       <c r="B251" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>MCBS</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -3102,7 +3242,7 @@
       <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr">
         <is>
-          <t>SWRD</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -3112,7 +3252,7 @@
       <c r="A253" t="inlineStr"/>
       <c r="B253" t="inlineStr">
         <is>
-          <t>SYRE</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -3122,7 +3262,7 @@
       <c r="A254" t="inlineStr"/>
       <c r="B254" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>MGRC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -3132,7 +3272,7 @@
       <c r="A255" t="inlineStr"/>
       <c r="B255" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>MGRT</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -3142,7 +3282,7 @@
       <c r="A256" t="inlineStr"/>
       <c r="B256" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>MIDD</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -3152,7 +3292,7 @@
       <c r="A257" t="inlineStr"/>
       <c r="B257" t="inlineStr">
         <is>
-          <t>TRAX</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -3162,7 +3302,7 @@
       <c r="A258" t="inlineStr"/>
       <c r="B258" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>MORN</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -3172,7 +3312,7 @@
       <c r="A259" t="inlineStr"/>
       <c r="B259" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -3182,7 +3322,7 @@
       <c r="A260" t="inlineStr"/>
       <c r="B260" t="inlineStr">
         <is>
-          <t>TROO</t>
+          <t>MSBI</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -3192,7 +3332,7 @@
       <c r="A261" t="inlineStr"/>
       <c r="B261" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>MSEX</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -3202,7 +3342,7 @@
       <c r="A262" t="inlineStr"/>
       <c r="B262" t="inlineStr">
         <is>
-          <t>UTHR</t>
+          <t>MTEX</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -3212,7 +3352,7 @@
       <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr">
         <is>
-          <t>VALU</t>
+          <t>MXCT</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -3222,7 +3362,7 @@
       <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr">
         <is>
-          <t>WCCB</t>
+          <t>MYFW</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -3232,7 +3372,7 @@
       <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr">
         <is>
-          <t>XNCR</t>
+          <t>MZTI</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -3242,7 +3382,7 @@
       <c r="A266" t="inlineStr"/>
       <c r="B266" t="inlineStr">
         <is>
-          <t>XZO</t>
+          <t>NAVN</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -3252,7 +3392,7 @@
       <c r="A267" t="inlineStr"/>
       <c r="B267" t="inlineStr">
         <is>
-          <t>YORW</t>
+          <t>NBBK</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -3262,11 +3402,1411 @@
       <c r="A268" t="inlineStr"/>
       <c r="B268" t="inlineStr">
         <is>
-          <t>YSWY</t>
+          <t>NBN</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr"/>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>NBTX</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr"/>
+      <c r="D269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr"/>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>NDAQ</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr"/>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>NECB</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr"/>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>NICE</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr"/>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>NMIH</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr"/>
+      <c r="D273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr"/>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>NOVT</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr"/>
+      <c r="D274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr"/>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>NPAC</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr"/>
+      <c r="D275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr"/>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>NRC</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr"/>
+      <c r="D276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr"/>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>NRDS</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr"/>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>NRIX</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr"/>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>NSIT</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr"/>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>NSSC</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr"/>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>NTCT</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr"/>
+      <c r="D281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr"/>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>NTGR</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr"/>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>NTNX</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr"/>
+      <c r="D283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr"/>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>NTRA</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr"/>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>NUTX</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr"/>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>NWBI</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr"/>
+      <c r="D286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr"/>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>NXPI</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr"/>
+      <c r="D287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr"/>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>OBT</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr"/>
+      <c r="D288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr"/>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>OFIX</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr"/>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>OFS</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr"/>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>OKTA</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr"/>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>OMAB</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr"/>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>OMCL</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr"/>
+      <c r="D293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr"/>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>ONC</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr"/>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>OPK</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr"/>
+      <c r="D295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr"/>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>OPLN</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr"/>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>OPRT</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr"/>
+      <c r="D297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr"/>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>OPRX</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr"/>
+      <c r="D298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr"/>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>ORKA</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr"/>
+      <c r="D299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr"/>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>ORRF</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr"/>
+      <c r="D300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr"/>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>OSG</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr"/>
+      <c r="D301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr"/>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>OSPN</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr"/>
+      <c r="D302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr"/>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>OSUR</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr"/>
+      <c r="D303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr"/>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>OSW</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr"/>
+      <c r="D304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr"/>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>OTAI</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr"/>
+      <c r="D305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr"/>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>OTTR</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr"/>
+      <c r="D306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr"/>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>OVBC</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr"/>
+      <c r="D307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr"/>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>OVLY</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr"/>
+      <c r="D308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr"/>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>OXLCO</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr"/>
+      <c r="D309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr"/>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>OXLCZ</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr"/>
+      <c r="D310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr"/>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>OZK</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr"/>
+      <c r="D311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr"/>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>PAA</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr"/>
+      <c r="D312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr"/>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>PACB</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr"/>
+      <c r="D313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr"/>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>PAGP</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr"/>
+      <c r="D314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr"/>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr"/>
+      <c r="D315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr"/>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>PDLB</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr"/>
+      <c r="D316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr"/>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>PDSB</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr"/>
+      <c r="D317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr"/>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>PEBO</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr"/>
+      <c r="D318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr"/>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>PFBC</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr"/>
+      <c r="D319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr"/>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>PFIS</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr"/>
+      <c r="D320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr"/>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>PGNY</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr"/>
+      <c r="D321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr"/>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>PGY</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr"/>
+      <c r="D322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr"/>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>PLBC</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr"/>
+      <c r="D323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr"/>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>PLBY</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr"/>
+      <c r="D324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr"/>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>PLGO</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr"/>
+      <c r="D325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr"/>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>PLMR</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr"/>
+      <c r="D326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr"/>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>PLSE</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
+      <c r="D327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr"/>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>PLUS</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr"/>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>PNFP</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr"/>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>PNTG</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr"/>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>PODD</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr"/>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>POOL</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr"/>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>POWW</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr"/>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>PPLC</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr"/>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>PRCT</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr"/>
+      <c r="D335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr"/>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>PRME</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr"/>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>PRVA</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr"/>
+      <c r="D337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr"/>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>PSIG</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr"/>
+      <c r="D338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr"/>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>PTON</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr"/>
+      <c r="D339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr"/>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>QDEL</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr"/>
+      <c r="D340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr"/>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>QLYS</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr"/>
+      <c r="D341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr"/>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>QSI</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr"/>
+      <c r="D342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr"/>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>RCBC</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr"/>
+      <c r="D343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr"/>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>RCEL</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr"/>
+      <c r="D344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr"/>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr"/>
+      <c r="D345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr"/>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>REF</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr"/>
+      <c r="D346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr"/>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr"/>
+      <c r="D347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr"/>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>RELY</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr"/>
+      <c r="D348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr"/>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>REYN</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr"/>
+      <c r="D349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr"/>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>RGCO</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr"/>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>RIGL</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr"/>
+      <c r="D351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr"/>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>RLAY</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr"/>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>RMBI</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr"/>
+      <c r="D353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr"/>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>ROIV</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr"/>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>ROOT</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr"/>
+      <c r="D355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr"/>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>RPAY</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr"/>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>RPC</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr"/>
+      <c r="D357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr"/>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>RRBI</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr"/>
+      <c r="D358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr"/>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>RYZ</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr"/>
+      <c r="D359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr"/>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>SBAC</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr"/>
+      <c r="D360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr"/>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>SBFG</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr"/>
+      <c r="D361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr"/>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr"/>
+      <c r="D362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr"/>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>SCHL</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr"/>
+      <c r="D363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr"/>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>SEPN</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr"/>
+      <c r="D364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr"/>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr"/>
+      <c r="D365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr"/>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>SFNC</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr"/>
+      <c r="D366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr"/>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>SFST</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr"/>
+      <c r="D367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr"/>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>SGHT</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr"/>
+      <c r="D368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr"/>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr"/>
+      <c r="D369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr"/>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>SHOE</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr"/>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>SHPH</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr"/>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>SIBN</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr"/>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>SIGI</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr"/>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>SLAB</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr"/>
+      <c r="D374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr"/>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>SNFCA</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr"/>
+      <c r="D375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr"/>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>SNY</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr"/>
+      <c r="D376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr"/>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>SOMN</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr"/>
+      <c r="D377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr"/>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>SPFI</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr"/>
+      <c r="D378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr"/>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>SPTX</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr"/>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>SRCE</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr"/>
+      <c r="D380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr"/>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>SRZN</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr"/>
+      <c r="D381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr"/>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>SSTI</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr"/>
+      <c r="D382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr"/>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>STAA</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr"/>
+      <c r="D383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr"/>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>STBA</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr"/>
+      <c r="D384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr"/>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>STLD</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr"/>
+      <c r="D385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr"/>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>STRC</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr"/>
+      <c r="D386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr"/>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>SUNB</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr"/>
+      <c r="D387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr"/>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>SWIM</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr"/>
+      <c r="D388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr"/>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>SWRD</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr"/>
+      <c r="D389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr"/>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>TACO</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr"/>
+      <c r="D390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr"/>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>TACT</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr"/>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>TBCH</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr"/>
+      <c r="D392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr"/>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>TCMD</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr"/>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>TENB</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr"/>
+      <c r="D394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr"/>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>TFSL</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr"/>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>TGTX</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr"/>
+      <c r="D396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr"/>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>THFF</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr"/>
+      <c r="D397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr"/>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>TILE</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr"/>
+      <c r="D398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr"/>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>TMCI</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr"/>
+      <c r="D399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr"/>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>TNDM</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr"/>
+      <c r="D400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr"/>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>TRAX</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr"/>
+      <c r="D401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr"/>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr"/>
+      <c r="D402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr"/>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr"/>
+      <c r="D403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr"/>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr"/>
+      <c r="D404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr"/>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>UTHR</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr"/>
+      <c r="D405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr"/>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>VSXY</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr"/>
+      <c r="D406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr"/>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>WCCB</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr"/>
+      <c r="D407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr"/>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>YMAT</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr"/>
+      <c r="D408" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D408"/>
+  <dimension ref="A1:D324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,29 +441,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BSBK</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>ABCL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PCSA</t>
+          <t>BRKRP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ALGN</t>
+          <t>AHRT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>CHOW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -471,161 +471,165 @@
           <t>ABLV</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HBNB</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ASR</t>
+          <t>BANR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CEPO</t>
+          <t>FBIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ABSI</t>
+          <t>ACGL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BANR</t>
+          <t>BBSI</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COAG</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ACGL</t>
+          <t>ACIC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BBIO</t>
+          <t>BCBP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DHCNI</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BBSI</t>
+          <t>BGSI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FRAF</t>
+          <t>NSLRL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>ACNB</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BCBP</t>
+          <t>BOKF</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FVNNU</t>
+          <t>OSPN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ACNB</t>
+          <t>ACU</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BGSI</t>
+          <t>CASY</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MAYS</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ACT</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BKU</t>
+          <t>CHDN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MFIC</t>
+          <t>SHOE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>ADPT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BOTJ</t>
+          <t>CLRO</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NUWE</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CARG</t>
+          <t>COLL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PTLE</t>
+          <t>TOMZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -636,43 +640,35 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>COO</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>QNBC</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>CRNT</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STFS</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AEYE</t>
+          <t>AFRI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CIGI</t>
+          <t>CWST</t>
         </is>
       </c>
     </row>
@@ -680,13 +676,13 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AFRI</t>
+          <t>AGYS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CLBT</t>
+          <t>DPZ</t>
         </is>
       </c>
     </row>
@@ -700,7 +696,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>COLL</t>
+          <t>EJH</t>
         </is>
       </c>
     </row>
@@ -714,7 +710,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>ESTA</t>
         </is>
       </c>
     </row>
@@ -722,13 +718,13 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ALMR</t>
+          <t>ALRS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>EVER</t>
         </is>
       </c>
     </row>
@@ -736,13 +732,13 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DORM</t>
+          <t>EXTR</t>
         </is>
       </c>
     </row>
@@ -750,13 +746,13 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ALRS</t>
+          <t>AMRX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EVER</t>
+          <t>FISV</t>
         </is>
       </c>
     </row>
@@ -764,13 +760,13 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AMAL</t>
+          <t>ANIK</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>HBAN</t>
         </is>
       </c>
     </row>
@@ -778,13 +774,13 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EXYN</t>
+          <t>IDN</t>
         </is>
       </c>
     </row>
@@ -792,13 +788,13 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FHB</t>
+          <t>IMCR</t>
         </is>
       </c>
     </row>
@@ -806,13 +802,13 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>INSG</t>
         </is>
       </c>
     </row>
@@ -820,13 +816,13 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ANIK</t>
+          <t>AROW</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FLWS</t>
+          <t>KWY</t>
         </is>
       </c>
     </row>
@@ -834,13 +830,13 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ARQT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>LMAT</t>
         </is>
       </c>
     </row>
@@ -848,13 +844,13 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>ARX</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>HBAN</t>
+          <t>LWAY</t>
         </is>
       </c>
     </row>
@@ -862,13 +858,13 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AQB</t>
+          <t>ASBH</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>HLMN</t>
+          <t>MGEE</t>
         </is>
       </c>
     </row>
@@ -876,13 +872,13 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>ASND</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>NBIX</t>
         </is>
       </c>
     </row>
@@ -890,13 +886,13 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ARLP</t>
+          <t>ATLCL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>NBN</t>
         </is>
       </c>
     </row>
@@ -904,13 +900,13 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AROW</t>
+          <t>ATLCZ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IVA</t>
+          <t>NXST</t>
         </is>
       </c>
     </row>
@@ -918,13 +914,13 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>ATR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>JMSB</t>
+          <t>NYAX</t>
         </is>
       </c>
     </row>
@@ -932,13 +928,13 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>AUDC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>JRVR</t>
+          <t>OFIX</t>
         </is>
       </c>
     </row>
@@ -946,13 +942,13 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>AUPH</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KLRA</t>
+          <t>PATK</t>
         </is>
       </c>
     </row>
@@ -960,13 +956,13 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ASTL</t>
+          <t>AVBC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>KRMD</t>
+          <t>PAYX</t>
         </is>
       </c>
     </row>
@@ -974,13 +970,13 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ATEC</t>
+          <t>AVBH</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>KXIN</t>
+          <t>PECO</t>
         </is>
       </c>
     </row>
@@ -988,13 +984,13 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ATLCL</t>
+          <t>AWR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LIF</t>
+          <t>PEP</t>
         </is>
       </c>
     </row>
@@ -1002,13 +998,13 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ATLCZ</t>
+          <t>AXGN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LMAT</t>
+          <t>PLUR</t>
         </is>
       </c>
     </row>
@@ -1016,13 +1012,13 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ATR</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LWAY</t>
+          <t>PRTA</t>
         </is>
       </c>
     </row>
@@ -1030,13 +1026,13 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>BBCP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MVBF</t>
+          <t>QQQX</t>
         </is>
       </c>
     </row>
@@ -1044,13 +1040,13 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>BBIO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NXST</t>
+          <t>RARE</t>
         </is>
       </c>
     </row>
@@ -1058,13 +1054,13 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>BFST</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>OSIS</t>
+          <t>RDCM</t>
         </is>
       </c>
     </row>
@@ -1072,13 +1068,13 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AVBC</t>
+          <t>BHRB</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PATK</t>
+          <t>SIRI</t>
         </is>
       </c>
     </row>
@@ -1086,13 +1082,13 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AVBH</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>SMBC</t>
         </is>
       </c>
     </row>
@@ -1100,13 +1096,13 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>SOLS</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1110,13 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>PLUR</t>
+          <t>TCBK</t>
         </is>
       </c>
     </row>
@@ -1128,13 +1124,13 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>BMGL</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>PRPL</t>
+          <t>TCX</t>
         </is>
       </c>
     </row>
@@ -1142,13 +1138,13 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BANF</t>
+          <t>BMRC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>QNST</t>
+          <t>VMRK</t>
         </is>
       </c>
     </row>
@@ -1156,13 +1152,13 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BBT</t>
+          <t>BOOM</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>RARE</t>
+          <t>YORW</t>
         </is>
       </c>
     </row>
@@ -1170,189 +1166,137 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BETR</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>RBB</t>
-        </is>
-      </c>
+      <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BFST</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>RSVR</t>
-        </is>
-      </c>
+      <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BHRB</t>
+          <t>BSBK</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>SIRI</t>
-        </is>
-      </c>
+      <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BLLN</t>
+          <t>BSIN</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>SMBC</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BMRC</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>SNES</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BOBS</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>SYBT</t>
-        </is>
-      </c>
+      <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BOW</t>
+          <t>BUUU</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>TCBK</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>BVC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>TCBS</t>
-        </is>
-      </c>
+      <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BRLT</t>
+          <t>BVFL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>TOWN</t>
-        </is>
-      </c>
+      <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>BWFG</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>TREE</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>XFOR</t>
-        </is>
-      </c>
+      <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>CARL</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>XLAB</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BUUU</t>
+          <t>CATY</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>YORW</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BVS</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1362,7 +1306,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BWFG</t>
+          <t>CBK</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1372,7 +1316,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>CBU</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1382,7 +1326,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CAC</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1392,7 +1336,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>CCID</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1402,7 +1346,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CARL</t>
+          <t>CCNE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1412,7 +1356,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CATY</t>
+          <t>CDLR</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1422,7 +1366,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>CENT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1432,7 +1376,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CBK</t>
+          <t>CENTA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1442,7 +1386,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CBNK</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1452,7 +1396,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1462,7 +1406,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CBU</t>
+          <t>CHCO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1472,7 +1416,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CCBG</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1482,7 +1426,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CCNE</t>
+          <t>CHRD</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1492,7 +1436,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>CIGI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1502,7 +1446,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1512,7 +1456,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CDZI</t>
+          <t>CING</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1522,7 +1466,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CFBK</t>
+          <t>CIVB</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1532,7 +1476,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>CLGN</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1542,7 +1486,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1552,7 +1496,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>COAG</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1562,7 +1506,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CHCO</t>
+          <t>COFS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1572,7 +1516,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>COLM</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1582,7 +1526,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CHMG</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1592,7 +1536,7 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CHRD</t>
+          <t>CPB</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1602,7 +1546,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>CPRT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1612,7 +1556,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CING</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1622,7 +1566,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CIVB</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1632,7 +1576,7 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CLAR</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1642,7 +1586,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CLMB</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1652,7 +1596,7 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>CVBF</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1662,7 +1606,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>COFS</t>
+          <t>CZFS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1672,7 +1616,7 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>CZNC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -1682,7 +1626,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>COLB</t>
+          <t>CZWI</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -1692,7 +1636,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>COLM</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1702,7 +1646,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>DCOM</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -1712,7 +1656,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>DGII</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -1722,7 +1666,7 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1732,7 +1676,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>DMAA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1742,7 +1686,7 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CTKB</t>
+          <t>DMII</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1752,7 +1696,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>DORM</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1762,7 +1706,7 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -1772,7 +1716,7 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CZFS</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -1782,7 +1726,7 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CZNC</t>
+          <t>DUKU</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -1792,7 +1736,7 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CZWI</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -1802,7 +1746,7 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>EFSC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -1812,7 +1756,7 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DGICA</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -1822,7 +1766,7 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DHCNL</t>
+          <t>EPSN</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -1832,7 +1776,7 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>ERIC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -1842,7 +1786,7 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DOO</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -1852,7 +1796,7 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -1862,7 +1806,7 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DTIL</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -1872,7 +1816,7 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>DUKU</t>
+          <t>EWBC</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -1882,7 +1826,7 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>DYOR</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -1892,7 +1836,7 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -1902,7 +1846,7 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EBC</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -1912,7 +1856,7 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -1922,7 +1866,7 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -1932,7 +1876,7 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -1942,7 +1886,7 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EGHT</t>
+          <t>FBNC</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -1952,7 +1896,7 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ELMT</t>
+          <t>FCBM</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -1962,7 +1906,7 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>FCCO</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -1972,7 +1916,7 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ENTX</t>
+          <t>FCNCA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -1982,7 +1926,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ENVX</t>
+          <t>FDBC</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -1992,7 +1936,7 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EPSN</t>
+          <t>FGBI</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -2002,7 +1946,7 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ERIC</t>
+          <t>FIZZ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -2012,7 +1956,7 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -2022,7 +1966,7 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ESLT</t>
+          <t>FNLC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -2032,7 +1976,7 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>FRAF</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -2042,7 +1986,7 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EWBC</t>
+          <t>FRBA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -2052,7 +1996,7 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -2062,7 +2006,7 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -2072,7 +2016,7 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>FRME</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -2082,7 +2026,7 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>FSBC</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -2092,7 +2036,7 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>FSSL</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -2102,7 +2046,7 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>FBIZ</t>
+          <t>FTDR</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -2112,7 +2056,7 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>FBLA</t>
+          <t>FULT</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -2122,7 +2066,7 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>FCAP</t>
+          <t>FUNC</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -2132,7 +2076,7 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>FCBM</t>
+          <t>GAING</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -2142,7 +2086,7 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>FCCO</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -2152,7 +2096,7 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>FCNCA</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -2162,7 +2106,7 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>FDBC</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -2172,7 +2116,7 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>FFBC</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -2182,7 +2126,7 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>FGBI</t>
+          <t>GIBO</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2192,7 +2136,7 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>FIBK</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2202,7 +2146,7 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>FISI</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2212,7 +2156,7 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2222,7 +2166,7 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>GRFS</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2232,7 +2176,7 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>GSAT</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2242,7 +2186,7 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>GSBC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2252,7 +2196,7 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>FMBH</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2262,7 +2206,7 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>FMNB</t>
+          <t>HAFC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2272,7 +2216,7 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2282,7 +2226,7 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>FNLC</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2292,7 +2236,7 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>FNWD</t>
+          <t>HBIO</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2302,7 +2246,7 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>FRBA</t>
+          <t>HBNC</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -2312,7 +2256,7 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -2322,7 +2266,7 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>FRHC</t>
+          <t>HELE</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -2332,7 +2276,7 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FRME</t>
+          <t>HFWA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2342,7 +2286,7 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>FRMEP</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -2352,7 +2296,7 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>FSBC</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -2362,7 +2306,7 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>FSSL</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -2372,7 +2316,7 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>FSV</t>
+          <t>HWBK</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -2382,7 +2326,7 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>HWKN</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -2392,7 +2336,7 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>FULT</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -2402,7 +2346,7 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>FUNC</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -2412,7 +2356,7 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>FVN</t>
+          <t>III</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -2422,7 +2366,7 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>IIIV</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -2432,7 +2376,7 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>GDRX</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -2442,7 +2386,7 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>INVA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -2452,7 +2396,7 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>IOSP</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -2462,7 +2406,7 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>IPAR</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -2472,7 +2416,7 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>GLBE</t>
+          <t>IRON</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -2482,7 +2426,7 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>ISBA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -2492,7 +2436,7 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>GSBC</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -2502,7 +2446,7 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>HAFC</t>
+          <t>ITRI</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -2512,7 +2456,7 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -2522,7 +2466,7 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>JANX</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -2532,7 +2476,7 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>HBNC</t>
+          <t>JJSF</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -2542,7 +2486,7 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>HBT</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -2552,7 +2496,7 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>HCSG</t>
+          <t>JOUT</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -2562,7 +2506,7 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>HELE</t>
+          <t>JVA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -2572,7 +2516,7 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>HIFS</t>
+          <t>KARO</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -2582,7 +2526,7 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -2592,7 +2536,7 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>HOWL</t>
+          <t>KELYA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -2602,7 +2546,7 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>HQY</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -2612,7 +2556,7 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -2622,7 +2566,7 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>KINS</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -2632,7 +2576,7 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>KMRK</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -2642,7 +2586,7 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>HWBK</t>
+          <t>KROS</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -2652,7 +2596,7 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>HYNE</t>
+          <t>LBRX</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -2662,7 +2606,7 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>LCNB</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -2672,7 +2616,7 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>IBCP</t>
+          <t>LEGH</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -2682,7 +2626,7 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>LEGN</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -2692,7 +2636,7 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>ICUI</t>
+          <t>LGND</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -2702,7 +2646,7 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -2712,7 +2656,7 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>IMC</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -2722,7 +2666,7 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>INDB</t>
+          <t>LKFN</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -2732,7 +2676,7 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>INDP</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -2742,7 +2686,7 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>LLYVA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -2752,7 +2696,7 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>INTG</t>
+          <t>LLYVK</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -2762,7 +2706,7 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>LMRI</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -2772,7 +2716,7 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -2782,7 +2726,7 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>IRTC</t>
+          <t>LOVE</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -2792,7 +2736,7 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ISBA</t>
+          <t>LSBK</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -2802,7 +2746,7 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>LYEL</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -2812,7 +2756,7 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -2822,7 +2766,7 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>JJSF</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -2832,7 +2776,7 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -2842,7 +2786,7 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>JVA</t>
+          <t>MASS</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -2852,7 +2796,7 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>KARO</t>
+          <t>MAZE</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -2862,7 +2806,7 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>MBWM</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -2872,7 +2816,7 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>KIDS</t>
+          <t>MCHX</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -2882,7 +2826,7 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>KINS</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -2892,7 +2836,7 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>KLTR</t>
+          <t>MGYR</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -2902,7 +2846,7 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>KMTS</t>
+          <t>MICC</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -2912,7 +2856,7 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>KNSA</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -2922,7 +2866,7 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -2932,7 +2876,7 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>MORN</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -2942,7 +2886,7 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -2952,7 +2896,7 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>KROS</t>
+          <t>MRVI</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -2962,7 +2906,7 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>KRRO</t>
+          <t>MSBI</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -2972,7 +2916,7 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>MSEX</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -2982,7 +2926,7 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>KVHI</t>
+          <t>MTEX</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -2992,7 +2936,7 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>KYIV</t>
+          <t>MYFW</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -3002,7 +2946,7 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>LARK</t>
+          <t>MZTI</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -3012,7 +2956,7 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>LBRX</t>
+          <t>NBTB</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -3022,7 +2966,7 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>NBTX</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -3032,7 +2976,7 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>LFST</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -3042,7 +2986,7 @@
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>NRC</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -3052,7 +2996,7 @@
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>NRDS</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -3062,7 +3006,7 @@
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
-          <t>LIVN</t>
+          <t>NRIX</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -3072,7 +3016,7 @@
       <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr">
         <is>
-          <t>LKFN</t>
+          <t>NTLA</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -3082,7 +3026,7 @@
       <c r="A236" t="inlineStr"/>
       <c r="B236" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -3092,7 +3036,7 @@
       <c r="A237" t="inlineStr"/>
       <c r="B237" t="inlineStr">
         <is>
-          <t>LLYVA</t>
+          <t>NWBI</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -3102,7 +3046,7 @@
       <c r="A238" t="inlineStr"/>
       <c r="B238" t="inlineStr">
         <is>
-          <t>LLYVK</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -3112,7 +3056,7 @@
       <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr">
         <is>
-          <t>LMRI</t>
+          <t>NWFL</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -3122,7 +3066,7 @@
       <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>OBT</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -3132,7 +3076,7 @@
       <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr">
         <is>
-          <t>LOVE</t>
+          <t>OCTV</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -3142,7 +3086,7 @@
       <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>OIO</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -3152,7 +3096,7 @@
       <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr">
         <is>
-          <t>LSBK</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -3162,7 +3106,7 @@
       <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -3172,7 +3116,7 @@
       <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>OPK</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -3182,7 +3126,7 @@
       <c r="A246" t="inlineStr"/>
       <c r="B246" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>OPLN</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -3192,7 +3136,7 @@
       <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>ORRF</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -3202,7 +3146,7 @@
       <c r="A248" t="inlineStr"/>
       <c r="B248" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>OSW</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -3212,7 +3156,7 @@
       <c r="A249" t="inlineStr"/>
       <c r="B249" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>OVLY</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -3222,7 +3166,7 @@
       <c r="A250" t="inlineStr"/>
       <c r="B250" t="inlineStr">
         <is>
-          <t>MBWM</t>
+          <t>OZK</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -3232,7 +3176,7 @@
       <c r="A251" t="inlineStr"/>
       <c r="B251" t="inlineStr">
         <is>
-          <t>MCBS</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -3242,7 +3186,7 @@
       <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -3252,7 +3196,7 @@
       <c r="A253" t="inlineStr"/>
       <c r="B253" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -3262,7 +3206,7 @@
       <c r="A254" t="inlineStr"/>
       <c r="B254" t="inlineStr">
         <is>
-          <t>MGRC</t>
+          <t>PDLB</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -3272,7 +3216,7 @@
       <c r="A255" t="inlineStr"/>
       <c r="B255" t="inlineStr">
         <is>
-          <t>MGRT</t>
+          <t>PEBO</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -3282,7 +3226,7 @@
       <c r="A256" t="inlineStr"/>
       <c r="B256" t="inlineStr">
         <is>
-          <t>MIDD</t>
+          <t>PFIS</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -3292,7 +3236,7 @@
       <c r="A257" t="inlineStr"/>
       <c r="B257" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>PFXNZ</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -3302,7 +3246,7 @@
       <c r="A258" t="inlineStr"/>
       <c r="B258" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>PGC</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -3312,7 +3256,7 @@
       <c r="A259" t="inlineStr"/>
       <c r="B259" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>PGNY</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -3322,7 +3266,7 @@
       <c r="A260" t="inlineStr"/>
       <c r="B260" t="inlineStr">
         <is>
-          <t>MSBI</t>
+          <t>PLBC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -3332,7 +3276,7 @@
       <c r="A261" t="inlineStr"/>
       <c r="B261" t="inlineStr">
         <is>
-          <t>MSEX</t>
+          <t>PLGO</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -3342,7 +3286,7 @@
       <c r="A262" t="inlineStr"/>
       <c r="B262" t="inlineStr">
         <is>
-          <t>MTEX</t>
+          <t>PLMR</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -3352,7 +3296,7 @@
       <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr">
         <is>
-          <t>MXCT</t>
+          <t>PNFP</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -3362,7 +3306,7 @@
       <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr">
         <is>
-          <t>MYFW</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -3372,7 +3316,7 @@
       <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr">
         <is>
-          <t>MZTI</t>
+          <t>PODD</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -3382,7 +3326,7 @@
       <c r="A266" t="inlineStr"/>
       <c r="B266" t="inlineStr">
         <is>
-          <t>NAVN</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -3392,7 +3336,7 @@
       <c r="A267" t="inlineStr"/>
       <c r="B267" t="inlineStr">
         <is>
-          <t>NBBK</t>
+          <t>PRGS</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -3402,7 +3346,7 @@
       <c r="A268" t="inlineStr"/>
       <c r="B268" t="inlineStr">
         <is>
-          <t>NBN</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -3412,7 +3356,7 @@
       <c r="A269" t="inlineStr"/>
       <c r="B269" t="inlineStr">
         <is>
-          <t>NBTX</t>
+          <t>PTEN</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -3422,7 +3366,7 @@
       <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>PTLE</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
@@ -3432,7 +3376,7 @@
       <c r="A271" t="inlineStr"/>
       <c r="B271" t="inlineStr">
         <is>
-          <t>NECB</t>
+          <t>PTLO</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -3442,7 +3386,7 @@
       <c r="A272" t="inlineStr"/>
       <c r="B272" t="inlineStr">
         <is>
-          <t>NICE</t>
+          <t>PWRL</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -3452,7 +3396,7 @@
       <c r="A273" t="inlineStr"/>
       <c r="B273" t="inlineStr">
         <is>
-          <t>NMIH</t>
+          <t>PYPD</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -3462,7 +3406,7 @@
       <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr">
         <is>
-          <t>NOVT</t>
+          <t>QCRH</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -3472,7 +3416,7 @@
       <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr">
         <is>
-          <t>NPAC</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -3482,7 +3426,7 @@
       <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr">
         <is>
-          <t>NRC</t>
+          <t>RCBC</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -3492,7 +3436,7 @@
       <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr">
         <is>
-          <t>NRDS</t>
+          <t>RDWR</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
@@ -3502,7 +3446,7 @@
       <c r="A278" t="inlineStr"/>
       <c r="B278" t="inlineStr">
         <is>
-          <t>NRIX</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -3512,7 +3456,7 @@
       <c r="A279" t="inlineStr"/>
       <c r="B279" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>REF</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -3522,7 +3466,7 @@
       <c r="A280" t="inlineStr"/>
       <c r="B280" t="inlineStr">
         <is>
-          <t>NSSC</t>
+          <t>RELL</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -3532,7 +3476,7 @@
       <c r="A281" t="inlineStr"/>
       <c r="B281" t="inlineStr">
         <is>
-          <t>NTCT</t>
+          <t>REYN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
@@ -3542,7 +3486,7 @@
       <c r="A282" t="inlineStr"/>
       <c r="B282" t="inlineStr">
         <is>
-          <t>NTGR</t>
+          <t>RIGL</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
@@ -3552,7 +3496,7 @@
       <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>RMBI</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -3562,7 +3506,7 @@
       <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>ROOT</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -3572,7 +3516,7 @@
       <c r="A285" t="inlineStr"/>
       <c r="B285" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -3582,7 +3526,7 @@
       <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr">
         <is>
-          <t>NWBI</t>
+          <t>RPRX</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -3592,7 +3536,7 @@
       <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>RRBI</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -3602,7 +3546,7 @@
       <c r="A288" t="inlineStr"/>
       <c r="B288" t="inlineStr">
         <is>
-          <t>OBT</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -3612,7 +3556,7 @@
       <c r="A289" t="inlineStr"/>
       <c r="B289" t="inlineStr">
         <is>
-          <t>OFIX</t>
+          <t>RYZ</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
@@ -3622,7 +3566,7 @@
       <c r="A290" t="inlineStr"/>
       <c r="B290" t="inlineStr">
         <is>
-          <t>OFS</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
@@ -3632,7 +3576,7 @@
       <c r="A291" t="inlineStr"/>
       <c r="B291" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>SAGT</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
@@ -3642,7 +3586,7 @@
       <c r="A292" t="inlineStr"/>
       <c r="B292" t="inlineStr">
         <is>
-          <t>OMAB</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
@@ -3652,7 +3596,7 @@
       <c r="A293" t="inlineStr"/>
       <c r="B293" t="inlineStr">
         <is>
-          <t>OMCL</t>
+          <t>SBAC</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
@@ -3662,7 +3606,7 @@
       <c r="A294" t="inlineStr"/>
       <c r="B294" t="inlineStr">
         <is>
-          <t>ONC</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
@@ -3672,7 +3616,7 @@
       <c r="A295" t="inlineStr"/>
       <c r="B295" t="inlineStr">
         <is>
-          <t>OPK</t>
+          <t>SCAG</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
@@ -3682,7 +3626,7 @@
       <c r="A296" t="inlineStr"/>
       <c r="B296" t="inlineStr">
         <is>
-          <t>OPLN</t>
+          <t>SCHL</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
@@ -3692,7 +3636,7 @@
       <c r="A297" t="inlineStr"/>
       <c r="B297" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>SDGR</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
@@ -3702,7 +3646,7 @@
       <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>SFNC</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
@@ -3712,7 +3656,7 @@
       <c r="A299" t="inlineStr"/>
       <c r="B299" t="inlineStr">
         <is>
-          <t>ORKA</t>
+          <t>SGP</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
@@ -3722,7 +3666,7 @@
       <c r="A300" t="inlineStr"/>
       <c r="B300" t="inlineStr">
         <is>
-          <t>ORRF</t>
+          <t>SHPH</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
@@ -3732,7 +3676,7 @@
       <c r="A301" t="inlineStr"/>
       <c r="B301" t="inlineStr">
         <is>
-          <t>OSG</t>
+          <t>SIGI</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
@@ -3742,7 +3686,7 @@
       <c r="A302" t="inlineStr"/>
       <c r="B302" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>SNES</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
@@ -3752,7 +3696,7 @@
       <c r="A303" t="inlineStr"/>
       <c r="B303" t="inlineStr">
         <is>
-          <t>OSUR</t>
+          <t>SNFCA</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
@@ -3762,7 +3706,7 @@
       <c r="A304" t="inlineStr"/>
       <c r="B304" t="inlineStr">
         <is>
-          <t>OSW</t>
+          <t>SOMN</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
@@ -3772,7 +3716,7 @@
       <c r="A305" t="inlineStr"/>
       <c r="B305" t="inlineStr">
         <is>
-          <t>OTAI</t>
+          <t>SRCE</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
@@ -3782,7 +3726,7 @@
       <c r="A306" t="inlineStr"/>
       <c r="B306" t="inlineStr">
         <is>
-          <t>OTTR</t>
+          <t>SRPT</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
@@ -3792,7 +3736,7 @@
       <c r="A307" t="inlineStr"/>
       <c r="B307" t="inlineStr">
         <is>
-          <t>OVBC</t>
+          <t>SRZN</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
@@ -3802,7 +3746,7 @@
       <c r="A308" t="inlineStr"/>
       <c r="B308" t="inlineStr">
         <is>
-          <t>OVLY</t>
+          <t>SYNA</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
@@ -3812,7 +3756,7 @@
       <c r="A309" t="inlineStr"/>
       <c r="B309" t="inlineStr">
         <is>
-          <t>OXLCO</t>
+          <t>SYRE</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
@@ -3822,7 +3766,7 @@
       <c r="A310" t="inlineStr"/>
       <c r="B310" t="inlineStr">
         <is>
-          <t>OXLCZ</t>
+          <t>TACT</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
@@ -3832,7 +3776,7 @@
       <c r="A311" t="inlineStr"/>
       <c r="B311" t="inlineStr">
         <is>
-          <t>OZK</t>
+          <t>TCMD</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
@@ -3842,7 +3786,7 @@
       <c r="A312" t="inlineStr"/>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>TGTX</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
@@ -3852,7 +3796,7 @@
       <c r="A313" t="inlineStr"/>
       <c r="B313" t="inlineStr">
         <is>
-          <t>PACB</t>
+          <t>THFF</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
@@ -3862,7 +3806,7 @@
       <c r="A314" t="inlineStr"/>
       <c r="B314" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
@@ -3872,7 +3816,7 @@
       <c r="A315" t="inlineStr"/>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>TLS</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
@@ -3882,7 +3826,7 @@
       <c r="A316" t="inlineStr"/>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PDLB</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
@@ -3892,7 +3836,7 @@
       <c r="A317" t="inlineStr"/>
       <c r="B317" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
@@ -3902,7 +3846,7 @@
       <c r="A318" t="inlineStr"/>
       <c r="B318" t="inlineStr">
         <is>
-          <t>PEBO</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
@@ -3912,7 +3856,7 @@
       <c r="A319" t="inlineStr"/>
       <c r="B319" t="inlineStr">
         <is>
-          <t>PFBC</t>
+          <t>UTHR</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
@@ -3922,7 +3866,7 @@
       <c r="A320" t="inlineStr"/>
       <c r="B320" t="inlineStr">
         <is>
-          <t>PFIS</t>
+          <t>VIR</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
@@ -3932,7 +3876,7 @@
       <c r="A321" t="inlineStr"/>
       <c r="B321" t="inlineStr">
         <is>
-          <t>PGNY</t>
+          <t>WCCB</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
@@ -3942,7 +3886,7 @@
       <c r="A322" t="inlineStr"/>
       <c r="B322" t="inlineStr">
         <is>
-          <t>PGY</t>
+          <t>WHK</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
@@ -3952,7 +3896,7 @@
       <c r="A323" t="inlineStr"/>
       <c r="B323" t="inlineStr">
         <is>
-          <t>PLBC</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
@@ -3962,851 +3906,11 @@
       <c r="A324" t="inlineStr"/>
       <c r="B324" t="inlineStr">
         <is>
-          <t>PLBY</t>
+          <t>YSWY</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr"/>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr"/>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>PLGO</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr"/>
-      <c r="D325" t="inlineStr"/>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr"/>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>PLMR</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr"/>
-      <c r="D326" t="inlineStr"/>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr"/>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>PLSE</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr"/>
-      <c r="D327" t="inlineStr"/>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr"/>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>PLUS</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr"/>
-      <c r="D328" t="inlineStr"/>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr"/>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>PNFP</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr"/>
-      <c r="D329" t="inlineStr"/>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr"/>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>PNTG</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr"/>
-      <c r="D330" t="inlineStr"/>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr"/>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>PODD</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr"/>
-      <c r="D331" t="inlineStr"/>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr"/>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>POOL</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr"/>
-      <c r="D332" t="inlineStr"/>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr"/>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>POWW</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr"/>
-      <c r="D333" t="inlineStr"/>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr"/>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>PPLC</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr"/>
-      <c r="D334" t="inlineStr"/>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr"/>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>PRCT</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr"/>
-      <c r="D335" t="inlineStr"/>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr"/>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>PRME</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr"/>
-      <c r="D336" t="inlineStr"/>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr"/>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>PRVA</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr"/>
-      <c r="D337" t="inlineStr"/>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr"/>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>PSIG</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr"/>
-      <c r="D338" t="inlineStr"/>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr"/>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>PTON</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr"/>
-      <c r="D339" t="inlineStr"/>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr"/>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>QDEL</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr"/>
-      <c r="D340" t="inlineStr"/>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr"/>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>QLYS</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr"/>
-      <c r="D341" t="inlineStr"/>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr"/>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>QSI</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr"/>
-      <c r="D342" t="inlineStr"/>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr"/>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>RCBC</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr"/>
-      <c r="D343" t="inlineStr"/>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr"/>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>RCEL</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr"/>
-      <c r="D344" t="inlineStr"/>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr"/>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>REAL</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr"/>
-      <c r="D345" t="inlineStr"/>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr"/>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>REF</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr"/>
-      <c r="D346" t="inlineStr"/>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr"/>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>REGN</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr"/>
-      <c r="D347" t="inlineStr"/>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr"/>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>RELY</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr"/>
-      <c r="D348" t="inlineStr"/>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr"/>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>REYN</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr"/>
-      <c r="D349" t="inlineStr"/>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr"/>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>RGCO</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr"/>
-      <c r="D350" t="inlineStr"/>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr"/>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>RIGL</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr"/>
-      <c r="D351" t="inlineStr"/>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr"/>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>RLAY</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr"/>
-      <c r="D352" t="inlineStr"/>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr"/>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>RMBI</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr"/>
-      <c r="D353" t="inlineStr"/>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr"/>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>ROIV</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr"/>
-      <c r="D354" t="inlineStr"/>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr"/>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>ROOT</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr"/>
-      <c r="D355" t="inlineStr"/>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr"/>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>RPAY</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr"/>
-      <c r="D356" t="inlineStr"/>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr"/>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>RPC</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr"/>
-      <c r="D357" t="inlineStr"/>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr"/>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>RRBI</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr"/>
-      <c r="D358" t="inlineStr"/>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr"/>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>RYZ</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr"/>
-      <c r="D359" t="inlineStr"/>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr"/>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>SBAC</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr"/>
-      <c r="D360" t="inlineStr"/>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr"/>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>SBFG</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr"/>
-      <c r="D361" t="inlineStr"/>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr"/>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>SBUX</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr"/>
-      <c r="D362" t="inlineStr"/>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr"/>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>SCHL</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr"/>
-      <c r="D363" t="inlineStr"/>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr"/>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>SEPN</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr"/>
-      <c r="D364" t="inlineStr"/>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr"/>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>SEZL</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr"/>
-      <c r="D365" t="inlineStr"/>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr"/>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>SFNC</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr"/>
-      <c r="D366" t="inlineStr"/>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr"/>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>SFST</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr"/>
-      <c r="D367" t="inlineStr"/>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr"/>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>SGHT</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr"/>
-      <c r="D368" t="inlineStr"/>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr"/>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>SGP</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr"/>
-      <c r="D369" t="inlineStr"/>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr"/>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>SHOE</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr"/>
-      <c r="D370" t="inlineStr"/>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr"/>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>SHPH</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr"/>
-      <c r="D371" t="inlineStr"/>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr"/>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>SIBN</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr"/>
-      <c r="D372" t="inlineStr"/>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr"/>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>SIGI</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr"/>
-      <c r="D373" t="inlineStr"/>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr"/>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>SLAB</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr"/>
-      <c r="D374" t="inlineStr"/>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr"/>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>SNFCA</t>
-        </is>
-      </c>
-      <c r="C375" t="inlineStr"/>
-      <c r="D375" t="inlineStr"/>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr"/>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>SNY</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr"/>
-      <c r="D376" t="inlineStr"/>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr"/>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>SOMN</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr"/>
-      <c r="D377" t="inlineStr"/>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr"/>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>SPFI</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr"/>
-      <c r="D378" t="inlineStr"/>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr"/>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>SPTX</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr"/>
-      <c r="D379" t="inlineStr"/>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr"/>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>SRCE</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr"/>
-      <c r="D380" t="inlineStr"/>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr"/>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>SRZN</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr"/>
-      <c r="D381" t="inlineStr"/>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr"/>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>SSTI</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr"/>
-      <c r="D382" t="inlineStr"/>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr"/>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>STAA</t>
-        </is>
-      </c>
-      <c r="C383" t="inlineStr"/>
-      <c r="D383" t="inlineStr"/>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr"/>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>STBA</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr"/>
-      <c r="D384" t="inlineStr"/>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr"/>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>STLD</t>
-        </is>
-      </c>
-      <c r="C385" t="inlineStr"/>
-      <c r="D385" t="inlineStr"/>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr"/>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>STRC</t>
-        </is>
-      </c>
-      <c r="C386" t="inlineStr"/>
-      <c r="D386" t="inlineStr"/>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr"/>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>SUNB</t>
-        </is>
-      </c>
-      <c r="C387" t="inlineStr"/>
-      <c r="D387" t="inlineStr"/>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr"/>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>SWIM</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr"/>
-      <c r="D388" t="inlineStr"/>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr"/>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>SWRD</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr"/>
-      <c r="D389" t="inlineStr"/>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr"/>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>TACO</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr"/>
-      <c r="D390" t="inlineStr"/>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr"/>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>TACT</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr"/>
-      <c r="D391" t="inlineStr"/>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr"/>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>TBCH</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr"/>
-      <c r="D392" t="inlineStr"/>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr"/>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>TCMD</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr"/>
-      <c r="D393" t="inlineStr"/>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr"/>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>TENB</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr"/>
-      <c r="D394" t="inlineStr"/>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr"/>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>TFSL</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr"/>
-      <c r="D395" t="inlineStr"/>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr"/>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>TGTX</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr"/>
-      <c r="D396" t="inlineStr"/>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr"/>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>THFF</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr"/>
-      <c r="D397" t="inlineStr"/>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr"/>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>TILE</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr"/>
-      <c r="D398" t="inlineStr"/>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr"/>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>TMCI</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr"/>
-      <c r="D399" t="inlineStr"/>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr"/>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>TNDM</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr"/>
-      <c r="D400" t="inlineStr"/>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr"/>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>TRAX</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr"/>
-      <c r="D401" t="inlineStr"/>
-    </row>
-    <row r="402">
-      <c r="A402" t="inlineStr"/>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>TRMB</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr"/>
-      <c r="D402" t="inlineStr"/>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr"/>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>TRMD</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr"/>
-      <c r="D403" t="inlineStr"/>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr"/>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr"/>
-      <c r="D404" t="inlineStr"/>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr"/>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>UTHR</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr"/>
-      <c r="D405" t="inlineStr"/>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr"/>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>VSXY</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr"/>
-      <c r="D406" t="inlineStr"/>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr"/>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>WCCB</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr"/>
-      <c r="D407" t="inlineStr"/>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr"/>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>YMAT</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr"/>
-      <c r="D408" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
